--- a/output/mig_shocks.xlsx
+++ b/output/mig_shocks.xlsx
@@ -13,7 +13,487 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
   <si>
     <t>mig_Q_2</t>
   </si>
@@ -1089,7 +1569,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1108,11 +1588,16 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -1125,6 +1610,11 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1138,4046 +1628,4046 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="true"/>
-    <col min="2" max="2" width="13.42578125" customWidth="true"/>
-    <col min="3" max="3" width="16.42578125" customWidth="true"/>
-    <col min="4" max="4" width="16.42578125" customWidth="true"/>
-    <col min="5" max="5" width="16.42578125" customWidth="true"/>
-    <col min="6" max="6" width="16.42578125" customWidth="true"/>
-    <col min="7" max="7" width="16.42578125" customWidth="true"/>
-    <col min="8" max="8" width="16.42578125" customWidth="true"/>
-    <col min="9" max="9" width="16.42578125" customWidth="true"/>
-    <col min="10" max="10" width="16.42578125" customWidth="true"/>
-    <col min="11" max="11" width="16.42578125" customWidth="true"/>
-    <col min="12" max="12" width="16.28515625" customWidth="true"/>
-    <col min="13" max="13" width="16.42578125" customWidth="true"/>
-    <col min="14" max="14" width="16.42578125" customWidth="true"/>
-    <col min="15" max="15" width="16.42578125" customWidth="true"/>
-    <col min="16" max="16" width="16.42578125" customWidth="true"/>
-    <col min="17" max="17" width="15.7109375" customWidth="true"/>
-    <col min="18" max="18" width="16.42578125" customWidth="true"/>
-    <col min="19" max="19" width="16.42578125" customWidth="true"/>
-    <col min="20" max="20" width="16.42578125" customWidth="true"/>
-    <col min="21" max="21" width="16.28515625" customWidth="true"/>
-    <col min="22" max="22" width="15.7109375" customWidth="true"/>
-    <col min="23" max="23" width="16.42578125" customWidth="true"/>
-    <col min="24" max="24" width="16.42578125" customWidth="true"/>
-    <col min="25" max="25" width="16.42578125" customWidth="true"/>
-    <col min="26" max="26" width="16.28515625" customWidth="true"/>
-    <col min="27" max="27" width="15.7109375" customWidth="true"/>
-    <col min="28" max="28" width="16.42578125" customWidth="true"/>
-    <col min="29" max="29" width="16.42578125" customWidth="true"/>
-    <col min="30" max="30" width="16.42578125" customWidth="true"/>
-    <col min="31" max="31" width="16.42578125" customWidth="true"/>
-    <col min="32" max="32" width="15.7109375" customWidth="true"/>
-    <col min="33" max="33" width="16.42578125" customWidth="true"/>
-    <col min="34" max="34" width="15.5703125" customWidth="true"/>
-    <col min="35" max="35" width="16.42578125" customWidth="true"/>
-    <col min="36" max="36" width="16.42578125" customWidth="true"/>
-    <col min="37" max="37" width="15.7109375" customWidth="true"/>
-    <col min="38" max="38" width="16.42578125" customWidth="true"/>
-    <col min="39" max="39" width="16.42578125" customWidth="true"/>
-    <col min="40" max="40" width="16.28515625" customWidth="true"/>
-    <col min="41" max="41" width="15.42578125" customWidth="true"/>
+    <col min="2" max="2" width="14.42578125" customWidth="true"/>
+    <col min="3" max="3" width="14.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.42578125" customWidth="true"/>
+    <col min="5" max="5" width="14.42578125" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
+    <col min="7" max="7" width="14.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.42578125" customWidth="true"/>
+    <col min="9" max="9" width="14.42578125" customWidth="true"/>
+    <col min="10" max="10" width="14.42578125" customWidth="true"/>
+    <col min="11" max="11" width="14.42578125" customWidth="true"/>
+    <col min="12" max="12" width="14.42578125" customWidth="true"/>
+    <col min="13" max="13" width="14.42578125" customWidth="true"/>
+    <col min="14" max="14" width="14.42578125" customWidth="true"/>
+    <col min="15" max="15" width="14.42578125" customWidth="true"/>
+    <col min="16" max="16" width="14.42578125" customWidth="true"/>
+    <col min="17" max="17" width="14.42578125" customWidth="true"/>
+    <col min="18" max="18" width="14.42578125" customWidth="true"/>
+    <col min="19" max="19" width="14.42578125" customWidth="true"/>
+    <col min="20" max="20" width="14.42578125" customWidth="true"/>
+    <col min="21" max="21" width="13.7109375" customWidth="true"/>
+    <col min="22" max="22" width="14.42578125" customWidth="true"/>
+    <col min="23" max="23" width="14.42578125" customWidth="true"/>
+    <col min="24" max="24" width="14.42578125" customWidth="true"/>
+    <col min="25" max="25" width="14.42578125" customWidth="true"/>
+    <col min="26" max="26" width="14.42578125" customWidth="true"/>
+    <col min="27" max="27" width="14.42578125" customWidth="true"/>
+    <col min="28" max="28" width="14.42578125" customWidth="true"/>
+    <col min="29" max="29" width="13.7109375" customWidth="true"/>
+    <col min="30" max="30" width="14.42578125" customWidth="true"/>
+    <col min="31" max="31" width="14.42578125" customWidth="true"/>
+    <col min="32" max="32" width="14.42578125" customWidth="true"/>
+    <col min="33" max="33" width="14.42578125" customWidth="true"/>
+    <col min="34" max="34" width="14.42578125" customWidth="true"/>
+    <col min="35" max="35" width="14.42578125" customWidth="true"/>
+    <col min="36" max="36" width="14.42578125" customWidth="true"/>
+    <col min="37" max="37" width="14.42578125" customWidth="true"/>
+    <col min="38" max="38" width="14.42578125" customWidth="true"/>
+    <col min="39" max="39" width="14.42578125" customWidth="true"/>
+    <col min="40" max="40" width="14.42578125" customWidth="true"/>
+    <col min="41" max="41" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="B1" s="0">
-        <v>-0.4828926172556337</v>
+        <v>-0.1107428645225909</v>
       </c>
       <c r="C1" s="0">
-        <v>-0.39484432944967157</v>
+        <v>-0.095736370836377205</v>
       </c>
       <c r="D1" s="0">
-        <v>-0.39945191280445391</v>
+        <v>-0.10488887546989545</v>
       </c>
       <c r="E1" s="0">
-        <v>-0.39834168732770092</v>
+        <v>-0.095178263142475975</v>
       </c>
       <c r="F1" s="0">
-        <v>-0.3784133910899401</v>
+        <v>-0.080405561650117585</v>
       </c>
       <c r="G1" s="0">
-        <v>-0.35574995031790402</v>
+        <v>-0.088749732737430267</v>
       </c>
       <c r="H1" s="0">
-        <v>-0.359516829389113</v>
+        <v>-0.090679863714621459</v>
       </c>
       <c r="I1" s="0">
-        <v>-0.36429880065535408</v>
+        <v>-0.093856483266593779</v>
       </c>
       <c r="J1" s="0">
-        <v>-0.38738242537821532</v>
+        <v>-0.10453262505952855</v>
       </c>
       <c r="K1" s="0">
-        <v>-0.3641086410795345</v>
+        <v>-0.091259374414196251</v>
       </c>
       <c r="L1" s="0">
-        <v>-0.35128488612178393</v>
+        <v>-0.093082997989318517</v>
       </c>
       <c r="M1" s="0">
-        <v>-0.38378950777053367</v>
+        <v>-0.10783484186900835</v>
       </c>
       <c r="N1" s="0">
-        <v>-0.4200921881236116</v>
+        <v>-0.12283369596897212</v>
       </c>
       <c r="O1" s="0">
-        <v>-0.47903679194646986</v>
+        <v>-0.14681106797395399</v>
       </c>
       <c r="P1" s="0">
-        <v>-0.51589120389303478</v>
+        <v>-0.16173573355591819</v>
       </c>
       <c r="Q1" s="0">
-        <v>-0.50200016859607388</v>
+        <v>-0.15604324050607352</v>
       </c>
       <c r="R1" s="0">
-        <v>-0.49921390661362564</v>
+        <v>-0.15536181194574439</v>
       </c>
       <c r="S1" s="0">
-        <v>-0.48610791761536642</v>
+        <v>-0.1502104119090652</v>
       </c>
       <c r="T1" s="0">
-        <v>-0.46972525477307958</v>
+        <v>-0.14390485373846765</v>
       </c>
       <c r="U1" s="0">
-        <v>-0.4705878246758266</v>
+        <v>-0.14473266254801087</v>
       </c>
       <c r="V1" s="0">
-        <v>-0.46591448442666866</v>
+        <v>-0.14370178521221891</v>
       </c>
       <c r="W1" s="0">
-        <v>-0.47109859662545556</v>
+        <v>-0.14652654741622562</v>
       </c>
       <c r="X1" s="0">
-        <v>-0.47846425737199805</v>
+        <v>-0.15017414907680604</v>
       </c>
       <c r="Y1" s="0">
-        <v>-0.48596345182845058</v>
+        <v>-0.15374266878050058</v>
       </c>
       <c r="Z1" s="0">
-        <v>-0.49786784709042442</v>
+        <v>-0.15920757063091989</v>
       </c>
       <c r="AA1" s="0">
-        <v>-0.4867442581190432</v>
+        <v>-0.15525222627536026</v>
       </c>
       <c r="AB1" s="0">
-        <v>-0.47109127948726198</v>
+        <v>-0.14955049335410209</v>
       </c>
       <c r="AC1" s="0">
-        <v>-0.44999491615696785</v>
+        <v>-0.14186660452308661</v>
       </c>
       <c r="AD1" s="0">
-        <v>-0.43782211731522108</v>
+        <v>-0.13818468198484563</v>
       </c>
       <c r="AE1" s="0">
-        <v>-0.44211897148839935</v>
+        <v>-0.14111714373604786</v>
       </c>
       <c r="AF1" s="0">
-        <v>-0.44999956751630066</v>
+        <v>-0.14502784508844532</v>
       </c>
       <c r="AG1" s="0">
-        <v>-0.44920634999768333</v>
+        <v>-0.1450964111377854</v>
       </c>
       <c r="AH1" s="0">
-        <v>-0.44100530628683865</v>
+        <v>-0.14200630191622468</v>
       </c>
       <c r="AI1" s="0">
-        <v>-0.42807732332472559</v>
+        <v>-0.13698920206168227</v>
       </c>
       <c r="AJ1" s="0">
-        <v>-0.41666476244874778</v>
+        <v>-0.13249381165319327</v>
       </c>
       <c r="AK1" s="0">
-        <v>-0.41055240020246042</v>
+        <v>-0.13010872747130081</v>
       </c>
       <c r="AL1" s="0">
-        <v>-0.40987310015475004</v>
+        <v>-0.12979373998136196</v>
       </c>
       <c r="AM1" s="0">
-        <v>-0.40996687840468754</v>
+        <v>-0.12960568428678274</v>
       </c>
       <c r="AN1" s="0">
-        <v>-0.40612812220922107</v>
+        <v>-0.12766515469343107</v>
       </c>
       <c r="AO1" s="0">
-        <v>-0.39836042775243857</v>
+        <v>-0.12397941799758082</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>321</v>
+        <v>481</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.4924378346666668</v>
+        <v>-0.16275770258764655</v>
       </c>
       <c r="C2" s="0">
-        <v>0.0024309395604166228</v>
+        <v>0.022003809095469697</v>
       </c>
       <c r="D2" s="0">
-        <v>0.0032764860163193572</v>
+        <v>0.022281861504426629</v>
       </c>
       <c r="E2" s="0">
-        <v>0.0015240661836805054</v>
+        <v>0.02261190552769736</v>
       </c>
       <c r="F2" s="0">
-        <v>0.0025398906496527647</v>
+        <v>0.028312768630661178</v>
       </c>
       <c r="G2" s="0">
-        <v>0.0058814356847221583</v>
+        <v>0.022477721936252949</v>
       </c>
       <c r="H2" s="0">
-        <v>0.0046392121753471849</v>
+        <v>0.021957916390620252</v>
       </c>
       <c r="I2" s="0">
-        <v>0.0028296230326388398</v>
+        <v>0.020922668140674148</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.0052937343649305801</v>
+        <v>0.017099301718304198</v>
       </c>
       <c r="K2" s="0">
-        <v>0.0096502604302082795</v>
+        <v>0.024824626970022908</v>
       </c>
       <c r="L2" s="0">
-        <v>0.0058964723180554568</v>
+        <v>0.020728341248940754</v>
       </c>
       <c r="M2" s="0">
-        <v>0.0052421690552082465</v>
+        <v>0.020196251239284944</v>
       </c>
       <c r="N2" s="0">
-        <v>0.0065872710795137901</v>
+        <v>0.02056081273714341</v>
       </c>
       <c r="O2" s="0">
-        <v>0.0065116594881944323</v>
+        <v>0.020387482258185843</v>
       </c>
       <c r="P2" s="0">
-        <v>0.0060557431211805679</v>
+        <v>0.020053718516461132</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.0056347478972221809</v>
+        <v>0.019982026040851957</v>
       </c>
       <c r="R2" s="0">
-        <v>0.0055935890295138457</v>
+        <v>0.020282403610943137</v>
       </c>
       <c r="S2" s="0">
-        <v>0.0059527638048610387</v>
+        <v>0.020379558474728093</v>
       </c>
       <c r="T2" s="0">
-        <v>0.0080285476020832691</v>
+        <v>0.021287697432583953</v>
       </c>
       <c r="U2" s="0">
-        <v>0.0064638396833332501</v>
+        <v>0.020701105866660779</v>
       </c>
       <c r="V2" s="0">
-        <v>0.0065268080954860586</v>
+        <v>0.020590662347425646</v>
       </c>
       <c r="W2" s="0">
-        <v>0.0074163786656248898</v>
+        <v>0.020663351205557783</v>
       </c>
       <c r="X2" s="0">
-        <v>0.0072179089003471253</v>
+        <v>0.020454859007612819</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.0074642189670138248</v>
+        <v>0.020527999548952069</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.0073814699718749432</v>
+        <v>0.020452535508507032</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.0073296608760416437</v>
+        <v>0.020327874487193434</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.0073358705371526778</v>
+        <v>0.020342360347391696</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.0073532877222222126</v>
+        <v>0.020380480730023468</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.007384699726388777</v>
+        <v>0.020434819765239545</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.0073862817781249479</v>
+        <v>0.020381931488870998</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.0073580622982638566</v>
+        <v>0.020228617548805887</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.0073436392979165932</v>
+        <v>0.020133023009378061</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.007356508797222161</v>
+        <v>0.020139074256239241</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.007372994631597185</v>
+        <v>0.020160300292339832</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.0073862928249999182</v>
+        <v>0.020173072797594928</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.0073908031833332388</v>
+        <v>0.020159084700040412</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.0073830307298610731</v>
+        <v>0.020107149065063598</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.0073692589871527381</v>
+        <v>0.02003896838735927</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.0073613844149305052</v>
+        <v>0.019992830228797845</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.0073641002729166183</v>
+        <v>0.019983152365483918</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.49379786766666678</v>
+        <v>-0.16335356787586985</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0030417055368054946</v>
+        <v>0.022801556177234436</v>
       </c>
       <c r="D3" s="0">
-        <v>0.0030446016201388089</v>
+        <v>0.02279425490062878</v>
       </c>
       <c r="E3" s="0">
-        <v>0.0022842387965277271</v>
+        <v>0.02282076346023355</v>
       </c>
       <c r="F3" s="0">
-        <v>0.0028488282114582653</v>
+        <v>0.025613667151043833</v>
       </c>
       <c r="G3" s="0">
-        <v>0.005030728112847104</v>
+        <v>0.022651220722485484</v>
       </c>
       <c r="H3" s="0">
-        <v>0.0040821300322915754</v>
+        <v>0.02220556786452188</v>
       </c>
       <c r="I3" s="0">
-        <v>0.0024693637326388402</v>
+        <v>0.021396862708018178</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.0041916467312500538</v>
+        <v>0.018379945935769849</v>
       </c>
       <c r="K3" s="0">
-        <v>0.010720124317708302</v>
+        <v>0.025685909358027923</v>
       </c>
       <c r="L3" s="0">
-        <v>0.0065641840201388635</v>
+        <v>0.021424823112661497</v>
       </c>
       <c r="M3" s="0">
-        <v>0.0049700329944444288</v>
+        <v>0.020209472048681062</v>
       </c>
       <c r="N3" s="0">
-        <v>0.0061352898788193388</v>
+        <v>0.020829960136483021</v>
       </c>
       <c r="O3" s="0">
-        <v>0.0062676732513888278</v>
+        <v>0.020787227565779578</v>
       </c>
       <c r="P3" s="0">
-        <v>0.0056290780864582945</v>
+        <v>0.020457423902788565</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.0047370104256943546</v>
+        <v>0.019894454700523076</v>
       </c>
       <c r="R3" s="0">
-        <v>0.0046801776065971681</v>
+        <v>0.019909974282832425</v>
       </c>
       <c r="S3" s="0">
-        <v>0.0049690354031248782</v>
+        <v>0.020349699424266531</v>
       </c>
       <c r="T3" s="0">
-        <v>0.0068935491503471225</v>
+        <v>0.021105055585820483</v>
       </c>
       <c r="U3" s="0">
-        <v>0.0056437958729166349</v>
+        <v>0.020605459485421133</v>
       </c>
       <c r="V3" s="0">
-        <v>0.0059729179263888765</v>
+        <v>0.020691451445748483</v>
       </c>
       <c r="W3" s="0">
-        <v>0.0068839560357638607</v>
+        <v>0.020809795267345176</v>
       </c>
       <c r="X3" s="0">
-        <v>0.0071082276739583006</v>
+        <v>0.020713936699016351</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.0074045194552082583</v>
+        <v>0.020712133808092597</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.0072987098635415859</v>
+        <v>0.020634727750603418</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.0072749557506943674</v>
+        <v>0.020571288818172193</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.0072512147545137906</v>
+        <v>0.020436233909536698</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.0072725276343749146</v>
+        <v>0.020450755048063318</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.0073037269184027531</v>
+        <v>0.020488094026245865</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.0073372405038193977</v>
+        <v>0.020537350531904357</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.0073425902333332793</v>
+        <v>0.020480340578488646</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.0073194858822915876</v>
+        <v>0.020323779833662174</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.0073089759510415742</v>
+        <v>0.020224967296607332</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.007323926134722214</v>
+        <v>0.020227597551516336</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.007341988999652771</v>
+        <v>0.020245531130590057</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.007356899240972159</v>
+        <v>0.020255320757761555</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.0073632659690971436</v>
+        <v>0.020238714050839133</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.0073574736579860578</v>
+        <v>0.020184438828324054</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.0073457416975694079</v>
+        <v>0.020114175260965216</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.0073395865520832215</v>
+        <v>0.020066079899323363</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.49740144366666672</v>
+        <v>-0.16493238681031808</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0024989323968749315</v>
+        <v>0.023189948013246527</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0029152952829860639</v>
+        <v>0.023438863777525836</v>
       </c>
       <c r="E4" s="0">
-        <v>0.0020152306572916445</v>
+        <v>0.022883318704026795</v>
       </c>
       <c r="F4" s="0">
-        <v>0.0032092524850693698</v>
+        <v>0.024512750629386817</v>
       </c>
       <c r="G4" s="0">
-        <v>0.0037973479076388599</v>
+        <v>0.022734256372316259</v>
       </c>
       <c r="H4" s="0">
-        <v>0.0031572829878471769</v>
+        <v>0.022509219286223334</v>
       </c>
       <c r="I4" s="0">
-        <v>0.0020581324152777474</v>
+        <v>0.021808416587484732</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.0018554714916667056</v>
+        <v>0.020164775071835596</v>
       </c>
       <c r="K4" s="0">
-        <v>0.0089876397249999407</v>
+        <v>0.025571870905878067</v>
       </c>
       <c r="L4" s="0">
-        <v>0.0058474221979166185</v>
+        <v>0.022019070135795227</v>
       </c>
       <c r="M4" s="0">
-        <v>0.0046153907045138878</v>
+        <v>0.020841247957448843</v>
       </c>
       <c r="N4" s="0">
-        <v>0.0054451271347221164</v>
+        <v>0.020852366976117892</v>
       </c>
       <c r="O4" s="0">
-        <v>0.0055214583892360678</v>
+        <v>0.021083216987886493</v>
       </c>
       <c r="P4" s="0">
-        <v>0.0049916878871527071</v>
+        <v>0.020884458435249064</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.0042598296197915997</v>
+        <v>0.020458744810589832</v>
       </c>
       <c r="R4" s="0">
-        <v>0.0044293702190971165</v>
+        <v>0.020314049762696282</v>
       </c>
       <c r="S4" s="0">
-        <v>0.0043745725295138418</v>
+        <v>0.020240472958799469</v>
       </c>
       <c r="T4" s="0">
-        <v>0.0059992753732638349</v>
+        <v>0.021234550880934126</v>
       </c>
       <c r="U4" s="0">
-        <v>0.0050024250413193694</v>
+        <v>0.020699444948553192</v>
       </c>
       <c r="V4" s="0">
-        <v>0.00517256714861103</v>
+        <v>0.020762544324333634</v>
       </c>
       <c r="W4" s="0">
-        <v>0.0059071297638887965</v>
+        <v>0.020882819183222403</v>
       </c>
       <c r="X4" s="0">
-        <v>0.0059875766854166068</v>
+        <v>0.020726305053340333</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.0060034072010416439</v>
+        <v>0.020512046180127749</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.0058107605621526837</v>
+        <v>0.020291296516704093</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.0058724321215277153</v>
+        <v>0.020271297297075854</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.0059196320479165676</v>
+        <v>0.020200588631455664</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.0059284319496527016</v>
+        <v>0.020063987044590031</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.0059614437920138541</v>
+        <v>0.020070915158084297</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.0059963379499998748</v>
+        <v>0.020098442356457542</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.0060331389152776804</v>
+        <v>0.020138693917021125</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.0060445265736110421</v>
+        <v>0.020074295204006495</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.0060298905569444172</v>
+        <v>0.019911864364307051</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.0060255473798610515</v>
+        <v>0.019807219475648116</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.0060436922517360103</v>
+        <v>0.019803763824800775</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.0060643351229165976</v>
+        <v>0.019816014435644815</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.0060818967482638153</v>
+        <v>0.019820694345206096</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.00609110322743045</v>
+        <v>0.019799488614089995</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.0060886364562499073</v>
+        <v>0.019741201023739118</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.0060801792420137613</v>
+        <v>0.019667319615522583</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="B5" s="0">
-        <v>-0.50274217366666674</v>
+        <v>-0.16727229740129096</v>
       </c>
       <c r="C5" s="0">
-        <v>0.0018718560552081764</v>
+        <v>0.023689043374868005</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0023693725916666404</v>
+        <v>0.024184686736486945</v>
       </c>
       <c r="E5" s="0">
-        <v>0.0037398089274304769</v>
+        <v>0.024363633394098454</v>
       </c>
       <c r="F5" s="0">
-        <v>0.0041568167986110738</v>
+        <v>0.025122066683719232</v>
       </c>
       <c r="G5" s="0">
-        <v>0.002931806471527687</v>
+        <v>0.023382224592298662</v>
       </c>
       <c r="H5" s="0">
-        <v>0.0025658316555554617</v>
+        <v>0.023288036951929582</v>
       </c>
       <c r="I5" s="0">
-        <v>0.0019016814190971898</v>
+        <v>0.022787398904756142</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.00017144462326390639</v>
+        <v>0.021880746922185917</v>
       </c>
       <c r="K5" s="0">
-        <v>0.0059972802607637932</v>
+        <v>0.025094374305079496</v>
       </c>
       <c r="L5" s="0">
-        <v>0.0047908967972221115</v>
+        <v>0.022607162006737232</v>
       </c>
       <c r="M5" s="0">
-        <v>0.0039442918208332798</v>
+        <v>0.021975630707301668</v>
       </c>
       <c r="N5" s="0">
-        <v>0.0049348732881943627</v>
+        <v>0.021725611189028771</v>
       </c>
       <c r="O5" s="0">
-        <v>0.0047281903177083251</v>
+        <v>0.021321841575243045</v>
       </c>
       <c r="P5" s="0">
-        <v>0.0041786772211804832</v>
+        <v>0.021459827858516311</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.0035906633548610789</v>
+        <v>0.021073109676105744</v>
       </c>
       <c r="R5" s="0">
-        <v>0.0037480568298610679</v>
+        <v>0.021034393720896046</v>
       </c>
       <c r="S5" s="0">
-        <v>0.0038882681749999315</v>
+        <v>0.020731818994866532</v>
       </c>
       <c r="T5" s="0">
-        <v>0.0051590866725693138</v>
+        <v>0.021155923982957497</v>
       </c>
       <c r="U5" s="0">
-        <v>0.0042231317510415534</v>
+        <v>0.020927214934220846</v>
       </c>
       <c r="V5" s="0">
-        <v>0.0045637529944443367</v>
+        <v>0.020990757273174569</v>
       </c>
       <c r="W5" s="0">
-        <v>0.0050200172732637891</v>
+        <v>0.021120524979839711</v>
       </c>
       <c r="X5" s="0">
-        <v>0.004976146280902761</v>
+        <v>0.020976332363633471</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0049901479562499684</v>
+        <v>0.020740829866922716</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.0047273029826387933</v>
+        <v>0.020390288164728307</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.0048164074361110587</v>
+        <v>0.020281560009720149</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.0048908601809026786</v>
+        <v>0.020225529641220173</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.0049393252482638483</v>
+        <v>0.020133588833644987</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.0049696540892359984</v>
+        <v>0.019977342835157348</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.005011268697916571</v>
+        <v>0.019963341139622996</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.0050524328465277333</v>
+        <v>0.019971165165873956</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.0050948672354166336</v>
+        <v>0.019993394735760294</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.0051169453545137911</v>
+        <v>0.019913828240698917</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.0051172932142360414</v>
+        <v>0.019738939781287351</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.0051242388326387944</v>
+        <v>0.019622365985705815</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.0051479494885416366</v>
+        <v>0.01960668210932669</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.0051732006107638182</v>
+        <v>0.019607571392473783</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.005195313597916639</v>
+        <v>0.019601903706079518</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.005209632444097223</v>
+        <v>0.019571425340507639</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.0052129319298610532</v>
+        <v>0.019504906190675221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>325</v>
+        <v>485</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.50470724166666681</v>
+        <v>-0.16813324401817331</v>
       </c>
       <c r="C6" s="0">
-        <v>0.0020329393027777032</v>
+        <v>0.02574544796021545</v>
       </c>
       <c r="D6" s="0">
-        <v>0.0019076739225694088</v>
+        <v>0.025935891688289234</v>
       </c>
       <c r="E6" s="0">
-        <v>0.0023872155673609896</v>
+        <v>0.025750241324224123</v>
       </c>
       <c r="F6" s="0">
-        <v>0.0018722671517359402</v>
+        <v>0.025819497853944894</v>
       </c>
       <c r="G6" s="0">
-        <v>0.0019753683065971699</v>
+        <v>0.024960142753624313</v>
       </c>
       <c r="H6" s="0">
-        <v>0.0019185220874999294</v>
+        <v>0.024939283754654793</v>
       </c>
       <c r="I6" s="0">
-        <v>0.0014377883645832479</v>
+        <v>0.024466686085512345</v>
       </c>
       <c r="J6" s="0">
-        <v>-8.6631589930608044e-05</v>
+        <v>0.023743885493940218</v>
       </c>
       <c r="K6" s="0">
-        <v>0.0043818390083332215</v>
+        <v>0.026057818629300337</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0034525498385415969</v>
+        <v>0.023565074542873998</v>
       </c>
       <c r="M6" s="0">
-        <v>0.0029860478597221744</v>
+        <v>0.023355677020177028</v>
       </c>
       <c r="N6" s="0">
-        <v>0.0039348617381943498</v>
+        <v>0.023285476571790281</v>
       </c>
       <c r="O6" s="0">
-        <v>0.0041621555437499902</v>
+        <v>0.022741222833215093</v>
       </c>
       <c r="P6" s="0">
-        <v>0.0037453569201388315</v>
+        <v>0.022333585837176696</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.0030639825461804548</v>
+        <v>0.022225078184596164</v>
       </c>
       <c r="R6" s="0">
-        <v>0.0030819299315972266</v>
+        <v>0.022044066518614642</v>
       </c>
       <c r="S6" s="0">
-        <v>0.0032569399291665917</v>
+        <v>0.021822246288314279</v>
       </c>
       <c r="T6" s="0">
-        <v>0.0046652203520832769</v>
+        <v>0.021952865444760477</v>
       </c>
       <c r="U6" s="0">
-        <v>0.004082002109374927</v>
+        <v>0.021338850154075797</v>
       </c>
       <c r="V6" s="0">
-        <v>0.0042423503826388145</v>
+        <v>0.021643614506986257</v>
       </c>
       <c r="W6" s="0">
-        <v>0.004443875804513886</v>
+        <v>0.021612802657761516</v>
       </c>
       <c r="X6" s="0">
-        <v>0.0042965368072915852</v>
+        <v>0.021483389380185364</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0042997017378471067</v>
+        <v>0.021326308090679938</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.0039547885434027541</v>
+        <v>0.020897318276863402</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.0041294267520832761</v>
+        <v>0.020722352681874612</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.0042514497774304716</v>
+        <v>0.020549776419978509</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.0043240983423610824</v>
+        <v>0.020463422065053999</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.0043932093618054826</v>
+        <v>0.020340152305180281</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.0044558482190971693</v>
+        <v>0.020159942680353139</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.0045108069107638879</v>
+        <v>0.020119281905978358</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.004562116408333261</v>
+        <v>0.020101990883197911</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.0046135225465277476</v>
+        <v>0.020101213018675977</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.0046536129124999945</v>
+        <v>0.020003554261119313</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.0046786317267360489</v>
+        <v>0.019814637529101651</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.004703596206249939</v>
+        <v>0.019683961519701549</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.004736462968749966</v>
+        <v>0.019653095898628035</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.0047691069586804904</v>
+        <v>0.019639751071327552</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.0047986735402776879</v>
+        <v>0.019621264275327937</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.0048213356777776495</v>
+        <v>0.019579489303443096</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>326</v>
+        <v>486</v>
       </c>
       <c r="B7" s="0">
-        <v>-0.50929118566666676</v>
+        <v>-0.17014158728099071</v>
       </c>
       <c r="C7" s="0">
-        <v>0.00093254572500001132</v>
+        <v>0.029593391507947139</v>
       </c>
       <c r="D7" s="0">
-        <v>0.001278245295138869</v>
+        <v>0.030015497877183633</v>
       </c>
       <c r="E7" s="0">
-        <v>0.0013040787659721613</v>
+        <v>0.029309218925563058</v>
       </c>
       <c r="F7" s="0">
-        <v>0.0017960121371528581</v>
+        <v>0.029779834684115079</v>
       </c>
       <c r="G7" s="0">
-        <v>0.0013575378864583154</v>
+        <v>0.028578855912450386</v>
       </c>
       <c r="H7" s="0">
-        <v>0.001146133818402784</v>
+        <v>0.028636646793967463</v>
       </c>
       <c r="I7" s="0">
-        <v>0.00087212198611108559</v>
+        <v>0.028076009648663625</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.00032131552430553299</v>
+        <v>0.027488007646117987</v>
       </c>
       <c r="K7" s="0">
-        <v>0.0035036356555554482</v>
+        <v>0.029596191965142165</v>
       </c>
       <c r="L7" s="0">
-        <v>0.0029570276322914979</v>
+        <v>0.026399765025813815</v>
       </c>
       <c r="M7" s="0">
-        <v>0.0022077812732638202</v>
+        <v>0.026019586524999416</v>
       </c>
       <c r="N7" s="0">
-        <v>0.0027746268947916874</v>
+        <v>0.025868024778638248</v>
       </c>
       <c r="O7" s="0">
-        <v>0.0029406845124999026</v>
+        <v>0.025533138431421971</v>
       </c>
       <c r="P7" s="0">
-        <v>0.0029134241031248402</v>
+        <v>0.024988983365771281</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.0029242377586805035</v>
+        <v>0.024236305892631604</v>
       </c>
       <c r="R7" s="0">
-        <v>0.0026114381111109757</v>
+        <v>0.02413093720457482</v>
       </c>
       <c r="S7" s="0">
-        <v>0.0028073177999999306</v>
+        <v>0.023733630432480377</v>
       </c>
       <c r="T7" s="0">
-        <v>0.004000067188194345</v>
+        <v>0.023760248111773498</v>
       </c>
       <c r="U7" s="0">
-        <v>0.0036220217538193715</v>
+        <v>0.022671144964245656</v>
       </c>
       <c r="V7" s="0">
-        <v>0.0039912563232638578</v>
+        <v>0.022588911376757639</v>
       </c>
       <c r="W7" s="0">
-        <v>0.0041017242652777166</v>
+        <v>0.022545527095468729</v>
       </c>
       <c r="X7" s="0">
-        <v>0.0036738158229165934</v>
+        <v>0.022154744411615884</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.00377826995173608</v>
+        <v>0.022132344091125043</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.0034961525284721295</v>
+        <v>0.021871124774797749</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.003713637877430509</v>
+        <v>0.021685023007110064</v>
       </c>
       <c r="AB7" s="0">
-        <v>0.00389534270381936</v>
+        <v>0.021386297574410268</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.0040493114489583149</v>
+        <v>0.021179072928005492</v>
       </c>
       <c r="AD7" s="0">
-        <v>0.0041461614218749054</v>
+        <v>0.021043819837562389</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.0042465224371526786</v>
+        <v>0.020878662578113574</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.004347754480902688</v>
+        <v>0.020663137841597186</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.0044180753145832705</v>
+        <v>0.020584497230098135</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.0044813893180555295</v>
+        <v>0.020531840904753188</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.0045436759805554941</v>
+        <v>0.020498796828474195</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.0046055337437499455</v>
+        <v>0.020374987660397696</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.0046603354708332767</v>
+        <v>0.020165142273046333</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.0047070564114582436</v>
+        <v>0.02001380881741573</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.0047509264465277479</v>
+        <v>0.019961422034702244</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.0047925061677082659</v>
+        <v>0.01992800872095931</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.0048311798524304783</v>
+        <v>0.019891423422133504</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>327</v>
+        <v>487</v>
       </c>
       <c r="B8" s="0">
-        <v>-0.51378135466666675</v>
+        <v>-0.17210884531469733</v>
       </c>
       <c r="C8" s="0">
-        <v>0.0004059450753471916</v>
+        <v>0.036247249138823115</v>
       </c>
       <c r="D8" s="0">
-        <v>0.00023814120034715367</v>
+        <v>0.03682801506743022</v>
       </c>
       <c r="E8" s="0">
-        <v>0.001946030269791676</v>
+        <v>0.036148456155527801</v>
       </c>
       <c r="F8" s="0">
-        <v>0.0016896779281250223</v>
+        <v>0.036387971370162406</v>
       </c>
       <c r="G8" s="0">
-        <v>0.00041058338437493982</v>
+        <v>0.034307080416091575</v>
       </c>
       <c r="H8" s="0">
-        <v>0.00044884156944446918</v>
+        <v>0.034533043607774157</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.00015662179270847787</v>
+        <v>0.033557460197449429</v>
       </c>
       <c r="J8" s="0">
-        <v>-0.001072589937152757</v>
+        <v>0.03298797509168401</v>
       </c>
       <c r="K8" s="0">
-        <v>0.0023349780392359913</v>
+        <v>0.03540501914296771</v>
       </c>
       <c r="L8" s="0">
-        <v>0.0020153852305555549</v>
+        <v>0.031057626834548518</v>
       </c>
       <c r="M8" s="0">
-        <v>0.0016128073020833518</v>
+        <v>0.030358427387226015</v>
       </c>
       <c r="N8" s="0">
-        <v>0.0017621648211804124</v>
+        <v>0.029861607186537631</v>
       </c>
       <c r="O8" s="0">
-        <v>0.0015929735565970997</v>
+        <v>0.029423035993362347</v>
       </c>
       <c r="P8" s="0">
-        <v>0.0014230496871527332</v>
+        <v>0.029152538356885502</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.0021408942746526938</v>
+        <v>0.028066595843279928</v>
       </c>
       <c r="R8" s="0">
-        <v>0.0024854256684025962</v>
+        <v>0.027160552378449412</v>
       </c>
       <c r="S8" s="0">
-        <v>0.0018883146305554992</v>
+        <v>0.026459294123737688</v>
       </c>
       <c r="T8" s="0">
-        <v>0.0029113134458332857</v>
+        <v>0.026067308486251297</v>
       </c>
       <c r="U8" s="0">
-        <v>0.0026816231465277007</v>
+        <v>0.024868839786959456</v>
       </c>
       <c r="V8" s="0">
-        <v>0.0033249129062499772</v>
+        <v>0.024452026665562104</v>
       </c>
       <c r="W8" s="0">
-        <v>0.0034441387840277171</v>
+        <v>0.023614518321526105</v>
       </c>
       <c r="X8" s="0">
-        <v>0.0025651893951388889</v>
+        <v>0.02323418740139074</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.0029283120281249353</v>
+        <v>0.023141125511927343</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.0028156913565971498</v>
+        <v>0.023112964942801028</v>
       </c>
       <c r="AA8" s="0">
-        <v>0.003058181833333284</v>
+        <v>0.023042711139417634</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.00328505338923607</v>
+        <v>0.022661670078950955</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.0035160737649304603</v>
+        <v>0.022321763394729369</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.0037268028659721559</v>
+        <v>0.022044773597790342</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.0038565059298610875</v>
+        <v>0.02183988348720289</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.0039982449756943983</v>
+        <v>0.021614455771321778</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.0041515557222221991</v>
+        <v>0.021348149476888952</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.0042427660364582351</v>
+        <v>0.021215530077801817</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.0043220130076388474</v>
+        <v>0.021112472223821219</v>
       </c>
       <c r="AJ8" s="0">
-        <v>0.004398737899652728</v>
+        <v>0.021033438558651162</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.0044901340677082624</v>
+        <v>0.020872385564977575</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.0045858364611111035</v>
+        <v>0.020632726140877942</v>
       </c>
       <c r="AM8" s="0">
-        <v>0.0046626343802082526</v>
+        <v>0.020452164935631796</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.0047216237052082888</v>
+        <v>0.020369360540336504</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.0047756225399305232</v>
+        <v>0.02030767459316284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>328</v>
+        <v>488</v>
       </c>
       <c r="B9" s="0">
-        <v>-0.52019021066666682</v>
+        <v>-0.1749167292613526</v>
       </c>
       <c r="C9" s="0">
-        <v>-0.0008740037187500169</v>
+        <v>0.046523617663987743</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.000789853942708473</v>
+        <v>0.047208806498646637</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.00068247235694451902</v>
+        <v>0.046048064726465505</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.0011233589993057116</v>
+        <v>0.046418632751274891</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.00092194845520832212</v>
+        <v>0.043706247187409834</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.00087354198020839213</v>
+        <v>0.04418252010418873</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.0010799711399307466</v>
+        <v>0.042787320199794754</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.0019961272604167571</v>
+        <v>0.042230867673870125</v>
       </c>
       <c r="K9" s="0">
-        <v>0.00061035932708331051</v>
+        <v>0.04503339563674328</v>
       </c>
       <c r="L9" s="0">
-        <v>0.00067062152951380405</v>
+        <v>0.039248247717213205</v>
       </c>
       <c r="M9" s="0">
-        <v>0.00047321419305557198</v>
+        <v>0.038085026996394426</v>
       </c>
       <c r="N9" s="0">
-        <v>0.00090692773749989674</v>
+        <v>0.036873728620462683</v>
       </c>
       <c r="O9" s="0">
-        <v>0.00035806956249989554</v>
+        <v>0.035872474420907081</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.0001039490652778299</v>
+        <v>0.035767020562389368</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.00034396624409716026</v>
+        <v>0.034497492230983737</v>
       </c>
       <c r="R9" s="0">
-        <v>0.0012650117579861009</v>
+        <v>0.032838296737142302</v>
       </c>
       <c r="S9" s="0">
-        <v>0.0018397947829861265</v>
+        <v>0.031247160962381285</v>
       </c>
       <c r="T9" s="0">
-        <v>0.0018347045982638473</v>
+        <v>0.030313785950830431</v>
       </c>
       <c r="U9" s="0">
-        <v>0.0014005294354166305</v>
+        <v>0.028234452498058667</v>
       </c>
       <c r="V9" s="0">
-        <v>0.0021666703392360103</v>
+        <v>0.027941431256613056</v>
       </c>
       <c r="W9" s="0">
-        <v>0.002699854906944299</v>
+        <v>0.026050524877333357</v>
       </c>
       <c r="X9" s="0">
-        <v>0.002136571004166643</v>
+        <v>0.024883366201754877</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.0019201368218748622</v>
+        <v>0.024727986364617368</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.0017896289451387886</v>
+        <v>0.02451233215442741</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.0020374872777776383</v>
+        <v>0.024687927430006921</v>
       </c>
       <c r="AB9" s="0">
-        <v>0.0022408224246527331</v>
+        <v>0.024312537295184181</v>
       </c>
       <c r="AC9" s="0">
-        <v>0.0024987079545137898</v>
+        <v>0.023900587468944804</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.0028082118652777432</v>
+        <v>0.023461001197051468</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.0030839596048610747</v>
+        <v>0.023092444090852846</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.0032488551611110084</v>
+        <v>0.022795935711952601</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.003436010707986048</v>
+        <v>0.022490238311118571</v>
       </c>
       <c r="AH9" s="0">
-        <v>0.0036473845156249633</v>
+        <v>0.022155101529104423</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.0037607336652776828</v>
+        <v>0.021950905859871115</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.0038574999402776759</v>
+        <v>0.021781443285320435</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.0039501025979165596</v>
+        <v>0.021641703466905127</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.004075554295833228</v>
+        <v>0.021430415012264357</v>
       </c>
       <c r="AM9" s="0">
-        <v>0.0042186965527776787</v>
+        <v>0.021149408392297307</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.0043300146256943228</v>
+        <v>0.020928628217938686</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.0044063985809027475</v>
+        <v>0.020804915874534473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="B10" s="0">
-        <v>-0.5267394556666668</v>
+        <v>-0.17778612122431953</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.0019022347256943961</v>
+        <v>0.062976829300154399</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.0020057106954862736</v>
+        <v>0.063709398187967406</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.0015554537170140437</v>
+        <v>0.061943409687676414</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.0013172738322917441</v>
+        <v>0.062877066207258955</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.0017330117083332866</v>
+        <v>0.058930554066842569</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.0021028096680556487</v>
+        <v>0.059470472251153754</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.0023348679204862064</v>
+        <v>0.057114916395437025</v>
       </c>
       <c r="J10" s="0">
-        <v>-0.0029175823281250013</v>
+        <v>0.05633510997155608</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.0013572235100693941</v>
+        <v>0.060165239451561638</v>
       </c>
       <c r="L10" s="0">
-        <v>-0.0011525842541667561</v>
+        <v>0.052043664029636082</v>
       </c>
       <c r="M10" s="0">
-        <v>-0.0011169942826390056</v>
+        <v>0.05102779110249378</v>
       </c>
       <c r="N10" s="0">
-        <v>-0.00052226170069458178</v>
+        <v>0.048871588896928261</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.0005229103572917948</v>
+        <v>0.046968524913258092</v>
       </c>
       <c r="P10" s="0">
-        <v>-0.0016596589326389752</v>
+        <v>0.045906656441950022</v>
       </c>
       <c r="Q10" s="0">
-        <v>-0.0014247299197917007</v>
+        <v>0.044584863612058226</v>
       </c>
       <c r="R10" s="0">
-        <v>-0.00088592610034732202</v>
+        <v>0.042685333649962125</v>
       </c>
       <c r="S10" s="0">
-        <v>0.0003199413437500187</v>
+        <v>0.040214127223147364</v>
       </c>
       <c r="T10" s="0">
-        <v>0.0014482753961805313</v>
+        <v>0.037787166407845484</v>
       </c>
       <c r="U10" s="0">
-        <v>0.0001898584534721923</v>
+        <v>0.034422297350956352</v>
       </c>
       <c r="V10" s="0">
-        <v>0.00067134313923611355</v>
+        <v>0.03352055899800916</v>
       </c>
       <c r="W10" s="0">
-        <v>0.001358094420833178</v>
+        <v>0.031191021192010952</v>
       </c>
       <c r="X10" s="0">
-        <v>0.0015104520295138313</v>
+        <v>0.029133549864869674</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.0014999876482638124</v>
+        <v>0.027953672177495673</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.00036500025729163665</v>
+        <v>0.027543156066884521</v>
       </c>
       <c r="AA10" s="0">
-        <v>0.0005824089204860541</v>
+        <v>0.027618450943772278</v>
       </c>
       <c r="AB10" s="0">
-        <v>0.00083626301076383802</v>
+        <v>0.027260561276137667</v>
       </c>
       <c r="AC10" s="0">
-        <v>0.0010690753232638905</v>
+        <v>0.026887345674224312</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.0013957404496526826</v>
+        <v>0.02626311917688556</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.0017984108541665988</v>
+        <v>0.025630913409993107</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.0021589161857638035</v>
+        <v>0.025089569369724115</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.0023638208388888637</v>
+        <v>0.0246233237235279</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.002608641327083272</v>
+        <v>0.024166608480469177</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.0028979250843749198</v>
+        <v>0.023698545454423736</v>
       </c>
       <c r="AJ10" s="0">
-        <v>0.0030408956402777076</v>
+        <v>0.023363687640368679</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.0031593398409721089</v>
+        <v>0.023072498597178602</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.0032716487899304703</v>
+        <v>0.022821086018340299</v>
       </c>
       <c r="AM10" s="0">
-        <v>0.0034421725854166248</v>
+        <v>0.022512853069631626</v>
       </c>
       <c r="AN10" s="0">
-        <v>0.0036509971350693893</v>
+        <v>0.022148432288313143</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.0038111977003472135</v>
+        <v>0.021849050170244185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>330</v>
+        <v>490</v>
       </c>
       <c r="B11" s="0">
-        <v>-0.53416697766666676</v>
+        <v>-0.18104030883396921</v>
       </c>
       <c r="C11" s="0">
-        <v>-0.0023926686965278776</v>
+        <v>0.082417033661443664</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.0023956012697916576</v>
+        <v>0.083187900684074251</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.0023713778809028039</v>
+        <v>0.081251475375417784</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.0023343691312500692</v>
+        <v>0.082527438621589622</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.0024873625361112595</v>
+        <v>0.077977179343417274</v>
       </c>
       <c r="H11" s="0">
-        <v>-0.0025324071260417478</v>
+        <v>0.079741977982420567</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.0028309569968750781</v>
+        <v>0.075508680057012154</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.0036447205833334273</v>
+        <v>0.074782581055996583</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.0024393636083335215</v>
+        <v>0.08128696780926789</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.0025981001586805616</v>
+        <v>0.070213063832226003</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.0026393443673611294</v>
+        <v>0.068724498388106042</v>
       </c>
       <c r="N11" s="0">
-        <v>-0.0021597313083334671</v>
+        <v>0.065931252001297583</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.0019357323868055554</v>
+        <v>0.063552098802430138</v>
       </c>
       <c r="P11" s="0">
-        <v>-0.0025086462586805247</v>
+        <v>0.061308078331314367</v>
       </c>
       <c r="Q11" s="0">
-        <v>-0.0031029726152779213</v>
+        <v>0.059147205213859258</v>
       </c>
       <c r="R11" s="0">
-        <v>-0.0030071145479166894</v>
+        <v>0.056968454480121028</v>
       </c>
       <c r="S11" s="0">
-        <v>-0.0024106809215278524</v>
+        <v>0.054410121874042407</v>
       </c>
       <c r="T11" s="0">
-        <v>-0.00032664623194444964</v>
+        <v>0.050848437417486195</v>
       </c>
       <c r="U11" s="0">
-        <v>-6.0833586458475253e-05</v>
+        <v>0.044891316641566328</v>
       </c>
       <c r="V11" s="0">
-        <v>-0.0012201200368057163</v>
+        <v>0.043119837333470544</v>
       </c>
       <c r="W11" s="0">
-        <v>-0.0005914646861112649</v>
+        <v>0.039468786312426903</v>
       </c>
       <c r="X11" s="0">
-        <v>-0.00033705003506945361</v>
+        <v>0.036699858342891384</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.00049665725243058876</v>
+        <v>0.034478789071504048</v>
       </c>
       <c r="Z11" s="0">
-        <v>-9.9045952777876423e-05</v>
+        <v>0.033206209073975201</v>
       </c>
       <c r="AA11" s="0">
-        <v>-0.0012790440298611769</v>
+        <v>0.033099761797929131</v>
       </c>
       <c r="AB11" s="0">
-        <v>-0.0010957909861111781</v>
+        <v>0.032245780174389185</v>
       </c>
       <c r="AC11" s="0">
-        <v>-0.0008573763458333836</v>
+        <v>0.032037694421636891</v>
       </c>
       <c r="AD11" s="0">
-        <v>-0.00059094257881958569</v>
+        <v>0.031396206815329598</v>
       </c>
       <c r="AE11" s="0">
-        <v>-0.00017166774375004801</v>
+        <v>0.030372929288858624</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.00036943384444443252</v>
+        <v>0.029379081735084606</v>
       </c>
       <c r="AG11" s="0">
-        <v>0.00085960465173606825</v>
+        <v>0.028514607761855371</v>
       </c>
       <c r="AH11" s="0">
-        <v>0.0011210676368055283</v>
+        <v>0.027733687009058892</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.0014550042184026668</v>
+        <v>0.026997858408104626</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.0018683357249999477</v>
+        <v>0.026284466074741122</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.002057800126041565</v>
+        <v>0.02571131377548258</v>
       </c>
       <c r="AL11" s="0">
-        <v>0.0022094327899305211</v>
+        <v>0.025198851193996747</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.0023517921927082575</v>
+        <v>0.024745178195560914</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.0025946531288194023</v>
+        <v>0.024261787759347765</v>
       </c>
       <c r="AO11" s="0">
-        <v>0.0029112293253472084</v>
+        <v>0.023747970472920588</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>331</v>
+        <v>491</v>
       </c>
       <c r="B12" s="0">
-        <v>-0.54010278066666673</v>
+        <v>-0.18364093614627086</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.0012589136989583629</v>
+        <v>0.10517090094155176</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.0013484904135416817</v>
+        <v>0.10580993015471624</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.0011104577222222911</v>
+        <v>0.10320950836635356</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.0014117062124999755</v>
+        <v>0.10545627080138108</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.0017060296013888801</v>
+        <v>0.10002702104021828</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.0019329867430557526</v>
+        <v>0.10249658532690521</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.0018152979701390182</v>
+        <v>0.097818860182608894</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.0027931833152778909</v>
+        <v>0.096480363328798877</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.0024556320791667688</v>
+        <v>0.10457011934048537</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.0020892245600695478</v>
+        <v>0.092170235015842816</v>
       </c>
       <c r="M12" s="0">
-        <v>-0.0030010287576388581</v>
+        <v>0.091280531989394731</v>
       </c>
       <c r="N12" s="0">
-        <v>-0.0027473303048612951</v>
+        <v>0.088191098862777553</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.002898969580902854</v>
+        <v>0.085696331722334401</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.0031300779326389741</v>
+        <v>0.082653410099551294</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.0032947748263889576</v>
+        <v>0.079976412685900986</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.0040389289263889072</v>
+        <v>0.07704471357104048</v>
       </c>
       <c r="S12" s="0">
-        <v>-0.0043563784843749787</v>
+        <v>0.074705474262344765</v>
       </c>
       <c r="T12" s="0">
-        <v>-0.0035194275847222345</v>
+        <v>0.070610982406867362</v>
       </c>
       <c r="U12" s="0">
-        <v>-0.0020370071708334372</v>
+        <v>0.062823104733518972</v>
       </c>
       <c r="V12" s="0">
-        <v>-0.0016345595069445773</v>
+        <v>0.060080984140842668</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.0031020246708333152</v>
+        <v>0.054805642067428433</v>
       </c>
       <c r="X12" s="0">
-        <v>-0.0030855958704860695</v>
+        <v>0.050516949582177208</v>
       </c>
       <c r="Y12" s="0">
-        <v>-0.0022165050329860936</v>
+        <v>0.047805674140542903</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.0016095349246528787</v>
+        <v>0.045591282442345053</v>
       </c>
       <c r="AA12" s="0">
-        <v>-0.0021270662722222564</v>
+        <v>0.044207832351133965</v>
       </c>
       <c r="AB12" s="0">
-        <v>-0.0039886739572917995</v>
+        <v>0.041804785931248117</v>
       </c>
       <c r="AC12" s="0">
-        <v>-0.0038247649531251149</v>
+        <v>0.04124962684251253</v>
       </c>
       <c r="AD12" s="0">
-        <v>-0.0035526264684028197</v>
+        <v>0.040871930009048388</v>
       </c>
       <c r="AE12" s="0">
-        <v>-0.0032389964229166956</v>
+        <v>0.039816460603801916</v>
       </c>
       <c r="AF12" s="0">
-        <v>-0.002680240570138992</v>
+        <v>0.038230696842989208</v>
       </c>
       <c r="AG12" s="0">
-        <v>-0.0019187707357640202</v>
+        <v>0.036712809387534427</v>
       </c>
       <c r="AH12" s="0">
-        <v>-0.0012243522788195071</v>
+        <v>0.035366278790592599</v>
       </c>
       <c r="AI12" s="0">
-        <v>-0.00087084777118062728</v>
+        <v>0.034103804113198348</v>
       </c>
       <c r="AJ12" s="0">
-        <v>-0.00039050541805563197</v>
+        <v>0.03292775661151566</v>
       </c>
       <c r="AK12" s="0">
-        <v>0.00022761121423597788</v>
+        <v>0.031813303143721057</v>
       </c>
       <c r="AL12" s="0">
-        <v>0.00049480840277776796</v>
+        <v>0.030846806921430672</v>
       </c>
       <c r="AM12" s="0">
-        <v>0.00070404531944434591</v>
+        <v>0.029961601608531025</v>
       </c>
       <c r="AN12" s="0">
-        <v>0.00090023518784715373</v>
+        <v>0.029160243290941117</v>
       </c>
       <c r="AO12" s="0">
-        <v>0.001266679946180516</v>
+        <v>0.028362086023628077</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>332</v>
+        <v>492</v>
       </c>
       <c r="B13" s="0">
-        <v>-0.54377568666666676</v>
+        <v>-0.18525013032928478</v>
       </c>
       <c r="C13" s="0">
-        <v>0.00093759804756943276</v>
+        <v>0.1236099553859327</v>
       </c>
       <c r="D13" s="0">
-        <v>0.00098620421249984115</v>
+        <v>0.12463348074012075</v>
       </c>
       <c r="E13" s="0">
-        <v>0.00083020382152776406</v>
+        <v>0.12281989464294402</v>
       </c>
       <c r="F13" s="0">
-        <v>0.00080985442673608965</v>
+        <v>0.1251306952946255</v>
       </c>
       <c r="G13" s="0">
-        <v>0.00067133596319435187</v>
+        <v>0.12044374451355407</v>
       </c>
       <c r="H13" s="0">
-        <v>0.00046256228749985782</v>
+        <v>0.12355693060213016</v>
       </c>
       <c r="I13" s="0">
-        <v>0.00039138240312497352</v>
+        <v>0.11889407990501209</v>
       </c>
       <c r="J13" s="0">
-        <v>-2.0058576736258459e-05</v>
+        <v>0.11803091088152019</v>
       </c>
       <c r="K13" s="0">
-        <v>-7.5497335763952123e-05</v>
+        <v>0.12598208324776061</v>
       </c>
       <c r="L13" s="0">
-        <v>-7.8916111805549249e-05</v>
+        <v>0.11443764961056525</v>
       </c>
       <c r="M13" s="0">
-        <v>-0.00062485710902782099</v>
+        <v>0.11414138028525442</v>
       </c>
       <c r="N13" s="0">
-        <v>-0.0012866804635417459</v>
+        <v>0.11162469666438832</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.0017404332861110641</v>
+        <v>0.10898437954568645</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.0020971036072916513</v>
+        <v>0.10627124465019205</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.0024026201020832536</v>
+        <v>0.10334913969679263</v>
       </c>
       <c r="R13" s="0">
-        <v>-0.0027633389982638645</v>
+        <v>0.10106940497246596</v>
       </c>
       <c r="S13" s="0">
-        <v>-0.003872841089583412</v>
+        <v>0.098680004715177974</v>
       </c>
       <c r="T13" s="0">
-        <v>-0.004067966273264001</v>
+        <v>0.094977453863563294</v>
       </c>
       <c r="U13" s="0">
-        <v>-0.004350294063888982</v>
+        <v>0.086600249258649592</v>
       </c>
       <c r="V13" s="0">
-        <v>-0.0032110383677084178</v>
+        <v>0.084455502102507019</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.0029478177281250231</v>
+        <v>0.078559349317629396</v>
       </c>
       <c r="X13" s="0">
-        <v>-0.0055348130409723639</v>
+        <v>0.073457918609011824</v>
       </c>
       <c r="Y13" s="0">
-        <v>-0.0052908920253472713</v>
+        <v>0.07019333540858845</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.0049824363972222896</v>
+        <v>0.068414551002977345</v>
       </c>
       <c r="AA13" s="0">
-        <v>-0.0040781414652778514</v>
+        <v>0.066881294905168476</v>
       </c>
       <c r="AB13" s="0">
-        <v>-0.0050326874284722933</v>
+        <v>0.063354609597234671</v>
       </c>
       <c r="AC13" s="0">
-        <v>-0.0078827918295139576</v>
+        <v>0.06148847910731834</v>
       </c>
       <c r="AD13" s="0">
-        <v>-0.0077441287843751372</v>
+        <v>0.060583194769290166</v>
       </c>
       <c r="AE13" s="0">
-        <v>-0.0076003622874999954</v>
+        <v>0.059851706829368877</v>
       </c>
       <c r="AF13" s="0">
-        <v>-0.0074809151940973262</v>
+        <v>0.058514337491148496</v>
       </c>
       <c r="AG13" s="0">
-        <v>-0.006946257474305606</v>
+        <v>0.056791870843915765</v>
       </c>
       <c r="AH13" s="0">
-        <v>-0.0060468370194445287</v>
+        <v>0.055091931349643554</v>
       </c>
       <c r="AI13" s="0">
-        <v>-0.0051731678572917716</v>
+        <v>0.053561619492070535</v>
       </c>
       <c r="AJ13" s="0">
-        <v>-0.0048484907340278216</v>
+        <v>0.052020119809765203</v>
       </c>
       <c r="AK13" s="0">
-        <v>-0.0042609321079861706</v>
+        <v>0.050550395449263721</v>
       </c>
       <c r="AL13" s="0">
-        <v>-0.0033738271392361741</v>
+        <v>0.04912804150994067</v>
       </c>
       <c r="AM13" s="0">
-        <v>-0.0030846431871527922</v>
+        <v>0.04781962129365367</v>
       </c>
       <c r="AN13" s="0">
-        <v>-0.0029026082815972734</v>
+        <v>0.046558579836719752</v>
       </c>
       <c r="AO13" s="0">
-        <v>-0.0027317998805556076</v>
+        <v>0.045370169602065816</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>333</v>
+        <v>493</v>
       </c>
       <c r="B14" s="0">
-        <v>-0.5451120816666668</v>
+        <v>-0.18583563920433055</v>
       </c>
       <c r="C14" s="0">
-        <v>0.003258952246874891</v>
+        <v>0.13642670785816144</v>
       </c>
       <c r="D14" s="0">
-        <v>0.0032760685607639006</v>
+        <v>0.13840412311818437</v>
       </c>
       <c r="E14" s="0">
-        <v>0.0032246138975694505</v>
+        <v>0.13657559537030201</v>
       </c>
       <c r="F14" s="0">
-        <v>0.0031830448809027079</v>
+        <v>0.1381450592040184</v>
       </c>
       <c r="G14" s="0">
-        <v>0.0031236138211804261</v>
+        <v>0.13591262323497491</v>
       </c>
       <c r="H14" s="0">
-        <v>0.0029819970364582948</v>
+        <v>0.1379481251806268</v>
       </c>
       <c r="I14" s="0">
-        <v>0.0029446201718749125</v>
+        <v>0.13466619138407199</v>
       </c>
       <c r="J14" s="0">
-        <v>0.0026328376343749404</v>
+        <v>0.1345721230843277</v>
       </c>
       <c r="K14" s="0">
-        <v>0.0027135135340277117</v>
+        <v>0.1398904068364718</v>
       </c>
       <c r="L14" s="0">
-        <v>0.0026138630072917168</v>
+        <v>0.13136752439894722</v>
       </c>
       <c r="M14" s="0">
-        <v>0.0022043917052082525</v>
+        <v>0.1321058015538438</v>
       </c>
       <c r="N14" s="0">
-        <v>0.0019227563847221685</v>
+        <v>0.13054982686680758</v>
       </c>
       <c r="O14" s="0">
-        <v>0.0012052864961804581</v>
+        <v>0.12827705153326774</v>
       </c>
       <c r="P14" s="0">
-        <v>0.00081122831666646843</v>
+        <v>0.12615583504482186</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.00033378712395826238</v>
+        <v>0.12446222609075301</v>
       </c>
       <c r="R14" s="0">
-        <v>-6.6506729166748713e-05</v>
+        <v>0.12244466268290073</v>
       </c>
       <c r="S14" s="0">
-        <v>-0.00064838009062506696</v>
+        <v>0.1212225646633048</v>
       </c>
       <c r="T14" s="0">
-        <v>-0.0014533225062499655</v>
+        <v>0.11866224075875043</v>
       </c>
       <c r="U14" s="0">
-        <v>-0.0024880300899305929</v>
+        <v>0.11249060037861129</v>
       </c>
       <c r="V14" s="0">
-        <v>-0.0035229568670138711</v>
+        <v>0.10939356800451933</v>
       </c>
       <c r="W14" s="0">
-        <v>-0.0025350514833334392</v>
+        <v>0.10585606776406307</v>
       </c>
       <c r="X14" s="0">
-        <v>-0.0031276072906249999</v>
+        <v>0.10222501337494008</v>
       </c>
       <c r="Y14" s="0">
-        <v>-0.005907369944791796</v>
+        <v>0.099394737870169891</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0.0065680051218749425</v>
+        <v>0.098339032493910516</v>
       </c>
       <c r="AA14" s="0">
-        <v>-0.0066074517086806006</v>
+        <v>0.097075998687030637</v>
       </c>
       <c r="AB14" s="0">
-        <v>-0.0062425581288195753</v>
+        <v>0.09385086626814465</v>
       </c>
       <c r="AC14" s="0">
-        <v>-0.0080290279454862112</v>
+        <v>0.091946295399886982</v>
       </c>
       <c r="AD14" s="0">
-        <v>-0.01189313716840279</v>
+        <v>0.089947111790312326</v>
       </c>
       <c r="AE14" s="0">
-        <v>-0.011911753951041604</v>
+        <v>0.088885884680601449</v>
       </c>
       <c r="AF14" s="0">
-        <v>-0.012378818603819619</v>
+        <v>0.087875244009705616</v>
       </c>
       <c r="AG14" s="0">
-        <v>-0.013069032662847258</v>
+        <v>0.086478063459015306</v>
       </c>
       <c r="AH14" s="0">
-        <v>-0.013143930084027922</v>
+        <v>0.084885126777531461</v>
       </c>
       <c r="AI14" s="0">
-        <v>-0.012514007937500071</v>
+        <v>0.083331460452876302</v>
       </c>
       <c r="AJ14" s="0">
-        <v>-0.011963127190972367</v>
+        <v>0.081910971925124115</v>
       </c>
       <c r="AK14" s="0">
-        <v>-0.012166992061805659</v>
+        <v>0.080357392107367642</v>
       </c>
       <c r="AL14" s="0">
-        <v>-0.011874903290972239</v>
+        <v>0.078884659462459095</v>
       </c>
       <c r="AM14" s="0">
-        <v>-0.010917204029513961</v>
+        <v>0.077500135496956182</v>
       </c>
       <c r="AN14" s="0">
-        <v>-0.011096065855208337</v>
+        <v>0.076074802449707588</v>
       </c>
       <c r="AO14" s="0">
-        <v>-0.011439692864236073</v>
+        <v>0.074639483208057994</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="B15" s="0">
-        <v>-0.54538401416666682</v>
+        <v>-0.18595477979686748</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0043119079489583037</v>
+        <v>0.14469825244242859</v>
       </c>
       <c r="D15" s="0">
-        <v>0.0043097073163192992</v>
+        <v>0.14567493402533585</v>
       </c>
       <c r="E15" s="0">
-        <v>0.0043023794392359482</v>
+        <v>0.14497415290844629</v>
       </c>
       <c r="F15" s="0">
-        <v>0.0042947198850694637</v>
+        <v>0.14591656466487285</v>
       </c>
       <c r="G15" s="0">
-        <v>0.0042760345576388073</v>
+        <v>0.14445119496873218</v>
       </c>
       <c r="H15" s="0">
-        <v>0.0042547477750000109</v>
+        <v>0.14573615521202932</v>
       </c>
       <c r="I15" s="0">
-        <v>0.0042229447024304543</v>
+        <v>0.14402597689694804</v>
       </c>
       <c r="J15" s="0">
-        <v>0.0041604741687499827</v>
+        <v>0.14390432092556693</v>
       </c>
       <c r="K15" s="0">
-        <v>0.004153557117708262</v>
+        <v>0.14692018299971935</v>
       </c>
       <c r="L15" s="0">
-        <v>0.0041590607614583322</v>
+        <v>0.14222715153504792</v>
       </c>
       <c r="M15" s="0">
-        <v>0.0040002896982638259</v>
+        <v>0.14304334495802171</v>
       </c>
       <c r="N15" s="0">
-        <v>0.003884843759374923</v>
+        <v>0.14221652295487697</v>
       </c>
       <c r="O15" s="0">
-        <v>0.0037090139468749501</v>
+        <v>0.14126882865425147</v>
       </c>
       <c r="P15" s="0">
-        <v>0.0033863861090277503</v>
+        <v>0.13974342701120618</v>
       </c>
       <c r="Q15" s="0">
-        <v>0.0031246095690972146</v>
+        <v>0.1388241754703787</v>
       </c>
       <c r="R15" s="0">
-        <v>0.0028637848652778302</v>
+        <v>0.1378403322788912</v>
       </c>
       <c r="S15" s="0">
-        <v>0.0026007332305554298</v>
+        <v>0.13729175789297757</v>
       </c>
       <c r="T15" s="0">
-        <v>0.0021905642597221937</v>
+        <v>0.13611295440155491</v>
       </c>
       <c r="U15" s="0">
-        <v>0.0014016080451388917</v>
+        <v>0.13219485176763174</v>
       </c>
       <c r="V15" s="0">
-        <v>0.00044295978958319715</v>
+        <v>0.13044680540388121</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.00025985552013907485</v>
+        <v>0.12366450757937004</v>
       </c>
       <c r="X15" s="0">
-        <v>9.9626981597155349e-05</v>
+        <v>0.12601505537072361</v>
       </c>
       <c r="Y15" s="0">
-        <v>-0.00086567061666686929</v>
+        <v>0.12477298393958049</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0.0031994744954861867</v>
+        <v>0.12461770246088336</v>
       </c>
       <c r="AA15" s="0">
-        <v>-0.0039627835774306286</v>
+        <v>0.12294262895440075</v>
       </c>
       <c r="AB15" s="0">
-        <v>-0.004589484615625028</v>
+        <v>0.12010389318417192</v>
       </c>
       <c r="AC15" s="0">
-        <v>-0.0046975563597222436</v>
+        <v>0.11843277682515395</v>
       </c>
       <c r="AD15" s="0">
-        <v>-0.0067036266996527427</v>
+        <v>0.11644737637291236</v>
       </c>
       <c r="AE15" s="0">
-        <v>-0.010157834427083401</v>
+        <v>0.11438502839354509</v>
       </c>
       <c r="AF15" s="0">
-        <v>-0.010414189185763978</v>
+        <v>0.11326616233672976</v>
       </c>
       <c r="AG15" s="0">
-        <v>-0.011406405736805514</v>
+        <v>0.11205673665216845</v>
       </c>
       <c r="AH15" s="0">
-        <v>-0.012681243906250139</v>
+        <v>0.11045419090223814</v>
       </c>
       <c r="AI15" s="0">
-        <v>-0.013426156884375096</v>
+        <v>0.10864526749254681</v>
       </c>
       <c r="AJ15" s="0">
-        <v>-0.013283622095139003</v>
+        <v>0.10695283559850001</v>
       </c>
       <c r="AK15" s="0">
-        <v>-0.013555566696875077</v>
+        <v>0.10524569973782406</v>
       </c>
       <c r="AL15" s="0">
-        <v>-0.014364485482986189</v>
+        <v>0.10341343322223258</v>
       </c>
       <c r="AM15" s="0">
-        <v>-0.014652180604861176</v>
+        <v>0.10167380389613098</v>
       </c>
       <c r="AN15" s="0">
-        <v>-0.014147040361111141</v>
+        <v>0.10007745388822817</v>
       </c>
       <c r="AO15" s="0">
-        <v>-0.015058574748263998</v>
+        <v>0.098265776604646318</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>335</v>
+        <v>495</v>
       </c>
       <c r="B16" s="0">
-        <v>-0.5454146542666668</v>
+        <v>-0.18596820400938119</v>
       </c>
       <c r="C16" s="0">
-        <v>0.0045521309862500692</v>
+        <v>0.14853665947761849</v>
       </c>
       <c r="D16" s="0">
-        <v>0.004551325316319299</v>
+        <v>0.14910668529066889</v>
       </c>
       <c r="E16" s="0">
-        <v>0.0045509407163194515</v>
+        <v>0.14877598609941203</v>
       </c>
       <c r="F16" s="0">
-        <v>0.0045505511084722458</v>
+        <v>0.14926832320897021</v>
       </c>
       <c r="G16" s="0">
-        <v>0.0045488375643748524</v>
+        <v>0.14857821766596532</v>
       </c>
       <c r="H16" s="0">
-        <v>0.0045438292174304626</v>
+        <v>0.14925554663181534</v>
       </c>
       <c r="I16" s="0">
-        <v>0.0045307833797222363</v>
+        <v>0.14840673488680128</v>
       </c>
       <c r="J16" s="0">
-        <v>0.0045242903538889045</v>
+        <v>0.14839332481216494</v>
       </c>
       <c r="K16" s="0">
-        <v>0.0045264007223609903</v>
+        <v>0.14987502677819012</v>
       </c>
       <c r="L16" s="0">
-        <v>0.0045189494759722013</v>
+        <v>0.14756646984426186</v>
       </c>
       <c r="M16" s="0">
-        <v>0.0044885830363887713</v>
+        <v>0.14812856219773465</v>
       </c>
       <c r="N16" s="0">
-        <v>0.0044685073614582063</v>
+        <v>0.1478034722972936</v>
       </c>
       <c r="O16" s="0">
-        <v>0.0044490970392360172</v>
+        <v>0.14739231988097323</v>
       </c>
       <c r="P16" s="0">
-        <v>0.004411862891666507</v>
+        <v>0.14665805990630987</v>
       </c>
       <c r="Q16" s="0">
-        <v>0.0043163303388888963</v>
+        <v>0.14627296244498464</v>
       </c>
       <c r="R16" s="0">
-        <v>0.004261338590972108</v>
+        <v>0.14589178332226399</v>
       </c>
       <c r="S16" s="0">
-        <v>0.004178010708333236</v>
+        <v>0.14575206390474826</v>
       </c>
       <c r="T16" s="0">
-        <v>0.004084635047569396</v>
+        <v>0.14542664041042103</v>
       </c>
       <c r="U16" s="0">
-        <v>0.003880079288194338</v>
+        <v>0.14143893161188895</v>
       </c>
       <c r="V16" s="0">
-        <v>0.0035548711395831933</v>
+        <v>0.13880691127573402</v>
       </c>
       <c r="W16" s="0">
-        <v>0.0032287018555555709</v>
+        <v>0.13568204609754575</v>
       </c>
       <c r="X16" s="0">
-        <v>0.0029211234142361153</v>
+        <v>0.12721722434518265</v>
       </c>
       <c r="Y16" s="0">
-        <v>0.0029509672239582678</v>
+        <v>0.13526554483878148</v>
       </c>
       <c r="Z16" s="0">
-        <v>0.0023515397579860768</v>
+        <v>0.1304359634176534</v>
       </c>
       <c r="AA16" s="0">
-        <v>0.0013980344854166433</v>
+        <v>0.13299240873596269</v>
       </c>
       <c r="AB16" s="0">
-        <v>0.00088194582083323024</v>
+        <v>0.13389049051599225</v>
       </c>
       <c r="AC16" s="0">
-        <v>0.00052156769340272382</v>
+        <v>0.13241495746737722</v>
       </c>
       <c r="AD16" s="0">
-        <v>0.00039018913437505187</v>
+        <v>0.13094572733106269</v>
       </c>
       <c r="AE16" s="0">
-        <v>-0.00073699508923608104</v>
+        <v>0.12924303141549001</v>
       </c>
       <c r="AF16" s="0">
-        <v>-0.0023153351940972114</v>
+        <v>0.12765506755268205</v>
       </c>
       <c r="AG16" s="0">
-        <v>-0.0024710858680555559</v>
+        <v>0.126678214302512</v>
       </c>
       <c r="AH16" s="0">
-        <v>-0.0031633479461806715</v>
+        <v>0.12557664515789399</v>
       </c>
       <c r="AI16" s="0">
-        <v>-0.0039778078072916223</v>
+        <v>0.12411798939855165</v>
       </c>
       <c r="AJ16" s="0">
-        <v>-0.0045377240145834108</v>
+        <v>0.1224345306471281</v>
       </c>
       <c r="AK16" s="0">
-        <v>-0.0045329532954861973</v>
+        <v>0.12083454892746448</v>
       </c>
       <c r="AL16" s="0">
-        <v>-0.0049929822718750572</v>
+        <v>0.11912669492788301</v>
       </c>
       <c r="AM16" s="0">
-        <v>-0.0055636083506945821</v>
+        <v>0.11738725123768901</v>
       </c>
       <c r="AN16" s="0">
-        <v>-0.0058231000187500825</v>
+        <v>0.1157042589153804</v>
       </c>
       <c r="AO16" s="0">
-        <v>-0.005628624446180619</v>
+        <v>0.11410340427010869</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>336</v>
+        <v>496</v>
       </c>
       <c r="B17" s="0">
-        <v>-0.31117788041103289</v>
+        <v>-0.084623364717872476</v>
       </c>
       <c r="C17" s="0">
-        <v>-0.23541067968596968</v>
+        <v>-0.060831658554711836</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.22728820051482168</v>
+        <v>-0.050816315161778113</v>
       </c>
       <c r="E17" s="0">
-        <v>-0.23888906605653948</v>
+        <v>-0.05557107567120969</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.22422071734019139</v>
+        <v>-0.025815607778539425</v>
       </c>
       <c r="G17" s="0">
-        <v>-0.19172630703164179</v>
+        <v>-0.036554068633100061</v>
       </c>
       <c r="H17" s="0">
-        <v>-0.19131704841236713</v>
+        <v>-0.036855280708466123</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.20056858547375017</v>
+        <v>-0.041206134055569242</v>
       </c>
       <c r="J17" s="0">
-        <v>-0.25012216655180564</v>
+        <v>-0.063160911718041834</v>
       </c>
       <c r="K17" s="0">
-        <v>-0.22315630456115182</v>
+        <v>-0.040418567004743382</v>
       </c>
       <c r="L17" s="0">
-        <v>-0.18808467899294051</v>
+        <v>-0.033903819269692305</v>
       </c>
       <c r="M17" s="0">
-        <v>-0.21480172231507882</v>
+        <v>-0.048567170259762642</v>
       </c>
       <c r="N17" s="0">
-        <v>-0.24666685562155805</v>
+        <v>-0.062676099293552473</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.30093392663928681</v>
+        <v>-0.086467328032466581</v>
       </c>
       <c r="P17" s="0">
-        <v>-0.3185099169438329</v>
+        <v>-0.093771162639060351</v>
       </c>
       <c r="Q17" s="0">
-        <v>-0.27887122783754204</v>
+        <v>-0.075987012494404357</v>
       </c>
       <c r="R17" s="0">
-        <v>-0.27848435743881578</v>
+        <v>-0.075813882605074448</v>
       </c>
       <c r="S17" s="0">
-        <v>-0.26650123039459789</v>
+        <v>-0.070446840083892945</v>
       </c>
       <c r="T17" s="0">
-        <v>-0.24766387710750482</v>
+        <v>-0.061901028161008065</v>
       </c>
       <c r="U17" s="0">
-        <v>-0.24978785084856531</v>
+        <v>-0.062143206698986472</v>
       </c>
       <c r="V17" s="0">
-        <v>-0.25318788634898454</v>
+        <v>-0.063702137916616219</v>
       </c>
       <c r="W17" s="0">
-        <v>-0.26105715902030557</v>
+        <v>-0.066043518044152927</v>
       </c>
       <c r="X17" s="0">
-        <v>-0.26618632837044781</v>
+        <v>-0.068058877962437037</v>
       </c>
       <c r="Y17" s="0">
-        <v>-0.27434822013443649</v>
+        <v>-0.071333974214442153</v>
       </c>
       <c r="Z17" s="0">
-        <v>-0.29072766790040006</v>
+        <v>-0.078151942336847025</v>
       </c>
       <c r="AA17" s="0">
-        <v>-0.27914608162049126</v>
+        <v>-0.072641866238364369</v>
       </c>
       <c r="AB17" s="0">
-        <v>-0.26267245837337638</v>
+        <v>-0.064973151972641377</v>
       </c>
       <c r="AC17" s="0">
-        <v>-0.24104149236037958</v>
+        <v>-0.054835555604305058</v>
       </c>
       <c r="AD17" s="0">
-        <v>-0.23355749774627971</v>
+        <v>-0.050609587471828157</v>
       </c>
       <c r="AE17" s="0">
-        <v>-0.24599093634348607</v>
+        <v>-0.05520668776368802</v>
       </c>
       <c r="AF17" s="0">
-        <v>-0.25775643223659706</v>
+        <v>-0.059855219233771448</v>
       </c>
       <c r="AG17" s="0">
-        <v>-0.25598857464745711</v>
+        <v>-0.058785211578123761</v>
       </c>
       <c r="AH17" s="0">
-        <v>-0.24715890675525681</v>
+        <v>-0.054794331974886833</v>
       </c>
       <c r="AI17" s="0">
-        <v>-0.23602202399367767</v>
+        <v>-0.049817231045056289</v>
       </c>
       <c r="AJ17" s="0">
-        <v>-0.227464963063087</v>
+        <v>-0.046095773927360917</v>
       </c>
       <c r="AK17" s="0">
-        <v>-0.22648570323560008</v>
+        <v>-0.045733726189365359</v>
       </c>
       <c r="AL17" s="0">
-        <v>-0.23112223582062935</v>
+        <v>-0.047946620687525643</v>
       </c>
       <c r="AM17" s="0">
-        <v>-0.23517931979196971</v>
+        <v>-0.050043601956575208</v>
       </c>
       <c r="AN17" s="0">
-        <v>-0.2342672635837228</v>
+        <v>-0.050072576512029135</v>
       </c>
       <c r="AO17" s="0">
-        <v>-0.22904368626774246</v>
+        <v>-0.048363932190138147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>337</v>
+        <v>497</v>
       </c>
       <c r="B18" s="0">
-        <v>-0.4217993916666668</v>
+        <v>-0.13180919163398755</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.00038800602777788826</v>
+        <v>0.029175073915595762</v>
       </c>
       <c r="D18" s="0">
-        <v>0.001584937964583311</v>
+        <v>0.029808307076928223</v>
       </c>
       <c r="E18" s="0">
-        <v>-0.0025038902940972552</v>
+        <v>0.031483657772088655</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.00013345134270842385</v>
+        <v>0.04668465531006185</v>
       </c>
       <c r="G18" s="0">
-        <v>0.0076631940197915971</v>
+        <v>0.03017800556290649</v>
       </c>
       <c r="H18" s="0">
-        <v>0.0047647064777776582</v>
+        <v>0.029183513786690454</v>
       </c>
       <c r="I18" s="0">
-        <v>0.0005423724506944394</v>
+        <v>0.026893022625965633</v>
       </c>
       <c r="J18" s="0">
-        <v>-0.01841208667187505</v>
+        <v>0.018055322990375568</v>
       </c>
       <c r="K18" s="0">
-        <v>0.016457395785763884</v>
+        <v>0.036762046744613808</v>
       </c>
       <c r="L18" s="0">
-        <v>0.0076983245763888042</v>
+        <v>0.025864334835758437</v>
       </c>
       <c r="M18" s="0">
-        <v>0.006171607600694351</v>
+        <v>0.024559220703505181</v>
       </c>
       <c r="N18" s="0">
-        <v>0.0093101947715277245</v>
+        <v>0.025426599405734333</v>
       </c>
       <c r="O18" s="0">
-        <v>0.0091337804739582973</v>
+        <v>0.025030026282699736</v>
       </c>
       <c r="P18" s="0">
-        <v>0.0080699755934027784</v>
+        <v>0.024231499644914729</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.0070876446093749434</v>
+        <v>0.024041917854109942</v>
       </c>
       <c r="R18" s="0">
-        <v>0.0069916013677083222</v>
+        <v>0.024767112322113673</v>
       </c>
       <c r="S18" s="0">
-        <v>0.0078296779350693901</v>
+        <v>0.024984759109343415</v>
       </c>
       <c r="T18" s="0">
-        <v>0.012673183568402746</v>
+        <v>0.027152208740770678</v>
       </c>
       <c r="U18" s="0">
-        <v>0.0090222118475693502</v>
+        <v>0.025871072574240095</v>
       </c>
       <c r="V18" s="0">
-        <v>0.0091691154499998762</v>
+        <v>0.025468027891558703</v>
       </c>
       <c r="W18" s="0">
-        <v>0.01124507486458326</v>
+        <v>0.026869383091655985</v>
       </c>
       <c r="X18" s="0">
-        <v>0.010781919059374923</v>
+        <v>0.02608311722398635</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.011356600768055614</v>
+        <v>0.026058621923474353</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.011163509114236081</v>
+        <v>0.025824753446109055</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.01104261085347219</v>
+        <v>0.025465972752470624</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.011057077729861031</v>
+        <v>0.025395796098652466</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.011097694327777741</v>
+        <v>0.025396764145247056</v>
       </c>
       <c r="AD18" s="0">
-        <v>0.011170974005555445</v>
+        <v>0.02544404192199003</v>
       </c>
       <c r="AE18" s="0">
-        <v>0.011174645488194357</v>
+        <v>0.025234896417233098</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.011108785589583281</v>
+        <v>0.0247888644487004</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.011075117525347178</v>
+        <v>0.024492212115562122</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.011105132902083314</v>
+        <v>0.024448904524587353</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.011143589201736026</v>
+        <v>0.024447199890543048</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.011174609382638812</v>
+        <v>0.024429502787863527</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.011185120936111015</v>
+        <v>0.024351710837953885</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.011166977427430502</v>
+        <v>0.024187073884576273</v>
       </c>
       <c r="AM18" s="0">
-        <v>0.011134836386111013</v>
+        <v>0.023987793956849961</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.011116453798263815</v>
+        <v>0.023844926519495505</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.011122784832638788</v>
+        <v>0.023792065186640107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>338</v>
+        <v>498</v>
       </c>
       <c r="B19" s="0">
-        <v>-0.42497280166666679</v>
+        <v>-0.13319954382713328</v>
       </c>
       <c r="C19" s="0">
-        <v>0.0010369078552083244</v>
+        <v>0.030219834300164859</v>
       </c>
       <c r="D19" s="0">
-        <v>0.0010437049055554985</v>
+        <v>0.03041387868881322</v>
       </c>
       <c r="E19" s="0">
-        <v>-0.00073040200763890926</v>
+        <v>0.03087177698872428</v>
       </c>
       <c r="F19" s="0">
-        <v>0.00058703429930545472</v>
+        <v>0.038182306906281313</v>
       </c>
       <c r="G19" s="0">
-        <v>0.0056780529211805097</v>
+        <v>0.030034223470145675</v>
       </c>
       <c r="H19" s="0">
-        <v>0.0034646966395833201</v>
+        <v>0.029174506211094041</v>
       </c>
       <c r="I19" s="0">
-        <v>-0.00029839255173613657</v>
+        <v>0.027457994491335583</v>
       </c>
       <c r="J19" s="0">
-        <v>-0.015840694646527875</v>
+        <v>0.020628783703033626</v>
       </c>
       <c r="K19" s="0">
-        <v>0.018953452050347153</v>
+        <v>0.037807411815565337</v>
       </c>
       <c r="L19" s="0">
-        <v>0.0092562241909721066</v>
+        <v>0.027188454034025748</v>
       </c>
       <c r="M19" s="0">
-        <v>0.0055365574239581985</v>
+        <v>0.02432649275892634</v>
       </c>
       <c r="N19" s="0">
-        <v>0.0082555069704860484</v>
+        <v>0.025888610716903186</v>
       </c>
       <c r="O19" s="0">
-        <v>0.008564418338888824</v>
+        <v>0.025831307879421391</v>
       </c>
       <c r="P19" s="0">
-        <v>0.0070743744638888661</v>
+        <v>0.025102364155247969</v>
       </c>
       <c r="Q19" s="0">
-        <v>0.0049928911590277347</v>
+        <v>0.02377506099019382</v>
       </c>
       <c r="R19" s="0">
-        <v>0.0048602783166665784</v>
+        <v>0.023811742666486099</v>
       </c>
       <c r="S19" s="0">
-        <v>0.0055342771774304919</v>
+        <v>0.024879182828060599</v>
       </c>
       <c r="T19" s="0">
-        <v>0.01002481172256936</v>
+        <v>0.026642609214487228</v>
       </c>
       <c r="U19" s="0">
-        <v>0.0071087335357638004</v>
+        <v>0.025534946522023212</v>
       </c>
       <c r="V19" s="0">
-        <v>0.007876671920486078</v>
+        <v>0.025647720130139936</v>
       </c>
       <c r="W19" s="0">
-        <v>0.010002772263194404</v>
+        <v>0.027400652389153186</v>
       </c>
       <c r="X19" s="0">
-        <v>0.010526010825347154</v>
+        <v>0.026839541998812291</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.011217315767013736</v>
+        <v>0.026610035838412583</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.010970398336458187</v>
+        <v>0.026291967022638186</v>
       </c>
       <c r="AA19" s="0">
-        <v>0.010914956693749922</v>
+        <v>0.026060333933323701</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.010859537818055431</v>
+        <v>0.025618908612249858</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.010909248660069426</v>
+        <v>0.025562732981433967</v>
       </c>
       <c r="AD19" s="0">
-        <v>0.01098203054062491</v>
+        <v>0.025569830405865336</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.011060209115624886</v>
+        <v>0.025612454984814681</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.011072679143402708</v>
+        <v>0.025400127118142685</v>
       </c>
       <c r="AG19" s="0">
-        <v>0.011018753018055494</v>
+        <v>0.024952155538729297</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.01099421908923609</v>
+        <v>0.024653194527403985</v>
       </c>
       <c r="AI19" s="0">
-        <v>0.011029092884027647</v>
+        <v>0.024606742989699032</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.01107122862048604</v>
+        <v>0.02460174994354946</v>
       </c>
       <c r="AK19" s="0">
-        <v>0.011106009176041542</v>
+        <v>0.02458112593050308</v>
       </c>
       <c r="AL19" s="0">
-        <v>0.01112085635312493</v>
+        <v>0.024500773643030351</v>
       </c>
       <c r="AM19" s="0">
-        <v>0.011107333555902765</v>
+        <v>0.024333928425249826</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.011079950613541611</v>
+        <v>0.024132656540793173</v>
       </c>
       <c r="AO19" s="0">
-        <v>0.011065583190277728</v>
+        <v>0.023987841941668555</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>339</v>
+        <v>499</v>
       </c>
       <c r="B20" s="0">
-        <v>-0.43338114566666674</v>
+        <v>-0.13688345467417917</v>
       </c>
       <c r="C20" s="0">
-        <v>-0.00022962808159726622</v>
+        <v>0.0309771873727324</v>
       </c>
       <c r="D20" s="0">
-        <v>0.00074189412013880808</v>
+        <v>0.03159890258572752</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.0013581909208333917</v>
+        <v>0.030580244138761807</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0014278414548610234</v>
+        <v>0.034550665001526357</v>
       </c>
       <c r="G20" s="0">
-        <v>0.0028000989322916059</v>
+        <v>0.030084991992929827</v>
       </c>
       <c r="H20" s="0">
-        <v>0.0013066506666666311</v>
+        <v>0.029717692868678605</v>
       </c>
       <c r="I20" s="0">
-        <v>-0.0012580099402778608</v>
+        <v>0.028157353741693571</v>
       </c>
       <c r="J20" s="0">
-        <v>-0.010389718157291727</v>
+        <v>0.024548528965283343</v>
       </c>
       <c r="K20" s="0">
-        <v>0.01491088036180549</v>
+        <v>0.037269400063485773</v>
       </c>
       <c r="L20" s="0">
-        <v>0.0075837578666665961</v>
+        <v>0.028717751030244872</v>
       </c>
       <c r="M20" s="0">
-        <v>0.0047090358781249342</v>
+        <v>0.025857386757479981</v>
       </c>
       <c r="N20" s="0">
-        <v>0.0066451033934027404</v>
+        <v>0.02588798138758967</v>
       </c>
       <c r="O20" s="0">
-        <v>0.006823220734375024</v>
+        <v>0.026553047867194465</v>
       </c>
       <c r="P20" s="0">
-        <v>0.0055871011749998867</v>
+        <v>0.026163106382875584</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.0038794440736110158</v>
+        <v>0.025187328827265352</v>
       </c>
       <c r="R20" s="0">
-        <v>0.0042750544302082036</v>
+        <v>0.024847912854996632</v>
       </c>
       <c r="S20" s="0">
-        <v>0.004147188919097212</v>
+        <v>0.024655986675981741</v>
       </c>
       <c r="T20" s="0">
-        <v>0.0079381587420137567</v>
+        <v>0.027048234907728029</v>
       </c>
       <c r="U20" s="0">
-        <v>0.005612180948958212</v>
+        <v>0.025786132560951771</v>
       </c>
       <c r="V20" s="0">
-        <v>0.0060091750142360345</v>
+        <v>0.025905704120906831</v>
       </c>
       <c r="W20" s="0">
-        <v>0.0077235807038193993</v>
+        <v>0.028061365228953021</v>
       </c>
       <c r="X20" s="0">
-        <v>0.0079112106690972239</v>
+        <v>0.027268569329539295</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.0079480945399305059</v>
+        <v>0.026448263875282717</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.0074985513166666573</v>
+        <v>0.025737487838706642</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.0076424275357638294</v>
+        <v>0.02556131384313598</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.0077525286618055356</v>
+        <v>0.025242374582716377</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.007773042706597233</v>
+        <v>0.02479150516027212</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.0078500509069443503</v>
+        <v>0.024714390694267431</v>
       </c>
       <c r="AE20" s="0">
-        <v>0.0079314522618054717</v>
+        <v>0.024695918306715952</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.0080173054486110673</v>
+        <v>0.024715188034600662</v>
       </c>
       <c r="AG20" s="0">
-        <v>0.0080438614010416298</v>
+        <v>0.024481442093684962</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.0080096971090277691</v>
+        <v>0.024014422044760134</v>
       </c>
       <c r="AI20" s="0">
-        <v>0.0079995503635416076</v>
+        <v>0.023698000899197848</v>
       </c>
       <c r="AJ20" s="0">
-        <v>0.0080418765208332688</v>
+        <v>0.023635297463765005</v>
       </c>
       <c r="AK20" s="0">
-        <v>0.0080900313465277485</v>
+        <v>0.023615356113950353</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.0081310018600694312</v>
+        <v>0.023581104463843212</v>
       </c>
       <c r="AM20" s="0">
-        <v>0.0081524742031249819</v>
+        <v>0.023488230445159051</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.0081467110833332024</v>
+        <v>0.023310054346325472</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.0081269706229166183</v>
+        <v>0.023098471051050482</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="B21" s="0">
-        <v>-0.44584285066666679</v>
+        <v>-0.14234324678332527</v>
       </c>
       <c r="C21" s="0">
-        <v>-0.0016929006274306602</v>
+        <v>0.031849256613476311</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.00053203257951395244</v>
+        <v>0.033061786838209872</v>
       </c>
       <c r="E21" s="0">
-        <v>0.0026656970340276924</v>
+        <v>0.03357599905071007</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0036386730857638221</v>
+        <v>0.035345383889328376</v>
       </c>
       <c r="G21" s="0">
-        <v>0.00078040116562494389</v>
+        <v>0.031385426342490849</v>
       </c>
       <c r="H21" s="0">
-        <v>-7.3522930902847339e-05</v>
+        <v>0.031248334348529541</v>
       </c>
       <c r="I21" s="0">
-        <v>-0.001623173168402825</v>
+        <v>0.030164171006044863</v>
       </c>
       <c r="J21" s="0">
-        <v>-0.0064604493565972865</v>
+        <v>0.028133024805091195</v>
       </c>
       <c r="K21" s="0">
-        <v>0.0079332359864582869</v>
+        <v>0.035744732537941526</v>
       </c>
       <c r="L21" s="0">
-        <v>0.0051184563190971857</v>
+        <v>0.030028452567364475</v>
       </c>
       <c r="M21" s="0">
-        <v>0.0031430747552083638</v>
+        <v>0.028624046765372679</v>
       </c>
       <c r="N21" s="0">
-        <v>0.0054544612791666012</v>
+        <v>0.027930158735556893</v>
       </c>
       <c r="O21" s="0">
-        <v>0.0049722206628471368</v>
+        <v>0.02700489295694623</v>
       </c>
       <c r="P21" s="0">
-        <v>0.0036900277295138224</v>
+        <v>0.027536878279913878</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.0023180118624999135</v>
+        <v>0.026658283129231731</v>
       </c>
       <c r="R21" s="0">
-        <v>0.0026852815420138616</v>
+        <v>0.0266140064060034</v>
       </c>
       <c r="S21" s="0">
-        <v>0.0030124517874999808</v>
+        <v>0.025847574592018373</v>
       </c>
       <c r="T21" s="0">
-        <v>0.0059776949951387826</v>
+        <v>0.026830431114082426</v>
       </c>
       <c r="U21" s="0">
-        <v>0.0037938018111111078</v>
+        <v>0.026379074507723348</v>
       </c>
       <c r="V21" s="0">
-        <v>0.0045885823934027061</v>
+        <v>0.026491693325072892</v>
       </c>
       <c r="W21" s="0">
-        <v>0.0056536759885416621</v>
+        <v>0.028939673599928269</v>
       </c>
       <c r="X21" s="0">
-        <v>0.0055512564687499877</v>
+        <v>0.028325366878732116</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.0055838595124999002</v>
+        <v>0.027381645431500304</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.0049705135118055521</v>
+        <v>0.026291098933103517</v>
       </c>
       <c r="AA21" s="0">
-        <v>0.0051784002684027728</v>
+        <v>0.025874711286077247</v>
       </c>
       <c r="AB21" s="0">
-        <v>0.0053520884295138451</v>
+        <v>0.025574158192530973</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.0054651517434027297</v>
+        <v>0.025214037698882912</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.0055358966809027086</v>
+        <v>0.024699904269313282</v>
       </c>
       <c r="AE21" s="0">
-        <v>0.0056329763586804305</v>
+        <v>0.024565147411312667</v>
       </c>
       <c r="AF21" s="0">
-        <v>0.0057290057520832383</v>
+        <v>0.024493203955550977</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.0058280040406249456</v>
+        <v>0.024463693868114159</v>
       </c>
       <c r="AH21" s="0">
-        <v>0.0058795048920138315</v>
+        <v>0.024184144215490918</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.0058803021878471862</v>
+        <v>0.023675235699143572</v>
       </c>
       <c r="AJ21" s="0">
-        <v>0.0058964952152776862</v>
+        <v>0.023321418376710305</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.0059518084913193769</v>
+        <v>0.023224527262115369</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.0060107199128471289</v>
+        <v>0.023173349342426045</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.0060623046819444082</v>
+        <v>0.023110350361963464</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.0060957073156249764</v>
+        <v>0.022991107221329545</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.0061033976059027828</v>
+        <v>0.022788686087050852</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>341</v>
+        <v>501</v>
       </c>
       <c r="B22" s="0">
-        <v>-0.4504280076666668</v>
+        <v>-0.14435212149250803</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.0013175390503472606</v>
+        <v>0.034887473148824587</v>
       </c>
       <c r="D22" s="0">
-        <v>-0.0016098284611111846</v>
+        <v>0.035416509304760528</v>
       </c>
       <c r="E22" s="0">
-        <v>-0.00049082650173620703</v>
+        <v>0.035223204395472586</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.0016924214045139227</v>
+        <v>0.035267467833033625</v>
       </c>
       <c r="G22" s="0">
-        <v>-0.001451706351388915</v>
+        <v>0.033733654965963956</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.0015843413118056251</v>
+        <v>0.033704342901700199</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.0027060017048611273</v>
+        <v>0.032736797698583855</v>
       </c>
       <c r="J22" s="0">
-        <v>-0.0062629608541667214</v>
+        <v>0.031107429864099458</v>
       </c>
       <c r="K22" s="0">
-        <v>0.0041634312350694036</v>
+        <v>0.0363945639168178</v>
       </c>
       <c r="L22" s="0">
-        <v>0.0019953471888888297</v>
+        <v>0.0313212512053846</v>
       </c>
       <c r="M22" s="0">
-        <v>0.00090687783854159765</v>
+        <v>0.031017354374989644</v>
       </c>
       <c r="N22" s="0">
-        <v>0.0031208449579859239</v>
+        <v>0.031014578765733325</v>
       </c>
       <c r="O22" s="0">
-        <v>0.0036512442298610721</v>
+        <v>0.029711237358803707</v>
       </c>
       <c r="P22" s="0">
-        <v>0.0026787347069443528</v>
+        <v>0.028799075799616887</v>
       </c>
       <c r="Q22" s="0">
-        <v>0.0010888800055555144</v>
+        <v>0.028796915963976089</v>
       </c>
       <c r="R22" s="0">
-        <v>0.0011307896406250184</v>
+        <v>0.028473166139476296</v>
       </c>
       <c r="S22" s="0">
-        <v>0.0015391748357638235</v>
+        <v>0.027981098369584307</v>
       </c>
       <c r="T22" s="0">
-        <v>0.0048251917461805682</v>
+        <v>0.02825101979352989</v>
       </c>
       <c r="U22" s="0">
-        <v>0.0034643731940971483</v>
+        <v>0.026883589369893421</v>
       </c>
       <c r="V22" s="0">
-        <v>0.0038385266579860082</v>
+        <v>0.027744270989120939</v>
       </c>
       <c r="W22" s="0">
-        <v>0.0043092446899304915</v>
+        <v>0.029855010074807592</v>
       </c>
       <c r="X22" s="0">
-        <v>0.0039654373899304365</v>
+        <v>0.029470682871491124</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.0039727855937499168</v>
+        <v>0.028900617747231169</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.003167942596180473</v>
+        <v>0.027596652260910737</v>
       </c>
       <c r="AA22" s="0">
-        <v>0.0035754061770832402</v>
+        <v>0.026976732091439991</v>
       </c>
       <c r="AB22" s="0">
-        <v>0.0038600981211804331</v>
+        <v>0.026373807281161125</v>
       </c>
       <c r="AC22" s="0">
-        <v>0.0040295925909721864</v>
+        <v>0.026038085372129021</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.0041908318934026911</v>
+        <v>0.025610669418672741</v>
       </c>
       <c r="AE22" s="0">
-        <v>0.0043369694836804537</v>
+        <v>0.025042508544069961</v>
       </c>
       <c r="AF22" s="0">
-        <v>0.0044651892298611107</v>
+        <v>0.024853055277269293</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.0045848976357637525</v>
+        <v>0.024729719925690025</v>
       </c>
       <c r="AH22" s="0">
-        <v>0.0047048299239582656</v>
+        <v>0.024653095575650513</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.0047983609885415826</v>
+        <v>0.024333664979788495</v>
       </c>
       <c r="AJ22" s="0">
-        <v>0.0048567282496527189</v>
+        <v>0.023791382871594768</v>
       </c>
       <c r="AK22" s="0">
-        <v>0.0049149661423610871</v>
+        <v>0.023405832229651705</v>
       </c>
       <c r="AL22" s="0">
-        <v>0.0049916453593749077</v>
+        <v>0.023277193624352863</v>
       </c>
       <c r="AM22" s="0">
-        <v>0.0050678060135415648</v>
+        <v>0.023196416730579886</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.0051367865277777156</v>
+        <v>0.023106646921021483</v>
       </c>
       <c r="AO22" s="0">
-        <v>0.0051896597600693539</v>
+        <v>0.022963426444302243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>342</v>
+        <v>502</v>
       </c>
       <c r="B23" s="0">
-        <v>-0.46112387766666674</v>
+        <v>-0.149038256064499</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.003886332039583329</v>
+        <v>0.039711273916062925</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.0030797290847222594</v>
+        <v>0.04059833799230441</v>
       </c>
       <c r="E23" s="0">
-        <v>-0.0030192821527778579</v>
+        <v>0.039550238415279333</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.0018714807243055973</v>
+        <v>0.04057968806128974</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.0028943771069445123</v>
+        <v>0.038450089961774431</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.0033876407812500342</v>
+        <v>0.038733818855243393</v>
       </c>
       <c r="I23" s="0">
-        <v>-0.0040269042048611814</v>
+        <v>0.03772184662160058</v>
       </c>
       <c r="J23" s="0">
-        <v>-0.0068115672350695378</v>
+        <v>0.036416470629528248</v>
       </c>
       <c r="K23" s="0">
-        <v>0.0021132323618054949</v>
+        <v>0.041001494290079037</v>
       </c>
       <c r="L23" s="0">
-        <v>0.00083835553090266801</v>
+        <v>0.035251298753127422</v>
       </c>
       <c r="M23" s="0">
-        <v>-0.00090980805972229462</v>
+        <v>0.03478638267719672</v>
       </c>
       <c r="N23" s="0">
-        <v>0.0004129450465276685</v>
+        <v>0.034868885721015312</v>
       </c>
       <c r="O23" s="0">
-        <v>0.00080050194201386482</v>
+        <v>0.034369755817296566</v>
       </c>
       <c r="P23" s="0">
-        <v>0.0007369422468749276</v>
+        <v>0.033054478976621199</v>
       </c>
       <c r="Q23" s="0">
-        <v>0.00076228644062498142</v>
+        <v>0.031599019816536546</v>
       </c>
       <c r="R23" s="0">
-        <v>3.2487967708271469e-05</v>
+        <v>0.031810258714197008</v>
       </c>
       <c r="S23" s="0">
-        <v>0.0004896178350693994</v>
+        <v>0.03109703513711079</v>
       </c>
       <c r="T23" s="0">
-        <v>0.0032727660305555402</v>
+        <v>0.031287086094557617</v>
       </c>
       <c r="U23" s="0">
-        <v>0.0023907547420138342</v>
+        <v>0.028912825828062923</v>
       </c>
       <c r="V23" s="0">
-        <v>0.0032523477034721586</v>
+        <v>0.028906012542813251</v>
       </c>
       <c r="W23" s="0">
-        <v>0.0035106707927083365</v>
+        <v>0.031385007968548227</v>
       </c>
       <c r="X23" s="0">
-        <v>0.0025122120260416265</v>
+        <v>0.030384777471479101</v>
       </c>
       <c r="Y23" s="0">
-        <v>0.0027559330055554883</v>
+        <v>0.030288492762665226</v>
       </c>
       <c r="Z23" s="0">
-        <v>0.0020976397177082107</v>
+        <v>0.029566968206794043</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.0026050920892360385</v>
+        <v>0.028974228810193191</v>
       </c>
       <c r="AB23" s="0">
-        <v>0.0030290575847222168</v>
+        <v>0.028078931221948985</v>
       </c>
       <c r="AC23" s="0">
-        <v>0.0033883091184027099</v>
+        <v>0.027452992777937779</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.0036142810135416092</v>
+        <v>0.027038851591859005</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.0038484452260415525</v>
+        <v>0.026543172461096439</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.0040846464479165623</v>
+        <v>0.025916191802524316</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.0042487198111110245</v>
+        <v>0.025664643219102074</v>
       </c>
       <c r="AH23" s="0">
-        <v>0.0043964448722221272</v>
+        <v>0.025483073639831062</v>
       </c>
       <c r="AI23" s="0">
-        <v>0.0045417734322916173</v>
+        <v>0.025353177001245678</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.0046861001951388195</v>
+        <v>0.024989490267896972</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.0048139654413193456</v>
+        <v>0.024410911028497722</v>
       </c>
       <c r="AL23" s="0">
-        <v>0.0049229780611110274</v>
+        <v>0.023990198728516182</v>
       </c>
       <c r="AM23" s="0">
-        <v>0.0050253357798610279</v>
+        <v>0.02382554941444005</v>
       </c>
       <c r="AN23" s="0">
-        <v>0.0051223495899305185</v>
+        <v>0.023711148548781948</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.0052125860840276927</v>
+        <v>0.023591002216054771</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>343</v>
+        <v>503</v>
       </c>
       <c r="B24" s="0">
-        <v>-0.47160093866666675</v>
+        <v>-0.15362852480981454</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.005117257937152897</v>
+        <v>0.047472488091334364</v>
       </c>
       <c r="D24" s="0">
-        <v>-0.005508937337500075</v>
+        <v>0.048401417813244127</v>
       </c>
       <c r="E24" s="0">
-        <v>-0.001523492978819486</v>
+        <v>0.048050732762561221</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.0021217072690972736</v>
+        <v>0.048483929640721089</v>
       </c>
       <c r="G24" s="0">
-        <v>-0.0051058421104167029</v>
+        <v>0.045116563106180729</v>
       </c>
       <c r="H24" s="0">
-        <v>-0.0050166100937500402</v>
+        <v>0.045547979834380664</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.0064291369590279146</v>
+        <v>0.04410367363642937</v>
       </c>
       <c r="J24" s="0">
-        <v>-0.0085663428923611895</v>
+        <v>0.042938619007640712</v>
       </c>
       <c r="K24" s="0">
-        <v>-0.00061558860243060565</v>
+        <v>0.047717829248015653</v>
       </c>
       <c r="L24" s="0">
-        <v>-0.0013603017368056256</v>
+        <v>0.040917522297043644</v>
       </c>
       <c r="M24" s="0">
-        <v>-0.0022994787444444711</v>
+        <v>0.039929893414434411</v>
       </c>
       <c r="N24" s="0">
-        <v>-0.0019507703725694658</v>
+        <v>0.039629930485494472</v>
       </c>
       <c r="O24" s="0">
-        <v>-0.0023454098805556481</v>
+        <v>0.039162701388749256</v>
       </c>
       <c r="P24" s="0">
-        <v>-0.0027418261333334573</v>
+        <v>0.038794887724288261</v>
       </c>
       <c r="Q24" s="0">
-        <v>-0.001066627794097331</v>
+        <v>0.036764508021758235</v>
       </c>
       <c r="R24" s="0">
-        <v>-0.00026249539652783982</v>
+        <v>0.035365108383657529</v>
       </c>
       <c r="S24" s="0">
-        <v>-0.001655569434375114</v>
+        <v>0.034596353318300542</v>
       </c>
       <c r="T24" s="0">
-        <v>0.00073159652083321135</v>
+        <v>0.034192068037134454</v>
       </c>
       <c r="U24" s="0">
-        <v>0.0001958482822915766</v>
+        <v>0.031956156004780141</v>
       </c>
       <c r="V24" s="0">
-        <v>0.0016969575204860421</v>
+        <v>0.031208995865299873</v>
       </c>
       <c r="W24" s="0">
-        <v>0.0019758782951387888</v>
+        <v>0.032197327657004872</v>
       </c>
       <c r="X24" s="0">
-        <v>-7.497210520840316e-05</v>
+        <v>0.031641099565548614</v>
       </c>
       <c r="Y24" s="0">
-        <v>0.00077233001527771171</v>
+        <v>0.031410531946225916</v>
       </c>
       <c r="Z24" s="0">
-        <v>0.00050954129374991552</v>
+        <v>0.031345904517283155</v>
       </c>
       <c r="AA24" s="0">
-        <v>0.0010753632902777417</v>
+        <v>0.031179904892329299</v>
       </c>
       <c r="AB24" s="0">
-        <v>0.0016047557034721831</v>
+        <v>0.030245369093930739</v>
       </c>
       <c r="AC24" s="0">
-        <v>0.0021438198447916164</v>
+        <v>0.029365821786885703</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.0026355339218748779</v>
+        <v>0.028657937882128282</v>
       </c>
       <c r="AE24" s="0">
-        <v>0.002938187574305529</v>
+        <v>0.028156233943441765</v>
       </c>
       <c r="AF24" s="0">
-        <v>0.0032689231975693849</v>
+        <v>0.027585187742545356</v>
       </c>
       <c r="AG24" s="0">
-        <v>0.0036266548263888532</v>
+        <v>0.026896028380590676</v>
       </c>
       <c r="AH24" s="0">
-        <v>0.0038394893041665545</v>
+        <v>0.026573530281878227</v>
       </c>
       <c r="AI24" s="0">
-        <v>0.0040244060826388215</v>
+        <v>0.026324368291994246</v>
       </c>
       <c r="AJ24" s="0">
-        <v>0.0042034369267360261</v>
+        <v>0.026132484423411952</v>
       </c>
       <c r="AK24" s="0">
-        <v>0.0044167011059026975</v>
+        <v>0.025720030292130793</v>
       </c>
       <c r="AL24" s="0">
-        <v>0.0046400129656248845</v>
+        <v>0.0251042632742061</v>
       </c>
       <c r="AM24" s="0">
-        <v>0.0048192102906249312</v>
+        <v>0.024646119755515516</v>
       </c>
       <c r="AN24" s="0">
-        <v>0.0049568578302082713</v>
+        <v>0.024440372072273665</v>
       </c>
       <c r="AO24" s="0">
-        <v>0.0050828599215276826</v>
+        <v>0.02428746366058801</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>344</v>
+        <v>504</v>
       </c>
       <c r="B25" s="0">
-        <v>-0.48655493566666674</v>
+        <v>-0.16018025387263496</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.0081075655635417521</v>
+        <v>0.058052334983969278</v>
       </c>
       <c r="D25" s="0">
-        <v>-0.0079113979746528451</v>
+        <v>0.059026718143675543</v>
       </c>
       <c r="E25" s="0">
-        <v>-0.007660462713194538</v>
+        <v>0.057646746001998851</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.00868934077986111</v>
+        <v>0.058055711909110151</v>
       </c>
       <c r="G25" s="0">
-        <v>-0.0082185092909722313</v>
+        <v>0.054834418723098695</v>
       </c>
       <c r="H25" s="0">
-        <v>-0.0081056604725694981</v>
+        <v>0.055636764490767321</v>
       </c>
       <c r="I25" s="0">
-        <v>-0.0085869279527778786</v>
+        <v>0.053782521232761817</v>
       </c>
       <c r="J25" s="0">
-        <v>-0.010724527568402809</v>
+        <v>0.052905546744431611</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.0046432437107639668</v>
+        <v>0.057601938842459816</v>
       </c>
       <c r="L25" s="0">
-        <v>-0.0045009423927084291</v>
+        <v>0.04994454331014548</v>
       </c>
       <c r="M25" s="0">
-        <v>-0.0049612200767361614</v>
+        <v>0.048423065249687917</v>
       </c>
       <c r="N25" s="0">
-        <v>-0.0039487889006944998</v>
+        <v>0.047145234466217198</v>
       </c>
       <c r="O25" s="0">
-        <v>-0.0052291500319445183</v>
+        <v>0.04604546945244125</v>
       </c>
       <c r="P25" s="0">
-        <v>-0.0063071547961806029</v>
+        <v>0.046041162391693598</v>
       </c>
       <c r="Q25" s="0">
-        <v>-0.0052616203486112179</v>
+        <v>0.044427983787237571</v>
       </c>
       <c r="R25" s="0">
-        <v>-0.0031120558069445128</v>
+        <v>0.041872793937439305</v>
       </c>
       <c r="S25" s="0">
-        <v>-0.0017704263652778543</v>
+        <v>0.039738154394568334</v>
       </c>
       <c r="T25" s="0">
-        <v>-0.0017819424868056322</v>
+        <v>0.03904848003505617</v>
       </c>
       <c r="U25" s="0">
-        <v>-0.0027945545631944957</v>
+        <v>0.035730790646410486</v>
       </c>
       <c r="V25" s="0">
-        <v>-0.0010067563979167526</v>
+        <v>0.035452671959002355</v>
       </c>
       <c r="W25" s="0">
-        <v>0.00023841460416662574</v>
+        <v>0.035014158244247633</v>
       </c>
       <c r="X25" s="0">
-        <v>-0.0010757396680556308</v>
+        <v>0.032930176999015938</v>
       </c>
       <c r="Y25" s="0">
-        <v>-0.0015806695628473024</v>
+        <v>0.033090304408420437</v>
       </c>
       <c r="Z25" s="0">
-        <v>-0.0018851712489583172</v>
+        <v>0.032619539547223984</v>
       </c>
       <c r="AA25" s="0">
-        <v>-0.0013068391388890164</v>
+        <v>0.033033240046375686</v>
       </c>
       <c r="AB25" s="0">
-        <v>-0.00083232240034725267</v>
+        <v>0.03233115167877422</v>
       </c>
       <c r="AC25" s="0">
-        <v>-0.00023052584618066252</v>
+        <v>0.031492408094691275</v>
       </c>
       <c r="AD25" s="0">
-        <v>0.00049170704826384613</v>
+        <v>0.030526323925375416</v>
       </c>
       <c r="AE25" s="0">
-        <v>0.0011351725055554489</v>
+        <v>0.029737172043153699</v>
       </c>
       <c r="AF25" s="0">
-        <v>0.0015199736555554515</v>
+        <v>0.0291421113171722</v>
       </c>
       <c r="AG25" s="0">
-        <v>0.0019567109621527194</v>
+        <v>0.02849149530994519</v>
       </c>
       <c r="AH25" s="0">
-        <v>0.0024499553503471438</v>
+        <v>0.027737625906930512</v>
       </c>
       <c r="AI25" s="0">
-        <v>0.0027144668934027676</v>
+        <v>0.027337544877856324</v>
       </c>
       <c r="AJ25" s="0">
-        <v>0.0029402861538194163</v>
+        <v>0.027014681654147867</v>
       </c>
       <c r="AK25" s="0">
-        <v>0.0031563877999999379</v>
+        <v>0.026754967805989655</v>
       </c>
       <c r="AL25" s="0">
-        <v>0.0034491337152777746</v>
+        <v>0.026290629619933933</v>
       </c>
       <c r="AM25" s="0">
-        <v>0.003783151068402768</v>
+        <v>0.025636292898499689</v>
       </c>
       <c r="AN25" s="0">
-        <v>0.0040429179815971716</v>
+        <v>0.025137782992584248</v>
       </c>
       <c r="AO25" s="0">
-        <v>0.0042211655624999067</v>
+        <v>0.024886748948003259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>345</v>
+        <v>505</v>
       </c>
       <c r="B26" s="0">
-        <v>-0.50183650866666674</v>
+        <v>-0.16687550237039195</v>
       </c>
       <c r="C26" s="0">
-        <v>-0.010513222674652767</v>
+        <v>0.073294642872468688</v>
       </c>
       <c r="D26" s="0">
-        <v>-0.010754909527777745</v>
+        <v>0.074166063288269926</v>
       </c>
       <c r="E26" s="0">
-        <v>-0.0097036309208333726</v>
+        <v>0.072447933973772916</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.009148143000694553</v>
+        <v>0.073706081090952932</v>
       </c>
       <c r="G26" s="0">
-        <v>-0.010116900013541708</v>
+        <v>0.069106671648730508</v>
       </c>
       <c r="H26" s="0">
-        <v>-0.010979937268402906</v>
+        <v>0.069808600493705561</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.011520611781250079</v>
+        <v>0.067158962441705175</v>
       </c>
       <c r="J26" s="0">
-        <v>-0.012880098122916739</v>
+        <v>0.065972920615293335</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.0092402835402778383</v>
+        <v>0.071364556230657739</v>
       </c>
       <c r="L26" s="0">
-        <v>-0.0087600528815972578</v>
+        <v>0.062051685810801373</v>
       </c>
       <c r="M26" s="0">
-        <v>-0.0086766464027778212</v>
+        <v>0.06098410909940595</v>
       </c>
       <c r="N26" s="0">
-        <v>-0.0072881452284723203</v>
+        <v>0.058745731134269577</v>
       </c>
       <c r="O26" s="0">
-        <v>-0.0072889998722222571</v>
+        <v>0.056676704434901116</v>
       </c>
       <c r="P26" s="0">
-        <v>-0.0099411158114583453</v>
+        <v>0.055395175910426232</v>
       </c>
       <c r="Q26" s="0">
-        <v>-0.0093924477524305883</v>
+        <v>0.054123073451053536</v>
       </c>
       <c r="R26" s="0">
-        <v>-0.0081345702395833608</v>
+        <v>0.052025918475513175</v>
       </c>
       <c r="S26" s="0">
-        <v>-0.005320095408680614</v>
+        <v>0.048796145234708474</v>
       </c>
       <c r="T26" s="0">
-        <v>-0.0026864367812500225</v>
+        <v>0.046171591253544302</v>
       </c>
       <c r="U26" s="0">
-        <v>-0.0056217527256945954</v>
+        <v>0.042000968327127436</v>
       </c>
       <c r="V26" s="0">
-        <v>-0.0044979618562500656</v>
+        <v>0.041015225718524534</v>
       </c>
       <c r="W26" s="0">
-        <v>-0.0028940446138890352</v>
+        <v>0.041243706899655154</v>
       </c>
       <c r="X26" s="0">
-        <v>-0.0025380881312500603</v>
+        <v>0.037841784563695607</v>
       </c>
       <c r="Y26" s="0">
-        <v>-0.0025621971819444487</v>
+        <v>0.036218579668907729</v>
       </c>
       <c r="Z26" s="0">
-        <v>-0.0052104018597223245</v>
+        <v>0.035896661782127602</v>
       </c>
       <c r="AA26" s="0">
-        <v>-0.0047031117739584349</v>
+        <v>0.036074657781349634</v>
       </c>
       <c r="AB26" s="0">
-        <v>-0.0041106880100695298</v>
+        <v>0.035555358286413527</v>
       </c>
       <c r="AC26" s="0">
-        <v>-0.0035673538034723395</v>
+        <v>0.035031004175574226</v>
       </c>
       <c r="AD26" s="0">
-        <v>-0.0028049887322917346</v>
+        <v>0.033987128337487911</v>
       </c>
       <c r="AE26" s="0">
-        <v>-0.0018652901402778643</v>
+        <v>0.032832531264481851</v>
       </c>
       <c r="AF26" s="0">
-        <v>-0.0010239942343751038</v>
+        <v>0.031877161977073722</v>
       </c>
       <c r="AG26" s="0">
-        <v>-0.00054577660833343613</v>
+        <v>0.031102429882309782</v>
       </c>
       <c r="AH26" s="0">
-        <v>2.5568946874998666e-05</v>
+        <v>0.030293678946752722</v>
       </c>
       <c r="AI26" s="0">
-        <v>0.00070065029444438265</v>
+        <v>0.029403363483555208</v>
       </c>
       <c r="AJ26" s="0">
-        <v>0.0010343296520832768</v>
+        <v>0.028860329536016121</v>
       </c>
       <c r="AK26" s="0">
-        <v>0.0013107695729165925</v>
+        <v>0.028401006206263756</v>
       </c>
       <c r="AL26" s="0">
-        <v>0.0015728894173610568</v>
+        <v>0.028015272479436946</v>
       </c>
       <c r="AM26" s="0">
-        <v>0.0019708377284720639</v>
+        <v>0.027444172888455638</v>
       </c>
       <c r="AN26" s="0">
-        <v>0.0024581532444443721</v>
+        <v>0.026701576790508497</v>
       </c>
       <c r="AO26" s="0">
-        <v>0.0028320014618055112</v>
+        <v>0.026118150017442558</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>346</v>
+        <v>506</v>
       </c>
       <c r="B27" s="0">
-        <v>-0.51916739266666678</v>
+        <v>-0.17446860650082407</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.011664872419444583</v>
+        <v>0.092555159552896255</v>
       </c>
       <c r="D27" s="0">
-        <v>-0.011672009658680649</v>
+        <v>0.093302680686413841</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.011614740287500092</v>
+        <v>0.09146745292910724</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.01152882767430552</v>
+        <v>0.092895468622746141</v>
       </c>
       <c r="G27" s="0">
-        <v>-0.011884119567708351</v>
+        <v>0.088320483890324653</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.011989874944791701</v>
+        <v>0.090127091301401327</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.012684922148958444</v>
+        <v>0.085874908739182923</v>
       </c>
       <c r="J27" s="0">
-        <v>-0.014583533618750144</v>
+        <v>0.084826617399577808</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.011773261176736105</v>
+        <v>0.092075548512290412</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.012139527500347302</v>
+        <v>0.08094318702821468</v>
       </c>
       <c r="M27" s="0">
-        <v>-0.012235208857639013</v>
+        <v>0.079472695321694972</v>
       </c>
       <c r="N27" s="0">
-        <v>-0.011115026003125084</v>
+        <v>0.076816096323588379</v>
       </c>
       <c r="O27" s="0">
-        <v>-0.010591470204861175</v>
+        <v>0.074462606041181323</v>
       </c>
       <c r="P27" s="0">
-        <v>-0.011927511020833392</v>
+        <v>0.071976068153948414</v>
       </c>
       <c r="Q27" s="0">
-        <v>-0.013313501559722329</v>
+        <v>0.069806980474972136</v>
       </c>
       <c r="R27" s="0">
-        <v>-0.013089013577083419</v>
+        <v>0.067698143906895616</v>
       </c>
       <c r="S27" s="0">
-        <v>-0.01169637650312505</v>
+        <v>0.065123837513695618</v>
       </c>
       <c r="T27" s="0">
-        <v>-0.0068323150520833709</v>
+        <v>0.061227117932173281</v>
       </c>
       <c r="U27" s="0">
-        <v>-0.0062101185572916995</v>
+        <v>0.054242626871331009</v>
       </c>
       <c r="V27" s="0">
-        <v>-0.0089145125434028083</v>
+        <v>0.05253363053791596</v>
       </c>
       <c r="W27" s="0">
-        <v>-0.0074453653864583469</v>
+        <v>0.052654716147340318</v>
       </c>
       <c r="X27" s="0">
-        <v>-0.0068509722972222575</v>
+        <v>0.048729314433948387</v>
       </c>
       <c r="Y27" s="0">
-        <v>-0.0049050355357639908</v>
+        <v>0.045529056377618518</v>
       </c>
       <c r="Z27" s="0">
-        <v>-0.0062946853208334375</v>
+        <v>0.043849416294400416</v>
       </c>
       <c r="AA27" s="0">
-        <v>-0.0090479556600694955</v>
+        <v>0.044248458562545188</v>
       </c>
       <c r="AB27" s="0">
-        <v>-0.0086201537458334143</v>
+        <v>0.042921707751227348</v>
       </c>
       <c r="AC27" s="0">
-        <v>-0.0080637676711806106</v>
+        <v>0.042746728786249667</v>
       </c>
       <c r="AD27" s="0">
-        <v>-0.0074418983354166968</v>
+        <v>0.041900434958518674</v>
       </c>
       <c r="AE27" s="0">
-        <v>-0.0064633271208334175</v>
+        <v>0.040327502653546253</v>
       </c>
       <c r="AF27" s="0">
-        <v>-0.0052005199190973128</v>
+        <v>0.038666606794727186</v>
       </c>
       <c r="AG27" s="0">
-        <v>-0.0040565729965277852</v>
+        <v>0.03726317445956185</v>
       </c>
       <c r="AH27" s="0">
-        <v>-0.0034462996086805919</v>
+        <v>0.036038286966801988</v>
       </c>
       <c r="AI27" s="0">
-        <v>-0.0026669429045140247</v>
+        <v>0.034819354077831148</v>
       </c>
       <c r="AJ27" s="0">
-        <v>-0.00170234626666671</v>
+        <v>0.033556878102090744</v>
       </c>
       <c r="AK27" s="0">
-        <v>-0.0012601227982639287</v>
+        <v>0.0326592040244525</v>
       </c>
       <c r="AL27" s="0">
-        <v>-0.00090618664340280652</v>
+        <v>0.031864670199303183</v>
       </c>
       <c r="AM27" s="0">
-        <v>-0.00057390014270841758</v>
+        <v>0.031169013431780239</v>
       </c>
       <c r="AN27" s="0">
-        <v>-7.1221833333754217e-06</v>
+        <v>0.030317997632603282</v>
       </c>
       <c r="AO27" s="0">
-        <v>0.00073164878402770528</v>
+        <v>0.029328711989957564</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>347</v>
+        <v>507</v>
       </c>
       <c r="B28" s="0">
-        <v>-0.53301759966666673</v>
+        <v>-0.18053673689619454</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.0090284972559027121</v>
+        <v>0.11323185106344581</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.009237775144444571</v>
+        <v>0.11378411847534159</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.0086812845586806686</v>
+        <v>0.11156003848430623</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.0093850933097222589</v>
+        <v>0.11363355971427537</v>
       </c>
       <c r="G28" s="0">
-        <v>-0.010069708306250202</v>
+        <v>0.10859477503679291</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.010600266620486187</v>
+        <v>0.11084496145800106</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.010323775892014053</v>
+        <v>0.1066407714704329</v>
       </c>
       <c r="J28" s="0">
-        <v>-0.012605086473263971</v>
+        <v>0.10505942212244587</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.011820612478125048</v>
+        <v>0.11274615187605505</v>
       </c>
       <c r="L28" s="0">
-        <v>-0.010960663456944464</v>
+        <v>0.10162410518623778</v>
       </c>
       <c r="M28" s="0">
-        <v>-0.013087889567014011</v>
+        <v>0.10076356790341179</v>
       </c>
       <c r="N28" s="0">
-        <v>-0.01249465267395844</v>
+        <v>0.098106780629894808</v>
       </c>
       <c r="O28" s="0">
-        <v>-0.012847498785069411</v>
+        <v>0.095818850827927557</v>
       </c>
       <c r="P28" s="0">
-        <v>-0.013385585935763999</v>
+        <v>0.092900077352466442</v>
       </c>
       <c r="Q28" s="0">
-        <v>-0.013768837003125145</v>
+        <v>0.090419993733363582</v>
       </c>
       <c r="R28" s="0">
-        <v>-0.015504090262500103</v>
+        <v>0.087638688515871088</v>
       </c>
       <c r="S28" s="0">
-        <v>-0.016243898938888945</v>
+        <v>0.085500374327554654</v>
       </c>
       <c r="T28" s="0">
-        <v>-0.014289367375000084</v>
+        <v>0.081833893312001971</v>
       </c>
       <c r="U28" s="0">
-        <v>-0.010827555134027889</v>
+        <v>0.073523326171597819</v>
       </c>
       <c r="V28" s="0">
-        <v>-0.0098874589253472589</v>
+        <v>0.070902514888381826</v>
       </c>
       <c r="W28" s="0">
-        <v>-0.013308334465277849</v>
+        <v>0.070932990601530035</v>
       </c>
       <c r="X28" s="0">
-        <v>-0.013268611578125089</v>
+        <v>0.065849006507690405</v>
       </c>
       <c r="Y28" s="0">
-        <v>-0.011239795984027801</v>
+        <v>0.062760995708639924</v>
       </c>
       <c r="Z28" s="0">
-        <v>-0.009822831701041701</v>
+        <v>0.059945863204743988</v>
       </c>
       <c r="AA28" s="0">
-        <v>-0.011029956322569479</v>
+        <v>0.058547036693473609</v>
       </c>
       <c r="AB28" s="0">
-        <v>-0.015373035491666742</v>
+        <v>0.055789493690418634</v>
       </c>
       <c r="AC28" s="0">
-        <v>-0.014990411317708341</v>
+        <v>0.055069640842144683</v>
       </c>
       <c r="AD28" s="0">
-        <v>-0.014355261232638861</v>
+        <v>0.054797203492236733</v>
       </c>
       <c r="AE28" s="0">
-        <v>-0.013623110477083422</v>
+        <v>0.053594663780907333</v>
       </c>
       <c r="AF28" s="0">
-        <v>-0.012318866155208386</v>
+        <v>0.051485647793147862</v>
       </c>
       <c r="AG28" s="0">
-        <v>-0.010541669198263992</v>
+        <v>0.049281616315618157</v>
       </c>
       <c r="AH28" s="0">
-        <v>-0.0089209674107639803</v>
+        <v>0.0473796614782971</v>
       </c>
       <c r="AI28" s="0">
-        <v>-0.0080957697034723108</v>
+        <v>0.045616888575716066</v>
       </c>
       <c r="AJ28" s="0">
-        <v>-0.0069746484479167314</v>
+        <v>0.043883590011063296</v>
       </c>
       <c r="AK28" s="0">
-        <v>-0.0055320871829862006</v>
+        <v>0.042124616237682981</v>
       </c>
       <c r="AL28" s="0">
-        <v>-0.0049083658670139307</v>
+        <v>0.040745692613574566</v>
       </c>
       <c r="AM28" s="0">
-        <v>-0.0044199066579861945</v>
+        <v>0.039479482319118638</v>
       </c>
       <c r="AN28" s="0">
-        <v>-0.0039619158298611623</v>
+        <v>0.038333779494188029</v>
       </c>
       <c r="AO28" s="0">
-        <v>-0.0031066826611111367</v>
+        <v>0.037043252260771063</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>348</v>
+        <v>508</v>
       </c>
       <c r="B29" s="0">
-        <v>-0.54158771266666672</v>
+        <v>-0.18429152288510142</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.0039109346621529761</v>
+        <v>0.12898082270527375</v>
       </c>
       <c r="D29" s="0">
-        <v>-0.0037979551149306401</v>
+        <v>0.12982282718624003</v>
       </c>
       <c r="E29" s="0">
-        <v>-0.0041612129076388227</v>
+        <v>0.12824077981208545</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.0042096328048610854</v>
+        <v>0.13030234285355866</v>
       </c>
       <c r="G29" s="0">
-        <v>-0.0045308783208334313</v>
+        <v>0.1263506488306006</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.0050193586375000265</v>
+        <v>0.12884467303551767</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.0051834620947917021</v>
+        <v>0.12502505670007794</v>
       </c>
       <c r="J29" s="0">
-        <v>-0.0061431805916668525</v>
+        <v>0.12412499343232598</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.0062758815513889177</v>
+        <v>0.13079558481723835</v>
       </c>
       <c r="L29" s="0">
-        <v>-0.0062789768881944541</v>
+        <v>0.12122842293246551</v>
       </c>
       <c r="M29" s="0">
-        <v>-0.0075527637656251922</v>
+        <v>0.12082785660533665</v>
       </c>
       <c r="N29" s="0">
-        <v>-0.0090959757437500954</v>
+        <v>0.11870496207418528</v>
       </c>
       <c r="O29" s="0">
-        <v>-0.010153666255902749</v>
+        <v>0.11637663044637239</v>
       </c>
       <c r="P29" s="0">
-        <v>-0.010984778813541873</v>
+        <v>0.11406217730848989</v>
       </c>
       <c r="Q29" s="0">
-        <v>-0.011696457617361156</v>
+        <v>0.11151743807643691</v>
       </c>
       <c r="R29" s="0">
-        <v>-0.012537220877430588</v>
+        <v>0.10949636493080912</v>
       </c>
       <c r="S29" s="0">
-        <v>-0.015125132893055615</v>
+        <v>0.10731663660533305</v>
       </c>
       <c r="T29" s="0">
-        <v>-0.015578887767013938</v>
+        <v>0.10422697046539653</v>
       </c>
       <c r="U29" s="0">
-        <v>-0.016234366640625053</v>
+        <v>0.096455303221901489</v>
       </c>
       <c r="V29" s="0">
-        <v>-0.013575225233333377</v>
+        <v>0.094484643220892645</v>
       </c>
       <c r="W29" s="0">
-        <v>-0.012957286889236252</v>
+        <v>0.094532985248322002</v>
       </c>
       <c r="X29" s="0">
-        <v>-0.018991799845486157</v>
+        <v>0.089528485028046945</v>
       </c>
       <c r="Y29" s="0">
-        <v>-0.018421365559722291</v>
+        <v>0.086575422388039253</v>
       </c>
       <c r="Z29" s="0">
-        <v>-0.017700926025000063</v>
+        <v>0.084985520096391584</v>
       </c>
       <c r="AA29" s="0">
-        <v>-0.015590269610416707</v>
+        <v>0.083596334155801838</v>
       </c>
       <c r="AB29" s="0">
-        <v>-0.017816270021527858</v>
+        <v>0.080199840436175229</v>
       </c>
       <c r="AC29" s="0">
-        <v>-0.024465945248263954</v>
+        <v>0.078483961027433061</v>
       </c>
       <c r="AD29" s="0">
-        <v>-0.024142062533680619</v>
+        <v>0.07757784256040004</v>
       </c>
       <c r="AE29" s="0">
-        <v>-0.023806279572569533</v>
+        <v>0.077143950205796188</v>
       </c>
       <c r="AF29" s="0">
-        <v>-0.023527039596875077</v>
+        <v>0.076037116578168182</v>
       </c>
       <c r="AG29" s="0">
-        <v>-0.022278856618402842</v>
+        <v>0.074348977208942457</v>
       </c>
       <c r="AH29" s="0">
-        <v>-0.020179589306250079</v>
+        <v>0.072453765350342952</v>
       </c>
       <c r="AI29" s="0">
-        <v>-0.018140447436458373</v>
+        <v>0.070889936827061503</v>
       </c>
       <c r="AJ29" s="0">
-        <v>-0.01738231551805558</v>
+        <v>0.069278422610074816</v>
       </c>
       <c r="AK29" s="0">
-        <v>-0.016010827393055593</v>
+        <v>0.067640276272277214</v>
       </c>
       <c r="AL29" s="0">
-        <v>-0.013940426909375081</v>
+        <v>0.065895904466486604</v>
       </c>
       <c r="AM29" s="0">
-        <v>-0.013265203390277813</v>
+        <v>0.064520281649981817</v>
       </c>
       <c r="AN29" s="0">
-        <v>-0.012840021098958321</v>
+        <v>0.063175830785952042</v>
       </c>
       <c r="AO29" s="0">
-        <v>-0.012441061004166754</v>
+        <v>0.061916940311712118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>349</v>
+        <v>509</v>
       </c>
       <c r="B30" s="0">
-        <v>-0.54470596966666673</v>
+        <v>-0.18565771113645946</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0015001926267360632</v>
+        <v>0.13977577731192187</v>
       </c>
       <c r="D30" s="0">
-        <v>0.0015392712246526941</v>
+        <v>0.14133949824916067</v>
       </c>
       <c r="E30" s="0">
-        <v>0.0014200025954861366</v>
+        <v>0.13988063410390336</v>
       </c>
       <c r="F30" s="0">
-        <v>0.0013223560906248104</v>
+        <v>0.1412281569780825</v>
       </c>
       <c r="G30" s="0">
-        <v>0.0011846292989583507</v>
+        <v>0.13938324998488058</v>
       </c>
       <c r="H30" s="0">
-        <v>0.00085329297951375338</v>
+        <v>0.14094703963849817</v>
       </c>
       <c r="I30" s="0">
-        <v>0.00076750649965273742</v>
+        <v>0.13836273928255213</v>
       </c>
       <c r="J30" s="0">
-        <v>4.0027719097168735e-05</v>
+        <v>0.13819208589511392</v>
       </c>
       <c r="K30" s="0">
-        <v>0.00022597760347220497</v>
+        <v>0.14245330148965163</v>
       </c>
       <c r="L30" s="0">
-        <v>-2.846737500060946e-06</v>
+        <v>0.13567832004815894</v>
       </c>
       <c r="M30" s="0">
-        <v>-0.00095864890625008137</v>
+        <v>0.13610354695201021</v>
       </c>
       <c r="N30" s="0">
-        <v>-0.0016151427767361346</v>
+        <v>0.13480921398181137</v>
       </c>
       <c r="O30" s="0">
-        <v>-0.0032883001253473099</v>
+        <v>0.13285961085172732</v>
       </c>
       <c r="P30" s="0">
-        <v>-0.0042068890385417168</v>
+        <v>0.13105231855873564</v>
       </c>
       <c r="Q30" s="0">
-        <v>-0.0053202039111112098</v>
+        <v>0.12964920132340285</v>
       </c>
       <c r="R30" s="0">
-        <v>-0.0062534039732639046</v>
+        <v>0.12787211881983984</v>
       </c>
       <c r="S30" s="0">
-        <v>-0.0076106143114582636</v>
+        <v>0.12680415240715343</v>
       </c>
       <c r="T30" s="0">
-        <v>-0.0094877758368056009</v>
+        <v>0.12456145803734817</v>
       </c>
       <c r="U30" s="0">
-        <v>-0.0118995733152778</v>
+        <v>0.11919042724891933</v>
       </c>
       <c r="V30" s="0">
-        <v>-0.014313182577430639</v>
+        <v>0.11637049935210385</v>
       </c>
       <c r="W30" s="0">
-        <v>-0.012005452432639063</v>
+        <v>0.11755944515213544</v>
       </c>
       <c r="X30" s="0">
-        <v>-0.013386563485763836</v>
+        <v>0.11459288262047411</v>
       </c>
       <c r="Y30" s="0">
-        <v>-0.019871628778125039</v>
+        <v>0.11200613728288789</v>
       </c>
       <c r="Z30" s="0">
-        <v>-0.021412679689236158</v>
+        <v>0.1111912997402424</v>
       </c>
       <c r="AA30" s="0">
-        <v>-0.021504170919791732</v>
+        <v>0.11026438226468828</v>
       </c>
       <c r="AB30" s="0">
-        <v>-0.02065137602951389</v>
+        <v>0.10766259172112955</v>
       </c>
       <c r="AC30" s="0">
-        <v>-0.024819082692708494</v>
+        <v>0.10606608952574553</v>
       </c>
       <c r="AD30" s="0">
-        <v>-0.033834730972222338</v>
+        <v>0.10403680183464065</v>
       </c>
       <c r="AE30" s="0">
-        <v>-0.033877714831944516</v>
+        <v>0.10322878024746002</v>
       </c>
       <c r="AF30" s="0">
-        <v>-0.034967086986458396</v>
+        <v>0.10260964876268591</v>
       </c>
       <c r="AG30" s="0">
-        <v>-0.036577007666666717</v>
+        <v>0.10159200767273587</v>
       </c>
       <c r="AH30" s="0">
-        <v>-0.036751095365625042</v>
+        <v>0.10038538423545332</v>
       </c>
       <c r="AI30" s="0">
-        <v>-0.035280617147916749</v>
+        <v>0.099103518382815142</v>
       </c>
       <c r="AJ30" s="0">
-        <v>-0.033994579103472256</v>
+        <v>0.098140099772998715</v>
       </c>
       <c r="AK30" s="0">
-        <v>-0.034469633501041763</v>
+        <v>0.09689182050058319</v>
       </c>
       <c r="AL30" s="0">
-        <v>-0.033787477229861196</v>
+        <v>0.095704778763864948</v>
       </c>
       <c r="AM30" s="0">
-        <v>-0.031552243043055594</v>
+        <v>0.094557310517333501</v>
       </c>
       <c r="AN30" s="0">
-        <v>-0.031968998651388969</v>
+        <v>0.093468300774063359</v>
       </c>
       <c r="AO30" s="0">
-        <v>-0.032770223580902924</v>
+        <v>0.092323344535053475</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>350</v>
+        <v>510</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.54534047756666681</v>
+        <v>-0.18593570529741982</v>
       </c>
       <c r="C31" s="0">
-        <v>0.0039535637670137236</v>
+        <v>0.14655624911801743</v>
       </c>
       <c r="D31" s="0">
-        <v>0.0039479872076387803</v>
+        <v>0.14727577775364098</v>
       </c>
       <c r="E31" s="0">
-        <v>0.0039311985107639558</v>
+        <v>0.1467351039161125</v>
       </c>
       <c r="F31" s="0">
-        <v>0.0039129269628472843</v>
+        <v>0.14752333994020178</v>
       </c>
       <c r="G31" s="0">
-        <v>0.0038699645795139408</v>
+        <v>0.14636251508587886</v>
       </c>
       <c r="H31" s="0">
-        <v>0.0038197284993054526</v>
+        <v>0.14734343974025094</v>
       </c>
       <c r="I31" s="0">
-        <v>0.0037462733489582729</v>
+        <v>0.14602746794352017</v>
       </c>
       <c r="J31" s="0">
-        <v>0.0036005643979166724</v>
+        <v>0.1459335645703484</v>
       </c>
       <c r="K31" s="0">
-        <v>0.0035830918406249972</v>
+        <v>0.14824606916746946</v>
       </c>
       <c r="L31" s="0">
-        <v>0.0035980027520833291</v>
+        <v>0.14463633919560073</v>
       </c>
       <c r="M31" s="0">
-        <v>0.0032271539124998365</v>
+        <v>0.14518893077998174</v>
       </c>
       <c r="N31" s="0">
-        <v>0.0029581440552082228</v>
+        <v>0.144547009490435</v>
       </c>
       <c r="O31" s="0">
-        <v>0.0025482794249999108</v>
+        <v>0.14377018527308155</v>
       </c>
       <c r="P31" s="0">
-        <v>0.0017961337673609856</v>
+        <v>0.14253002158151415</v>
       </c>
       <c r="Q31" s="0">
-        <v>0.0011857150527776476</v>
+        <v>0.14178026890517825</v>
       </c>
       <c r="R31" s="0">
-        <v>0.00057752446354153442</v>
+        <v>0.14091511922886835</v>
       </c>
       <c r="S31" s="0">
-        <v>-3.6038247916758692e-05</v>
+        <v>0.14043500323096694</v>
       </c>
       <c r="T31" s="0">
-        <v>-0.00099262433506952519</v>
+        <v>0.13937411129669722</v>
       </c>
       <c r="U31" s="0">
-        <v>-0.0028318831413194348</v>
+        <v>0.13606845496095146</v>
       </c>
       <c r="V31" s="0">
-        <v>-0.0050680408711806235</v>
+        <v>0.13446508738915885</v>
       </c>
       <c r="W31" s="0">
-        <v>-0.0067043191402776925</v>
+        <v>0.13159384824794568</v>
       </c>
       <c r="X31" s="0">
-        <v>-0.0058665940197917266</v>
+        <v>0.13326026676287564</v>
       </c>
       <c r="Y31" s="0">
-        <v>-0.0081184630506945243</v>
+        <v>0.13216261552672387</v>
       </c>
       <c r="Z31" s="0">
-        <v>-0.013564113029861158</v>
+        <v>0.131521583569184</v>
       </c>
       <c r="AA31" s="0">
-        <v>-0.015344501526041721</v>
+        <v>0.13002180951003184</v>
       </c>
       <c r="AB31" s="0">
-        <v>-0.016805570882986287</v>
+        <v>0.12784223693960514</v>
       </c>
       <c r="AC31" s="0">
-        <v>-0.01705700104687502</v>
+        <v>0.12659256626763274</v>
       </c>
       <c r="AD31" s="0">
-        <v>-0.021737090006944459</v>
+        <v>0.12472547253831111</v>
       </c>
       <c r="AE31" s="0">
-        <v>-0.029796268637152845</v>
+        <v>0.1224083387600523</v>
       </c>
       <c r="AF31" s="0">
-        <v>-0.03039393700034726</v>
+        <v>0.12159195815447361</v>
       </c>
       <c r="AG31" s="0">
-        <v>-0.032708618756597363</v>
+        <v>0.1206124895135397</v>
       </c>
       <c r="AH31" s="0">
-        <v>-0.035682615259374995</v>
+        <v>0.11922521809109318</v>
       </c>
       <c r="AI31" s="0">
-        <v>-0.037420001842013995</v>
+        <v>0.11774825163241241</v>
       </c>
       <c r="AJ31" s="0">
-        <v>-0.037086676453125078</v>
+        <v>0.1164784762473064</v>
       </c>
       <c r="AK31" s="0">
-        <v>-0.037720476380208479</v>
+        <v>0.11520661364317906</v>
       </c>
       <c r="AL31" s="0">
-        <v>-0.03960722051527793</v>
+        <v>0.11366023566006317</v>
       </c>
       <c r="AM31" s="0">
-        <v>-0.040277776795138998</v>
+        <v>0.11227364357284268</v>
       </c>
       <c r="AN31" s="0">
-        <v>-0.039098396064930652</v>
+        <v>0.11113503955222412</v>
       </c>
       <c r="AO31" s="0">
-        <v>-0.041224594138194626</v>
+        <v>0.10959399128532643</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>351</v>
+        <v>511</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.54541197106666672</v>
+        <v>-0.18596702843074348</v>
       </c>
       <c r="C32" s="0">
-        <v>0.0045124071440277849</v>
+        <v>0.14956991890751686</v>
       </c>
       <c r="D32" s="0">
-        <v>0.0045102694634722154</v>
+        <v>0.1499860468091474</v>
       </c>
       <c r="E32" s="0">
-        <v>0.0045095187714583318</v>
+        <v>0.14973473215478383</v>
       </c>
       <c r="F32" s="0">
-        <v>0.0045084015092360366</v>
+        <v>0.15014552586245555</v>
       </c>
       <c r="G32" s="0">
-        <v>0.0045047051177081743</v>
+        <v>0.14960537353267006</v>
       </c>
       <c r="H32" s="0">
-        <v>0.0044927174282637363</v>
+        <v>0.15011723379245295</v>
       </c>
       <c r="I32" s="0">
-        <v>0.0044626546604166198</v>
+        <v>0.14947549913620911</v>
       </c>
       <c r="J32" s="0">
-        <v>0.0044475144107638531</v>
+        <v>0.149478175633803</v>
       </c>
       <c r="K32" s="0">
-        <v>0.0044517793884026879</v>
+        <v>0.15059927854177987</v>
       </c>
       <c r="L32" s="0">
-        <v>0.0044354161468749265</v>
+        <v>0.1488392953672682</v>
       </c>
       <c r="M32" s="0">
-        <v>0.0043643043180555674</v>
+        <v>0.14924000865279388</v>
       </c>
       <c r="N32" s="0">
-        <v>0.004317611502777762</v>
+        <v>0.14901194604558007</v>
       </c>
       <c r="O32" s="0">
-        <v>0.0042725044243054899</v>
+        <v>0.14870444018515916</v>
       </c>
       <c r="P32" s="0">
-        <v>0.0041859532246526507</v>
+        <v>0.14815551637433622</v>
       </c>
       <c r="Q32" s="0">
-        <v>0.003963213027777801</v>
+        <v>0.14786146773553027</v>
       </c>
       <c r="R32" s="0">
-        <v>0.0038350598843749366</v>
+        <v>0.14754430182997713</v>
       </c>
       <c r="S32" s="0">
-        <v>0.0036406869486110822</v>
+        <v>0.1474256006988991</v>
       </c>
       <c r="T32" s="0">
-        <v>0.0034229388395832228</v>
+        <v>0.14712151434375112</v>
       </c>
       <c r="U32" s="0">
-        <v>0.0029473897579860293</v>
+        <v>0.1440239582663011</v>
       </c>
       <c r="V32" s="0">
-        <v>0.0021897186388887264</v>
+        <v>0.14195804706724494</v>
       </c>
       <c r="W32" s="0">
-        <v>0.0014305542409721599</v>
+        <v>0.14139934953422484</v>
       </c>
       <c r="X32" s="0">
-        <v>0.00071678860763879594</v>
+        <v>0.13556126406823227</v>
       </c>
       <c r="Y32" s="0">
-        <v>0.00078266272013871553</v>
+        <v>0.14099224834441321</v>
       </c>
       <c r="Z32" s="0">
-        <v>-0.00061375666875007617</v>
+        <v>0.13771511332661798</v>
       </c>
       <c r="AA32" s="0">
-        <v>-0.0028400341274306138</v>
+        <v>0.13861773671100075</v>
       </c>
       <c r="AB32" s="0">
-        <v>-0.0040447646208333632</v>
+        <v>0.13886316442767341</v>
       </c>
       <c r="AC32" s="0">
-        <v>-0.0048849999204861883</v>
+        <v>0.13773924693304904</v>
       </c>
       <c r="AD32" s="0">
-        <v>-0.0051908826555556731</v>
+        <v>0.13668304454554256</v>
       </c>
       <c r="AE32" s="0">
-        <v>-0.0078203014243056757</v>
+        <v>0.1351590697245719</v>
       </c>
       <c r="AF32" s="0">
-        <v>-0.011502506117708311</v>
+        <v>0.13360237369976335</v>
       </c>
       <c r="AG32" s="0">
-        <v>-0.011865469710069521</v>
+        <v>0.13296121183307119</v>
       </c>
       <c r="AH32" s="0">
-        <v>-0.01348028351111108</v>
+        <v>0.13207087909199802</v>
       </c>
       <c r="AI32" s="0">
-        <v>-0.015380084540277839</v>
+        <v>0.13086843896307129</v>
       </c>
       <c r="AJ32" s="0">
-        <v>-0.01668583036527771</v>
+        <v>0.12955651462065737</v>
       </c>
       <c r="AK32" s="0">
-        <v>-0.016673968436111242</v>
+        <v>0.12845132088220171</v>
       </c>
       <c r="AL32" s="0">
-        <v>-0.017746629263194591</v>
+        <v>0.12713738317143092</v>
       </c>
       <c r="AM32" s="0">
-        <v>-0.019077346566319542</v>
+        <v>0.1257746635981688</v>
       </c>
       <c r="AN32" s="0">
-        <v>-0.0196820841395835</v>
+        <v>0.12454353197385522</v>
       </c>
       <c r="AO32" s="0">
-        <v>-0.01922756012777771</v>
+        <v>0.1234879617762927</v>
       </c>
     </row>
   </sheetData>

--- a/output/mig_shocks.xlsx
+++ b/output/mig_shocks.xlsx
@@ -13,7 +13,103 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="544">
+  <si>
+    <t>mig_Q_2</t>
+  </si>
+  <si>
+    <t>mig_Q_3</t>
+  </si>
+  <si>
+    <t>mig_Q_4</t>
+  </si>
+  <si>
+    <t>mig_Q_5</t>
+  </si>
+  <si>
+    <t>mig_Q_6</t>
+  </si>
+  <si>
+    <t>mig_Q_7</t>
+  </si>
+  <si>
+    <t>mig_Q_8</t>
+  </si>
+  <si>
+    <t>mig_Q_9</t>
+  </si>
+  <si>
+    <t>mig_Q_10</t>
+  </si>
+  <si>
+    <t>mig_Q_11</t>
+  </si>
+  <si>
+    <t>mig_Q_12</t>
+  </si>
+  <si>
+    <t>mig_Q_13</t>
+  </si>
+  <si>
+    <t>mig_Q_14</t>
+  </si>
+  <si>
+    <t>mig_Q_15</t>
+  </si>
+  <si>
+    <t>mig_Q_16</t>
+  </si>
+  <si>
+    <t>mig_Q_17</t>
+  </si>
+  <si>
+    <t>mig_NQ_2</t>
+  </si>
+  <si>
+    <t>mig_NQ_3</t>
+  </si>
+  <si>
+    <t>mig_NQ_4</t>
+  </si>
+  <si>
+    <t>mig_NQ_5</t>
+  </si>
+  <si>
+    <t>mig_NQ_6</t>
+  </si>
+  <si>
+    <t>mig_NQ_7</t>
+  </si>
+  <si>
+    <t>mig_NQ_8</t>
+  </si>
+  <si>
+    <t>mig_NQ_9</t>
+  </si>
+  <si>
+    <t>mig_NQ_10</t>
+  </si>
+  <si>
+    <t>mig_NQ_11</t>
+  </si>
+  <si>
+    <t>mig_NQ_12</t>
+  </si>
+  <si>
+    <t>mig_NQ_13</t>
+  </si>
+  <si>
+    <t>mig_NQ_14</t>
+  </si>
+  <si>
+    <t>mig_NQ_15</t>
+  </si>
+  <si>
+    <t>mig_NQ_16</t>
+  </si>
+  <si>
+    <t>mig_NQ_17</t>
+  </si>
   <si>
     <t>mig_Q_2</t>
   </si>
@@ -1569,7 +1665,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1593,11 +1689,12 @@
     <border/>
     <border/>
     <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -1615,6 +1712,7 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1628,4046 +1726,4046 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="true"/>
-    <col min="2" max="2" width="14.42578125" customWidth="true"/>
-    <col min="3" max="3" width="14.42578125" customWidth="true"/>
-    <col min="4" max="4" width="14.42578125" customWidth="true"/>
-    <col min="5" max="5" width="14.42578125" customWidth="true"/>
-    <col min="6" max="6" width="14.42578125" customWidth="true"/>
-    <col min="7" max="7" width="14.42578125" customWidth="true"/>
-    <col min="8" max="8" width="14.42578125" customWidth="true"/>
-    <col min="9" max="9" width="14.42578125" customWidth="true"/>
-    <col min="10" max="10" width="14.42578125" customWidth="true"/>
-    <col min="11" max="11" width="14.42578125" customWidth="true"/>
-    <col min="12" max="12" width="14.42578125" customWidth="true"/>
-    <col min="13" max="13" width="14.42578125" customWidth="true"/>
-    <col min="14" max="14" width="14.42578125" customWidth="true"/>
-    <col min="15" max="15" width="14.42578125" customWidth="true"/>
-    <col min="16" max="16" width="14.42578125" customWidth="true"/>
-    <col min="17" max="17" width="14.42578125" customWidth="true"/>
-    <col min="18" max="18" width="14.42578125" customWidth="true"/>
-    <col min="19" max="19" width="14.42578125" customWidth="true"/>
-    <col min="20" max="20" width="14.42578125" customWidth="true"/>
-    <col min="21" max="21" width="13.7109375" customWidth="true"/>
-    <col min="22" max="22" width="14.42578125" customWidth="true"/>
-    <col min="23" max="23" width="14.42578125" customWidth="true"/>
-    <col min="24" max="24" width="14.42578125" customWidth="true"/>
-    <col min="25" max="25" width="14.42578125" customWidth="true"/>
-    <col min="26" max="26" width="14.42578125" customWidth="true"/>
-    <col min="27" max="27" width="14.42578125" customWidth="true"/>
-    <col min="28" max="28" width="14.42578125" customWidth="true"/>
-    <col min="29" max="29" width="13.7109375" customWidth="true"/>
-    <col min="30" max="30" width="14.42578125" customWidth="true"/>
-    <col min="31" max="31" width="14.42578125" customWidth="true"/>
-    <col min="32" max="32" width="14.42578125" customWidth="true"/>
-    <col min="33" max="33" width="14.42578125" customWidth="true"/>
-    <col min="34" max="34" width="14.42578125" customWidth="true"/>
-    <col min="35" max="35" width="14.42578125" customWidth="true"/>
-    <col min="36" max="36" width="14.42578125" customWidth="true"/>
-    <col min="37" max="37" width="14.42578125" customWidth="true"/>
-    <col min="38" max="38" width="14.42578125" customWidth="true"/>
-    <col min="39" max="39" width="14.42578125" customWidth="true"/>
-    <col min="40" max="40" width="14.42578125" customWidth="true"/>
-    <col min="41" max="41" width="14.42578125" customWidth="true"/>
+    <col min="2" max="2" width="13.42578125" customWidth="true"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true"/>
+    <col min="4" max="4" width="16.42578125" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="7" max="7" width="16.42578125" customWidth="true"/>
+    <col min="8" max="8" width="16.42578125" customWidth="true"/>
+    <col min="9" max="9" width="15.7109375" customWidth="true"/>
+    <col min="10" max="10" width="16.42578125" customWidth="true"/>
+    <col min="11" max="11" width="16.42578125" customWidth="true"/>
+    <col min="12" max="12" width="16.42578125" customWidth="true"/>
+    <col min="13" max="13" width="16.42578125" customWidth="true"/>
+    <col min="14" max="14" width="16.28515625" customWidth="true"/>
+    <col min="15" max="15" width="16.42578125" customWidth="true"/>
+    <col min="16" max="16" width="16.42578125" customWidth="true"/>
+    <col min="17" max="17" width="16.42578125" customWidth="true"/>
+    <col min="18" max="18" width="16.42578125" customWidth="true"/>
+    <col min="19" max="19" width="16.42578125" customWidth="true"/>
+    <col min="20" max="20" width="16.42578125" customWidth="true"/>
+    <col min="21" max="21" width="16.42578125" customWidth="true"/>
+    <col min="22" max="22" width="16.42578125" customWidth="true"/>
+    <col min="23" max="23" width="16.42578125" customWidth="true"/>
+    <col min="24" max="24" width="16.42578125" customWidth="true"/>
+    <col min="25" max="25" width="16.42578125" customWidth="true"/>
+    <col min="26" max="26" width="16.42578125" customWidth="true"/>
+    <col min="27" max="27" width="16.42578125" customWidth="true"/>
+    <col min="28" max="28" width="16.42578125" customWidth="true"/>
+    <col min="29" max="29" width="16.42578125" customWidth="true"/>
+    <col min="30" max="30" width="16.42578125" customWidth="true"/>
+    <col min="31" max="31" width="16.42578125" customWidth="true"/>
+    <col min="32" max="32" width="16.42578125" customWidth="true"/>
+    <col min="33" max="33" width="15.7109375" customWidth="true"/>
+    <col min="34" max="34" width="16.42578125" customWidth="true"/>
+    <col min="35" max="35" width="16.42578125" customWidth="true"/>
+    <col min="36" max="36" width="15.42578125" customWidth="true"/>
+    <col min="37" max="37" width="16.42578125" customWidth="true"/>
+    <col min="38" max="38" width="16.28515625" customWidth="true"/>
+    <col min="39" max="39" width="15.7109375" customWidth="true"/>
+    <col min="40" max="40" width="15.7109375" customWidth="true"/>
+    <col min="41" max="41" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="B1" s="0">
-        <v>-0.1107428645225909</v>
+        <v>-0.30803898096419458</v>
       </c>
       <c r="C1" s="0">
-        <v>-0.095736370836377205</v>
+        <v>-0.25900438739246801</v>
       </c>
       <c r="D1" s="0">
-        <v>-0.10488887546989545</v>
+        <v>-0.25978882526852948</v>
       </c>
       <c r="E1" s="0">
-        <v>-0.095178263142475975</v>
+        <v>-0.25586735511683684</v>
       </c>
       <c r="F1" s="0">
-        <v>-0.080405561650117585</v>
+        <v>-0.24275421403957989</v>
       </c>
       <c r="G1" s="0">
-        <v>-0.088749732737430267</v>
+        <v>-0.22791608089898185</v>
       </c>
       <c r="H1" s="0">
-        <v>-0.090679863714621459</v>
+        <v>-0.2304079593477793</v>
       </c>
       <c r="I1" s="0">
-        <v>-0.093856483266593779</v>
+        <v>-0.23365261741205923</v>
       </c>
       <c r="J1" s="0">
-        <v>-0.10453262505952855</v>
+        <v>-0.24902608285594571</v>
       </c>
       <c r="K1" s="0">
-        <v>-0.091259374414196251</v>
+        <v>-0.23384247394064644</v>
       </c>
       <c r="L1" s="0">
-        <v>-0.093082997989318517</v>
+        <v>-0.22536593427361393</v>
       </c>
       <c r="M1" s="0">
-        <v>-0.10783484186900835</v>
+        <v>-0.24677992581274039</v>
       </c>
       <c r="N1" s="0">
-        <v>-0.12283369596897212</v>
+        <v>-0.270787492117398</v>
       </c>
       <c r="O1" s="0">
-        <v>-0.14681106797395399</v>
+        <v>-0.30975108096505166</v>
       </c>
       <c r="P1" s="0">
-        <v>-0.16173573355591819</v>
+        <v>-0.33412395444458853</v>
       </c>
       <c r="Q1" s="0">
-        <v>-0.15604324050607352</v>
+        <v>-0.32491786124368671</v>
       </c>
       <c r="R1" s="0">
-        <v>-0.15536181194574439</v>
+        <v>-0.32302475760816274</v>
       </c>
       <c r="S1" s="0">
-        <v>-0.1502104119090652</v>
+        <v>-0.31433803917659925</v>
       </c>
       <c r="T1" s="0">
-        <v>-0.14390485373846765</v>
+        <v>-0.30354154877701134</v>
       </c>
       <c r="U1" s="0">
-        <v>-0.14473266254801087</v>
+        <v>-0.30419128844935911</v>
       </c>
       <c r="V1" s="0">
-        <v>-0.14370178521221891</v>
+        <v>-0.30115690966135011</v>
       </c>
       <c r="W1" s="0">
-        <v>-0.14652654741622562</v>
+        <v>-0.30463618601934889</v>
       </c>
       <c r="X1" s="0">
-        <v>-0.15017414907680604</v>
+        <v>-0.30954129702193633</v>
       </c>
       <c r="Y1" s="0">
-        <v>-0.15374266878050058</v>
+        <v>-0.31452967751368538</v>
       </c>
       <c r="Z1" s="0">
-        <v>-0.15920757063091989</v>
+        <v>-0.32244309087148898</v>
       </c>
       <c r="AA1" s="0">
-        <v>-0.15525222627536026</v>
+        <v>-0.31508806687373769</v>
       </c>
       <c r="AB1" s="0">
-        <v>-0.14955049335410209</v>
+        <v>-0.30475677872284956</v>
       </c>
       <c r="AC1" s="0">
-        <v>-0.14186660452308661</v>
+        <v>-0.29084318665382436</v>
       </c>
       <c r="AD1" s="0">
-        <v>-0.13818468198484563</v>
+        <v>-0.2828652606984996</v>
       </c>
       <c r="AE1" s="0">
-        <v>-0.14111714373604786</v>
+        <v>-0.28583864782623053</v>
       </c>
       <c r="AF1" s="0">
-        <v>-0.14502784508844532</v>
+        <v>-0.29125239197936997</v>
       </c>
       <c r="AG1" s="0">
-        <v>-0.1450964111377854</v>
+        <v>-0.2909784159392742</v>
       </c>
       <c r="AH1" s="0">
-        <v>-0.14200630191622468</v>
+        <v>-0.28583595295269504</v>
       </c>
       <c r="AI1" s="0">
-        <v>-0.13698920206168227</v>
+        <v>-0.27712736602401</v>
       </c>
       <c r="AJ1" s="0">
-        <v>-0.13249381165319327</v>
+        <v>-0.26935014014309483</v>
       </c>
       <c r="AK1" s="0">
-        <v>-0.13010872747130081</v>
+        <v>-0.26523605109079873</v>
       </c>
       <c r="AL1" s="0">
-        <v>-0.12979373998136196</v>
+        <v>-0.26467667761521607</v>
       </c>
       <c r="AM1" s="0">
-        <v>-0.12960568428678274</v>
+        <v>-0.26458085341806098</v>
       </c>
       <c r="AN1" s="0">
-        <v>-0.12766515469343107</v>
+        <v>-0.26158027856899385</v>
       </c>
       <c r="AO1" s="0">
-        <v>-0.12397941799758082</v>
+        <v>-0.25598040693746577</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.16275770258764655</v>
+        <v>-0.32437011457316089</v>
       </c>
       <c r="C2" s="0">
-        <v>0.022003809095469697</v>
+        <v>0.0037367387732163441</v>
       </c>
       <c r="D2" s="0">
-        <v>0.022281861504426629</v>
+        <v>0.0042894531899560712</v>
       </c>
       <c r="E2" s="0">
-        <v>0.02261190552769736</v>
+        <v>0.0031299024481148646</v>
       </c>
       <c r="F2" s="0">
-        <v>0.028312768630661178</v>
+        <v>0.0037706650910997769</v>
       </c>
       <c r="G2" s="0">
-        <v>0.022477721936252949</v>
+        <v>0.0059721951904871439</v>
       </c>
       <c r="H2" s="0">
-        <v>0.021957916390620252</v>
+        <v>0.0052432726378985727</v>
       </c>
       <c r="I2" s="0">
-        <v>0.020922668140674148</v>
+        <v>0.0040683702025894088</v>
       </c>
       <c r="J2" s="0">
-        <v>0.017099301718304198</v>
+        <v>-0.00134800017577493</v>
       </c>
       <c r="K2" s="0">
-        <v>0.024824626970022908</v>
+        <v>0.0083269628042150282</v>
       </c>
       <c r="L2" s="0">
-        <v>0.020728341248940754</v>
+        <v>0.0058902113480018576</v>
       </c>
       <c r="M2" s="0">
-        <v>0.020196251239284944</v>
+        <v>0.0056241475580916999</v>
       </c>
       <c r="N2" s="0">
-        <v>0.02056081273714341</v>
+        <v>0.0065119691312033531</v>
       </c>
       <c r="O2" s="0">
-        <v>0.020387482258185843</v>
+        <v>0.0064446935727571581</v>
       </c>
       <c r="P2" s="0">
-        <v>0.020053718516461132</v>
+        <v>0.0061009403518335892</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.019982026040851957</v>
+        <v>0.0059089773521658713</v>
       </c>
       <c r="R2" s="0">
-        <v>0.020282403610943137</v>
+        <v>0.006074252365679292</v>
       </c>
       <c r="S2" s="0">
-        <v>0.020379558474728093</v>
+        <v>0.0062944097015037196</v>
       </c>
       <c r="T2" s="0">
-        <v>0.021287697432583953</v>
+        <v>0.0076717624150505065</v>
       </c>
       <c r="U2" s="0">
-        <v>0.020701105866660779</v>
+        <v>0.0066687558634392873</v>
       </c>
       <c r="V2" s="0">
-        <v>0.020590662347425646</v>
+        <v>0.0066967291103875934</v>
       </c>
       <c r="W2" s="0">
-        <v>0.020663351205557783</v>
+        <v>0.0072313437334135004</v>
       </c>
       <c r="X2" s="0">
-        <v>0.020454859007612819</v>
+        <v>0.0070728425552607933</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.020527999548952069</v>
+        <v>0.0072417541289861703</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.020452535508507032</v>
+        <v>0.0071734067065276101</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.020327874487193434</v>
+        <v>0.007094309457860784</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.020342360347391696</v>
+        <v>0.0071161420144055442</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.020380480730023468</v>
+        <v>0.0071531910975457533</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.020434819765239545</v>
+        <v>0.0072036422366580392</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.020381931488870998</v>
+        <v>0.0071867895895637596</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.020228617548805887</v>
+        <v>0.0071059709788813879</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.020133023009378061</v>
+        <v>0.0070591811352715226</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.020139074256239241</v>
+        <v>0.007074432818161799</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.020160300292339832</v>
+        <v>0.0070982785753587107</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.020173072797594928</v>
+        <v>0.0071159954949375085</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.020159084700040412</v>
+        <v>0.0071159931159994663</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.020107149065063598</v>
+        <v>0.0070911677031647606</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.02003896838735927</v>
+        <v>0.0070551563832741354</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.019992830228797845</v>
+        <v>0.0070323858061772304</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.019983152365483918</v>
+        <v>0.0070321877938583043</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.16335356787586985</v>
+        <v>-0.32527025238100693</v>
       </c>
       <c r="C3" s="0">
-        <v>0.022801556177234436</v>
+        <v>0.004074857574734009</v>
       </c>
       <c r="D3" s="0">
-        <v>0.02279425490062878</v>
+        <v>0.0041156359500815953</v>
       </c>
       <c r="E3" s="0">
-        <v>0.02282076346023355</v>
+        <v>0.0036146315640813551</v>
       </c>
       <c r="F3" s="0">
-        <v>0.025613667151043833</v>
+        <v>0.0039707419619725614</v>
       </c>
       <c r="G3" s="0">
-        <v>0.022651220722485484</v>
+        <v>0.005390376598327847</v>
       </c>
       <c r="H3" s="0">
-        <v>0.02220556786452188</v>
+        <v>0.0047907995798618557</v>
       </c>
       <c r="I3" s="0">
-        <v>0.021396862708018178</v>
+        <v>0.0038027283772158701</v>
       </c>
       <c r="J3" s="0">
-        <v>0.018379945935769849</v>
+        <v>-0.00060226579197314141</v>
       </c>
       <c r="K3" s="0">
-        <v>0.025685909358027923</v>
+        <v>0.0091423964667345908</v>
       </c>
       <c r="L3" s="0">
-        <v>0.021424823112661497</v>
+        <v>0.0063337134148797299</v>
       </c>
       <c r="M3" s="0">
-        <v>0.020209472048681062</v>
+        <v>0.0052871797707472138</v>
       </c>
       <c r="N3" s="0">
-        <v>0.020829960136483021</v>
+        <v>0.006217263173913236</v>
       </c>
       <c r="O3" s="0">
-        <v>0.020787227565779578</v>
+        <v>0.0063166785601982654</v>
       </c>
       <c r="P3" s="0">
-        <v>0.020457423902788565</v>
+        <v>0.0058761775949530822</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.019894454700523076</v>
+        <v>0.0052392901429054112</v>
       </c>
       <c r="R3" s="0">
-        <v>0.019909974282832425</v>
+        <v>0.005283167595502832</v>
       </c>
       <c r="S3" s="0">
-        <v>0.020349699424266531</v>
+        <v>0.005664832630174187</v>
       </c>
       <c r="T3" s="0">
-        <v>0.021105055585820483</v>
+        <v>0.0069249229723483503</v>
       </c>
       <c r="U3" s="0">
-        <v>0.020605459485421133</v>
+        <v>0.0061231099969739616</v>
       </c>
       <c r="V3" s="0">
-        <v>0.020691451445748483</v>
+        <v>0.0063567244468138084</v>
       </c>
       <c r="W3" s="0">
-        <v>0.020809795267345176</v>
+        <v>0.0069467040280018627</v>
       </c>
       <c r="X3" s="0">
-        <v>0.020713936699016351</v>
+        <v>0.0070508581532172385</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.020712133808092597</v>
+        <v>0.0072179469397500489</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.020634727750603418</v>
+        <v>0.007156352957022204</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.020571288818172193</v>
+        <v>0.0071262870749732796</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.020436233909536698</v>
+        <v>0.0070655838751330002</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.020450755048063318</v>
+        <v>0.0070973274804517596</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.020488094026245865</v>
+        <v>0.0071434661988864475</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.020537350531904357</v>
+        <v>0.0071953894099666483</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.020480340578488646</v>
+        <v>0.007181193292065886</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.020323779833662174</v>
+        <v>0.0071039775755847587</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.020224967296607332</v>
+        <v>0.0070599334306602887</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.020227597551516336</v>
+        <v>0.0070766396977592818</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.020245531130590057</v>
+        <v>0.0071015933137534674</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.020255320757761555</v>
+        <v>0.0071204412831463743</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.020238714050839133</v>
+        <v>0.0071217383288566544</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.020184438828324054</v>
+        <v>0.0070983040123879897</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.020114175260965216</v>
+        <v>0.0070637202851779506</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.020066079899323363</v>
+        <v>0.0070421497623366098</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.16493238681031808</v>
+        <v>-0.32765527906862901</v>
       </c>
       <c r="C4" s="0">
-        <v>0.023189948013246527</v>
+        <v>0.0037015617625064229</v>
       </c>
       <c r="D4" s="0">
-        <v>0.023438863777525836</v>
+        <v>0.0039709855746803274</v>
       </c>
       <c r="E4" s="0">
-        <v>0.022883318704026795</v>
+        <v>0.0034137858085938537</v>
       </c>
       <c r="F4" s="0">
-        <v>0.024512750629386817</v>
+        <v>0.0041985771643767234</v>
       </c>
       <c r="G4" s="0">
-        <v>0.022734256372316259</v>
+        <v>0.0045744144610230571</v>
       </c>
       <c r="H4" s="0">
-        <v>0.022509219286223334</v>
+        <v>0.00415117811166667</v>
       </c>
       <c r="I4" s="0">
-        <v>0.021808416587484732</v>
+        <v>0.0034416565533047692</v>
       </c>
       <c r="J4" s="0">
-        <v>0.020164775071835596</v>
+        <v>0.00091321283014225935</v>
       </c>
       <c r="K4" s="0">
-        <v>0.025571870905878067</v>
+        <v>0.0080234701672299152</v>
       </c>
       <c r="L4" s="0">
-        <v>0.022019070135795227</v>
+        <v>0.0059772301743503189</v>
       </c>
       <c r="M4" s="0">
-        <v>0.020841247957448843</v>
+        <v>0.0050612112846288859</v>
       </c>
       <c r="N4" s="0">
-        <v>0.020852366976117892</v>
+        <v>0.0056021407275815066</v>
       </c>
       <c r="O4" s="0">
-        <v>0.021083216987886493</v>
+        <v>0.0058225076788892115</v>
       </c>
       <c r="P4" s="0">
-        <v>0.020884458435249064</v>
+        <v>0.0054850300755506683</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.020458744810589832</v>
+        <v>0.0049762043239745361</v>
       </c>
       <c r="R4" s="0">
-        <v>0.020314049762696282</v>
+        <v>0.0050329156514364228</v>
       </c>
       <c r="S4" s="0">
-        <v>0.020240472958799469</v>
+        <v>0.0050768295934617326</v>
       </c>
       <c r="T4" s="0">
-        <v>0.021234550880934126</v>
+        <v>0.0063440739891555938</v>
       </c>
       <c r="U4" s="0">
-        <v>0.020699444948553192</v>
+        <v>0.0056910242352906718</v>
       </c>
       <c r="V4" s="0">
-        <v>0.020762544324333634</v>
+        <v>0.005815577918901773</v>
       </c>
       <c r="W4" s="0">
-        <v>0.020882819183222403</v>
+        <v>0.0063208008786541153</v>
       </c>
       <c r="X4" s="0">
-        <v>0.020726305053340333</v>
+        <v>0.006370790162932548</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.020512046180127749</v>
+        <v>0.0063397027964451919</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.020291296516704093</v>
+        <v>0.006186544546677838</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.020271297297075854</v>
+        <v>0.0062346069630991752</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.020200588631455664</v>
+        <v>0.0062513538316153481</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.020063987044590031</v>
+        <v>0.0062123045547152912</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.020070915158084297</v>
+        <v>0.0062518631246137315</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.020098442356457542</v>
+        <v>0.0063005586280026962</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.020138693917021125</v>
+        <v>0.0063547583144320649</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.020074295204006495</v>
+        <v>0.0063447575444794246</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.019911864364307051</v>
+        <v>0.0062734139110011567</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.019807219475648116</v>
+        <v>0.0062336451724050827</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.019803763824800775</v>
+        <v>0.0062525631991005035</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.019816014435644815</v>
+        <v>0.0062793033371859128</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.019820694345206096</v>
+        <v>0.0062999855427746587</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.019799488614089995</v>
+        <v>0.0063032507175688575</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.019741201023739118</v>
+        <v>0.0062821170460723042</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.019667319615522583</v>
+        <v>0.0062497980959121879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="B5" s="0">
-        <v>-0.16727229740129096</v>
+        <v>-0.33119004108874012</v>
       </c>
       <c r="C5" s="0">
-        <v>0.023689043374868005</v>
+        <v>0.0032488984569095385</v>
       </c>
       <c r="D5" s="0">
-        <v>0.024184686736486945</v>
+        <v>0.003590151575189078</v>
       </c>
       <c r="E5" s="0">
-        <v>0.024363633394098454</v>
+        <v>0.0044952629752254775</v>
       </c>
       <c r="F5" s="0">
-        <v>0.025122066683719232</v>
+        <v>0.0048002777790654471</v>
       </c>
       <c r="G5" s="0">
-        <v>0.023382224592298662</v>
+        <v>0.0039956884846190626</v>
       </c>
       <c r="H5" s="0">
-        <v>0.023288036951929582</v>
+        <v>0.0037472580619608677</v>
       </c>
       <c r="I5" s="0">
-        <v>0.022787398904756142</v>
+        <v>0.0033012264129223309</v>
       </c>
       <c r="J5" s="0">
-        <v>0.021880746922185917</v>
+        <v>0.0019354487519385771</v>
       </c>
       <c r="K5" s="0">
-        <v>0.025094374305079496</v>
+        <v>0.0060384574203989757</v>
       </c>
       <c r="L5" s="0">
-        <v>0.022607162006737232</v>
+        <v>0.0052873872122043055</v>
       </c>
       <c r="M5" s="0">
-        <v>0.021975630707301668</v>
+        <v>0.0047266476332236476</v>
       </c>
       <c r="N5" s="0">
-        <v>0.021725611189028771</v>
+        <v>0.0052695023459371744</v>
       </c>
       <c r="O5" s="0">
-        <v>0.021321841575243045</v>
+        <v>0.0051332971714865925</v>
       </c>
       <c r="P5" s="0">
-        <v>0.021459827858516311</v>
+        <v>0.0049389313818257443</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.021073109676105744</v>
+        <v>0.0045571499356978429</v>
       </c>
       <c r="R5" s="0">
-        <v>0.021034393720896046</v>
+        <v>0.0046293708396120195</v>
       </c>
       <c r="S5" s="0">
-        <v>0.020731818994866532</v>
+        <v>0.0046688512482371955</v>
       </c>
       <c r="T5" s="0">
-        <v>0.021155923982957497</v>
+        <v>0.0055888500500988446</v>
       </c>
       <c r="U5" s="0">
-        <v>0.020927214934220846</v>
+        <v>0.0051767938287180081</v>
       </c>
       <c r="V5" s="0">
-        <v>0.020990757273174569</v>
+        <v>0.0053984067233546901</v>
       </c>
       <c r="W5" s="0">
-        <v>0.021120524979839711</v>
+        <v>0.0057139957357239578</v>
       </c>
       <c r="X5" s="0">
-        <v>0.020976332363633471</v>
+        <v>0.0057116210722974155</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.020740829866922716</v>
+        <v>0.0057184840907177695</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.020390288164728307</v>
+        <v>0.0055034594216768224</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.020281560009720149</v>
+        <v>0.0055349576168643782</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.020225529641220173</v>
+        <v>0.0055920495003610078</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.020133588833644987</v>
+        <v>0.0056102406747022436</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.019977342835157348</v>
+        <v>0.0055858918690686148</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.019963341139622996</v>
+        <v>0.0056313336886681309</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.019971165165873956</v>
+        <v>0.0056843237448965991</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.019993394735760294</v>
+        <v>0.0057423822912690183</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.019913828240698917</v>
+        <v>0.005739713398067549</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.019738939781287351</v>
+        <v>0.0056786361337296436</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.019622365985705815</v>
+        <v>0.005646592041483497</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.01960668210932669</v>
+        <v>0.0056693208656058867</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.019607571392473783</v>
+        <v>0.0056992136440212034</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.019601903706079518</v>
+        <v>0.0057230122251244473</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.019571425340507639</v>
+        <v>0.0057297762810444948</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.019504906190675221</v>
+        <v>0.0057125903422152145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.16813324401817331</v>
+        <v>-0.33249062129656481</v>
       </c>
       <c r="C6" s="0">
-        <v>0.02574544796021545</v>
+        <v>0.0033000631753161767</v>
       </c>
       <c r="D6" s="0">
-        <v>0.025935891688289234</v>
+        <v>0.0032411259088179719</v>
       </c>
       <c r="E6" s="0">
-        <v>0.025750241324224123</v>
+        <v>0.0035753505673029751</v>
       </c>
       <c r="F6" s="0">
-        <v>0.025819497853944894</v>
+        <v>0.0032473687728105435</v>
       </c>
       <c r="G6" s="0">
-        <v>0.024960142753624313</v>
+        <v>0.003348168281100493</v>
       </c>
       <c r="H6" s="0">
-        <v>0.024939283754654793</v>
+        <v>0.0033042762125795998</v>
       </c>
       <c r="I6" s="0">
-        <v>0.024466686085512345</v>
+        <v>0.0029759516157548522</v>
       </c>
       <c r="J6" s="0">
-        <v>0.023743885493940218</v>
+        <v>0.0019536712461226419</v>
       </c>
       <c r="K6" s="0">
-        <v>0.026057818629300337</v>
+        <v>0.0048957054012539322</v>
       </c>
       <c r="L6" s="0">
-        <v>0.023565074542873998</v>
+        <v>0.004364622446366778</v>
       </c>
       <c r="M6" s="0">
-        <v>0.023355677020177028</v>
+        <v>0.0040909687778338298</v>
       </c>
       <c r="N6" s="0">
-        <v>0.023285476571790281</v>
+        <v>0.0047095196298718531</v>
       </c>
       <c r="O6" s="0">
-        <v>0.022741222833215093</v>
+        <v>0.0047585616468984512</v>
       </c>
       <c r="P6" s="0">
-        <v>0.022333585837176696</v>
+        <v>0.0044811462714759989</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.022225078184596164</v>
+        <v>0.0041922591848637608</v>
       </c>
       <c r="R6" s="0">
-        <v>0.022044066518614642</v>
+        <v>0.0042052556859400415</v>
       </c>
       <c r="S6" s="0">
-        <v>0.021822246288314279</v>
+        <v>0.0042909735496780097</v>
       </c>
       <c r="T6" s="0">
-        <v>0.021952865444760477</v>
+        <v>0.0051715880446149632</v>
       </c>
       <c r="U6" s="0">
-        <v>0.021338850154075797</v>
+        <v>0.0048771259214555598</v>
       </c>
       <c r="V6" s="0">
-        <v>0.021643614506986257</v>
+        <v>0.0051791171465112671</v>
       </c>
       <c r="W6" s="0">
-        <v>0.021612802657761516</v>
+        <v>0.0053122715916598343</v>
       </c>
       <c r="X6" s="0">
-        <v>0.021483389380185364</v>
+        <v>0.0052330587615923756</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.021326308090679938</v>
+        <v>0.0052611175159954322</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.020897318276863402</v>
+        <v>0.0050305832078293405</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.020722352681874612</v>
+        <v>0.0051026718310043153</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.020549776419978509</v>
+        <v>0.005157086847051808</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.020463422065053999</v>
+        <v>0.005213690309919871</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.020340152305180281</v>
+        <v>0.0052461528226287442</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.020159942680353139</v>
+        <v>0.0052438583230834945</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.020119281905978358</v>
+        <v>0.0052984071606156794</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.020101990883197911</v>
+        <v>0.0053583185626929156</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.020101213018675977</v>
+        <v>0.0054225010307438178</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.020003554261119313</v>
+        <v>0.0054321174520044506</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.019814637529101651</v>
+        <v>0.0053878697400582863</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.019683961519701549</v>
+        <v>0.0053681188165983738</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.019653095898628035</v>
+        <v>0.0053970902837904939</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.019639751071327552</v>
+        <v>0.0054320246298646896</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.019621264275327937</v>
+        <v>0.0054609058682722495</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.019579489303443096</v>
+        <v>0.0054733585150849393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="B7" s="0">
-        <v>-0.17014158728099071</v>
+        <v>-0.33552450452105209</v>
       </c>
       <c r="C7" s="0">
-        <v>0.029593391507947139</v>
+        <v>0.0025528116630092247</v>
       </c>
       <c r="D7" s="0">
-        <v>0.030015497877183633</v>
+        <v>0.0027721816513922725</v>
       </c>
       <c r="E7" s="0">
-        <v>0.029309218925563058</v>
+        <v>0.0028113517016961145</v>
       </c>
       <c r="F7" s="0">
-        <v>0.029779834684115079</v>
+        <v>0.0031589661485599105</v>
       </c>
       <c r="G7" s="0">
-        <v>0.028578855912450386</v>
+        <v>0.0028755370406989256</v>
       </c>
       <c r="H7" s="0">
-        <v>0.028636646793967463</v>
+        <v>0.0027694466074503141</v>
       </c>
       <c r="I7" s="0">
-        <v>0.028076009648663625</v>
+        <v>0.0025810903578074242</v>
       </c>
       <c r="J7" s="0">
-        <v>0.027488007646117987</v>
+        <v>0.0017761580092238243</v>
       </c>
       <c r="K7" s="0">
-        <v>0.029596191965142165</v>
+        <v>0.0042785961598082421</v>
       </c>
       <c r="L7" s="0">
-        <v>0.026399765025813815</v>
+        <v>0.0039472575178651475</v>
       </c>
       <c r="M7" s="0">
-        <v>0.026019586524999416</v>
+        <v>0.0035257097152523063</v>
       </c>
       <c r="N7" s="0">
-        <v>0.025868024778638248</v>
+        <v>0.0039306160879445202</v>
       </c>
       <c r="O7" s="0">
-        <v>0.025533138431421971</v>
+        <v>0.0040412036007675062</v>
       </c>
       <c r="P7" s="0">
-        <v>0.024988983365771281</v>
+        <v>0.0039250214640885574</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.024236305892631604</v>
+        <v>0.0039260251242050313</v>
       </c>
       <c r="R7" s="0">
-        <v>0.02413093720457482</v>
+        <v>0.0038725286863194211</v>
       </c>
       <c r="S7" s="0">
-        <v>0.023733630432480377</v>
+        <v>0.0040033440825981157</v>
       </c>
       <c r="T7" s="0">
-        <v>0.023760248111773498</v>
+        <v>0.0047646566610195324</v>
       </c>
       <c r="U7" s="0">
-        <v>0.022671144964245656</v>
+        <v>0.0044780570068400768</v>
       </c>
       <c r="V7" s="0">
-        <v>0.022588911376757639</v>
+        <v>0.0048071340893820055</v>
       </c>
       <c r="W7" s="0">
-        <v>0.022545527095468729</v>
+        <v>0.0050760506312243414</v>
       </c>
       <c r="X7" s="0">
-        <v>0.022154744411615884</v>
+        <v>0.0047946997624418349</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.022132344091125043</v>
+        <v>0.0048804329205295004</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.021871124774797749</v>
+        <v>0.0047195066786715895</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.021685023007110064</v>
+        <v>0.0048575818038411045</v>
       </c>
       <c r="AB7" s="0">
-        <v>0.021386297574410268</v>
+        <v>0.0049364865625964559</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.021179072928005492</v>
+        <v>0.005013524671022322</v>
       </c>
       <c r="AD7" s="0">
-        <v>0.021043819837562389</v>
+        <v>0.0050868135761094422</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.020878662578113574</v>
+        <v>0.0051407710613757289</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.020663137841597186</v>
+        <v>0.0051650169694999323</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.020584497230098135</v>
+        <v>0.0052301416149350098</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.020531840904753188</v>
+        <v>0.0052983054367897481</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.020498796828474195</v>
+        <v>0.0053699639730083026</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.020374987660397696</v>
+        <v>0.0053945330866791725</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.020165142273046333</v>
+        <v>0.005370749042994079</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.02001380881741573</v>
+        <v>0.0053659476545225866</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.019961422034702244</v>
+        <v>0.0054024761230727072</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.01992800872095931</v>
+        <v>0.0054435470339240944</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.019891423422133504</v>
+        <v>0.005478679956272851</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="B8" s="0">
-        <v>-0.17210884531469733</v>
+        <v>-0.33849632276407887</v>
       </c>
       <c r="C8" s="0">
-        <v>0.036247249138823115</v>
+        <v>0.0021587028425459282</v>
       </c>
       <c r="D8" s="0">
-        <v>0.03682801506743022</v>
+        <v>0.0020545359181071529</v>
       </c>
       <c r="E8" s="0">
-        <v>0.036148456155527801</v>
+        <v>0.0031785095537768338</v>
       </c>
       <c r="F8" s="0">
-        <v>0.036387971370162406</v>
+        <v>0.0030314518652324492</v>
       </c>
       <c r="G8" s="0">
-        <v>0.034307080416091575</v>
+        <v>0.0022112170945689093</v>
       </c>
       <c r="H8" s="0">
-        <v>0.034533043607774157</v>
+        <v>0.0022391332027927769</v>
       </c>
       <c r="I8" s="0">
-        <v>0.033557460197449429</v>
+        <v>0.0018693973455336981</v>
       </c>
       <c r="J8" s="0">
-        <v>0.03298797509168401</v>
+        <v>0.0012534387343372197</v>
       </c>
       <c r="K8" s="0">
-        <v>0.03540501914296771</v>
+        <v>0.0034816099260177673</v>
       </c>
       <c r="L8" s="0">
-        <v>0.031057626834548518</v>
+        <v>0.0032796632011203699</v>
       </c>
       <c r="M8" s="0">
-        <v>0.030358427387226015</v>
+        <v>0.003038640945198544</v>
       </c>
       <c r="N8" s="0">
-        <v>0.029861607186537631</v>
+        <v>0.0032031458669168726</v>
       </c>
       <c r="O8" s="0">
-        <v>0.029423035993362347</v>
+        <v>0.0031266631336583361</v>
       </c>
       <c r="P8" s="0">
-        <v>0.029152538356885502</v>
+        <v>0.0030167155753286629</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.028066595843279928</v>
+        <v>0.0033938068280130328</v>
       </c>
       <c r="R8" s="0">
-        <v>0.027160552378449412</v>
+        <v>0.0036157232525768817</v>
       </c>
       <c r="S8" s="0">
-        <v>0.026459294123737688</v>
+        <v>0.0033693383250544499</v>
       </c>
       <c r="T8" s="0">
-        <v>0.026067308486251297</v>
+        <v>0.0040494857049803556</v>
       </c>
       <c r="U8" s="0">
-        <v>0.024868839786959456</v>
+        <v>0.0038818931969293469</v>
       </c>
       <c r="V8" s="0">
-        <v>0.024452026665562104</v>
+        <v>0.0042676727654035176</v>
       </c>
       <c r="W8" s="0">
-        <v>0.023614518321526105</v>
+        <v>0.0044342074175914457</v>
       </c>
       <c r="X8" s="0">
-        <v>0.02323418740139074</v>
+        <v>0.0040478827741880948</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.023141125511927343</v>
+        <v>0.0042855329886164559</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.023112964942801028</v>
+        <v>0.0042285996535042112</v>
       </c>
       <c r="AA8" s="0">
-        <v>0.023042711139417634</v>
+        <v>0.004411686367423044</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.022661670078950955</v>
+        <v>0.0045582214301436198</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.022321763394729369</v>
+        <v>0.0046719896216215456</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.022044773597790342</v>
+        <v>0.0047883773047591857</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.02183988348720289</v>
+        <v>0.0048843165378857764</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.021614455771321778</v>
+        <v>0.0049667841028271167</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.021348149476888952</v>
+        <v>0.0050268833599291475</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.021215530077801817</v>
+        <v>0.0051063927826108168</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.021112472223821219</v>
+        <v>0.0051855260656607513</v>
       </c>
       <c r="AJ8" s="0">
-        <v>0.021033438558651162</v>
+        <v>0.0052671213875268748</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.020872385564977575</v>
+        <v>0.0053120042704538975</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.020632726140877942</v>
+        <v>0.0053163423585505919</v>
       </c>
       <c r="AM8" s="0">
-        <v>0.020452164935631796</v>
+        <v>0.0053322159869354747</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.020369360540336504</v>
+        <v>0.0053791346057811195</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.02030767459316284</v>
+        <v>0.0054287356645051407</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="B9" s="0">
-        <v>-0.1749167292613526</v>
+        <v>-0.34273802395121267</v>
       </c>
       <c r="C9" s="0">
-        <v>0.046523617663987743</v>
+        <v>0.0012684626038741717</v>
       </c>
       <c r="D9" s="0">
-        <v>0.047208806498646637</v>
+        <v>0.0013248839726216523</v>
       </c>
       <c r="E9" s="0">
-        <v>0.046048064726465505</v>
+        <v>0.0014002891914485617</v>
       </c>
       <c r="F9" s="0">
-        <v>0.046418632751274891</v>
+        <v>0.0011209767699759284</v>
       </c>
       <c r="G9" s="0">
-        <v>0.043706247187409834</v>
+        <v>0.0012727669229780859</v>
       </c>
       <c r="H9" s="0">
-        <v>0.04418252010418873</v>
+        <v>0.0013182366747200519</v>
       </c>
       <c r="I9" s="0">
-        <v>0.042787320199794754</v>
+        <v>0.0011839848255571048</v>
       </c>
       <c r="J9" s="0">
-        <v>0.042230867673870125</v>
+        <v>0.00060222796278531663</v>
       </c>
       <c r="K9" s="0">
-        <v>0.04503339563674328</v>
+        <v>0.0023087383804174049</v>
       </c>
       <c r="L9" s="0">
-        <v>0.039248247717213205</v>
+        <v>0.0023549613885988914</v>
       </c>
       <c r="M9" s="0">
-        <v>0.038085026996394426</v>
+        <v>0.0022317067828583029</v>
       </c>
       <c r="N9" s="0">
-        <v>0.036873728620462683</v>
+        <v>0.0025393940899652257</v>
       </c>
       <c r="O9" s="0">
-        <v>0.035872474420907081</v>
+        <v>0.0022427883598876608</v>
       </c>
       <c r="P9" s="0">
-        <v>0.035767020562389368</v>
+        <v>0.0019706392001845943</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.034497492230983737</v>
+        <v>0.0022672689007282774</v>
       </c>
       <c r="R9" s="0">
-        <v>0.032838296737142302</v>
+        <v>0.0027869011207210491</v>
       </c>
       <c r="S9" s="0">
-        <v>0.031247160962381285</v>
+        <v>0.0031645732665353103</v>
       </c>
       <c r="T9" s="0">
-        <v>0.030313785950830431</v>
+        <v>0.0033023562758103418</v>
       </c>
       <c r="U9" s="0">
-        <v>0.028234452498058667</v>
+        <v>0.0030283889120976885</v>
       </c>
       <c r="V9" s="0">
-        <v>0.027941431256613056</v>
+        <v>0.0035177906693183727</v>
       </c>
       <c r="W9" s="0">
-        <v>0.026050524877333357</v>
+        <v>0.0038371990057950696</v>
       </c>
       <c r="X9" s="0">
-        <v>0.024883366201754877</v>
+        <v>0.0035525484085287642</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.024727986364617368</v>
+        <v>0.003593837704791796</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.02451233215442741</v>
+        <v>0.0035086669958644262</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.024687927430006921</v>
+        <v>0.0036890083420038924</v>
       </c>
       <c r="AB9" s="0">
-        <v>0.024312537295184181</v>
+        <v>0.0038484207460306279</v>
       </c>
       <c r="AC9" s="0">
-        <v>0.023900587468944804</v>
+        <v>0.0040178814125339558</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.023461001197051468</v>
+        <v>0.0041862857989561353</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.023092444090852846</v>
+        <v>0.0043480601594096139</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.022795935711952601</v>
+        <v>0.004468526990625196</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.022490238311118571</v>
+        <v>0.004582594148883277</v>
       </c>
       <c r="AH9" s="0">
-        <v>0.022155101529104423</v>
+        <v>0.0046830342529040796</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.021950905859871115</v>
+        <v>0.0047779633463537656</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.021781443285320435</v>
+        <v>0.004869273648792331</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.021641703466905127</v>
+        <v>0.0049619013422271228</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.021430415012264357</v>
+        <v>0.0050303853278668587</v>
       </c>
       <c r="AM9" s="0">
-        <v>0.021149408392297307</v>
+        <v>0.0050675878280037993</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.020928628217938686</v>
+        <v>0.0051073811309728916</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.020804915874534473</v>
+        <v>0.0051663469492665122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="B10" s="0">
-        <v>-0.17778612122431953</v>
+        <v>-0.34707264159456896</v>
       </c>
       <c r="C10" s="0">
-        <v>0.062976829300154399</v>
+        <v>0.00052676250384679942</v>
       </c>
       <c r="D10" s="0">
-        <v>0.063709398187967406</v>
+        <v>0.00046617953289697616</v>
       </c>
       <c r="E10" s="0">
-        <v>0.061943409687676414</v>
+        <v>0.00076477469782359336</v>
       </c>
       <c r="F10" s="0">
-        <v>0.062877066207258955</v>
+        <v>0.00092865924740307012</v>
       </c>
       <c r="G10" s="0">
-        <v>0.058930554066842569</v>
+        <v>0.00065955172374874711</v>
       </c>
       <c r="H10" s="0">
-        <v>0.059470472251153754</v>
+        <v>0.00043668952715515528</v>
       </c>
       <c r="I10" s="0">
-        <v>0.057114916395437025</v>
+        <v>0.00029588945772534946</v>
       </c>
       <c r="J10" s="0">
-        <v>0.05633510997155608</v>
+        <v>-8.9290449029654693e-05</v>
       </c>
       <c r="K10" s="0">
-        <v>0.060165239451561638</v>
+        <v>0.00095949378360503986</v>
       </c>
       <c r="L10" s="0">
-        <v>0.052043664029636082</v>
+        <v>0.0011001075012619234</v>
       </c>
       <c r="M10" s="0">
-        <v>0.05102779110249378</v>
+        <v>0.0011325173291540096</v>
       </c>
       <c r="N10" s="0">
-        <v>0.048871588896928261</v>
+        <v>0.0015308742888880584</v>
       </c>
       <c r="O10" s="0">
-        <v>0.046968524913258092</v>
+        <v>0.0015553230544846693</v>
       </c>
       <c r="P10" s="0">
-        <v>0.045906656441950022</v>
+        <v>0.00086344092351930545</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.044584863612058226</v>
+        <v>0.0010468244450346921</v>
       </c>
       <c r="R10" s="0">
-        <v>0.042685333649962125</v>
+        <v>0.0014080680328242637</v>
       </c>
       <c r="S10" s="0">
-        <v>0.040214127223147364</v>
+        <v>0.0021262166581331602</v>
       </c>
       <c r="T10" s="0">
-        <v>0.037787166407845484</v>
+        <v>0.0028759147509725483</v>
       </c>
       <c r="U10" s="0">
-        <v>0.034422297350956352</v>
+        <v>0.0021822842221097378</v>
       </c>
       <c r="V10" s="0">
-        <v>0.03352055899800916</v>
+        <v>0.0025099953742557593</v>
       </c>
       <c r="W10" s="0">
-        <v>0.031191021192010952</v>
+        <v>0.0029542317672168264</v>
       </c>
       <c r="X10" s="0">
-        <v>0.029133549864869674</v>
+        <v>0.0030274786790925436</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.027953672177495673</v>
+        <v>0.00310197334982766</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.027543156066884521</v>
+        <v>0.0025316392034875155</v>
       </c>
       <c r="AA10" s="0">
-        <v>0.027618450943772278</v>
+        <v>0.0026754143685475264</v>
       </c>
       <c r="AB10" s="0">
-        <v>0.027260561276137667</v>
+        <v>0.0028619671842934936</v>
       </c>
       <c r="AC10" s="0">
-        <v>0.026887345674224312</v>
+        <v>0.0030428293610118896</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.02626311917688556</v>
+        <v>0.0032604303396131908</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.025630913409993107</v>
+        <v>0.0034939458014503202</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.025089569369724115</v>
+        <v>0.0037147954147426685</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.0246233237235279</v>
+        <v>0.0038633048133268929</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.024166608480469177</v>
+        <v>0.0040175098008400087</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.023698545454423736</v>
+        <v>0.0041719868430301994</v>
       </c>
       <c r="AJ10" s="0">
-        <v>0.023363687640368679</v>
+        <v>0.0042874895633154084</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.023072498597178602</v>
+        <v>0.0043938862858370151</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.022821086018340299</v>
+        <v>0.0045002223614792319</v>
       </c>
       <c r="AM10" s="0">
-        <v>0.022512853069631626</v>
+        <v>0.0045999247837376269</v>
       </c>
       <c r="AN10" s="0">
-        <v>0.022148432288313143</v>
+        <v>0.0046825270705555264</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.021849050170244185</v>
+        <v>0.0047560788518727463</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="B11" s="0">
-        <v>-0.18104030883396921</v>
+        <v>-0.35198854684893299</v>
       </c>
       <c r="C11" s="0">
-        <v>0.082417033661443664</v>
+        <v>0.00014030820242922124</v>
       </c>
       <c r="D11" s="0">
-        <v>0.083187900684074251</v>
+        <v>0.00013737362406114861</v>
       </c>
       <c r="E11" s="0">
-        <v>0.081251475375417784</v>
+        <v>0.00015911646039536297</v>
       </c>
       <c r="F11" s="0">
-        <v>0.082527438621589622</v>
+        <v>0.0001902281137760746</v>
       </c>
       <c r="G11" s="0">
-        <v>0.077977179343417274</v>
+        <v>9.5660241737631461e-05</v>
       </c>
       <c r="H11" s="0">
-        <v>0.079741977982420567</v>
+        <v>6.9607391276409777e-05</v>
       </c>
       <c r="I11" s="0">
-        <v>0.075508680057012154</v>
+        <v>-0.0001120081810236689</v>
       </c>
       <c r="J11" s="0">
-        <v>0.074782581055996583</v>
+        <v>-0.00063960181568794487</v>
       </c>
       <c r="K11" s="0">
-        <v>0.08128696780926789</v>
+        <v>0.0001549940856431452</v>
       </c>
       <c r="L11" s="0">
-        <v>0.070213063832226003</v>
+        <v>7.6917400940532709e-05</v>
       </c>
       <c r="M11" s="0">
-        <v>0.068724498388106042</v>
+        <v>5.9615579647163429e-05</v>
       </c>
       <c r="N11" s="0">
-        <v>0.065931252001297583</v>
+        <v>0.00038545748544528262</v>
       </c>
       <c r="O11" s="0">
-        <v>0.063552098802430138</v>
+        <v>0.00054470230352157256</v>
       </c>
       <c r="P11" s="0">
-        <v>0.061308078331314367</v>
+        <v>0.000190206107305099</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.059147205213859258</v>
+        <v>-0.00015562621663854217</v>
       </c>
       <c r="R11" s="0">
-        <v>0.056968454480121028</v>
+        <v>-6.2297929101133868e-05</v>
       </c>
       <c r="S11" s="0">
-        <v>0.054410121874042407</v>
+        <v>0.00034249055191137796</v>
       </c>
       <c r="T11" s="0">
-        <v>0.050848437417486195</v>
+        <v>0.0016545731663619354</v>
       </c>
       <c r="U11" s="0">
-        <v>0.044891316641566328</v>
+        <v>0.0018440678203310728</v>
       </c>
       <c r="V11" s="0">
-        <v>0.043119837333470544</v>
+        <v>0.0012023864240943974</v>
       </c>
       <c r="W11" s="0">
-        <v>0.039468786312426903</v>
+        <v>0.0016313572171174574</v>
       </c>
       <c r="X11" s="0">
-        <v>0.036699858342891384</v>
+        <v>0.0017966815918496785</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.034478789071504048</v>
+        <v>0.0023225123880064595</v>
       </c>
       <c r="Z11" s="0">
-        <v>0.033206209073975201</v>
+        <v>0.0020090078968846596</v>
       </c>
       <c r="AA11" s="0">
-        <v>0.033099761797929131</v>
+        <v>0.0013956787276795566</v>
       </c>
       <c r="AB11" s="0">
-        <v>0.032245780174389185</v>
+        <v>0.0015187393647094244</v>
       </c>
       <c r="AC11" s="0">
-        <v>0.032037694421636891</v>
+        <v>0.0016976778588587832</v>
       </c>
       <c r="AD11" s="0">
-        <v>0.031396206815329598</v>
+        <v>0.0019029163051078393</v>
       </c>
       <c r="AE11" s="0">
-        <v>0.030372929288858624</v>
+        <v>0.0021850499988197024</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.029379081735084606</v>
+        <v>0.0025145021363337967</v>
       </c>
       <c r="AG11" s="0">
-        <v>0.028514607761855371</v>
+        <v>0.0028249430634042414</v>
       </c>
       <c r="AH11" s="0">
-        <v>0.027733687009058892</v>
+        <v>0.0030127942353770326</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.026997858408104626</v>
+        <v>0.0032284826029911123</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.026284466074741122</v>
+        <v>0.0034682718788680445</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.02571131377548258</v>
+        <v>0.0036157727142290042</v>
       </c>
       <c r="AL11" s="0">
-        <v>0.025198851193996747</v>
+        <v>0.0037450543566364563</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.024745178195560914</v>
+        <v>0.0038721089563700088</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.024261787759347765</v>
+        <v>0.0040214979327414593</v>
       </c>
       <c r="AO11" s="0">
-        <v>0.023747970472920588</v>
+        <v>0.0041779784084873131</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="B12" s="0">
-        <v>-0.18364093614627086</v>
+        <v>-0.35591715791956591</v>
       </c>
       <c r="C12" s="0">
-        <v>0.10517090094155176</v>
+        <v>0.00082014237412168475</v>
       </c>
       <c r="D12" s="0">
-        <v>0.10580993015471624</v>
+        <v>0.00076447014289643118</v>
       </c>
       <c r="E12" s="0">
-        <v>0.10320950836635356</v>
+        <v>0.00091968118537289465</v>
       </c>
       <c r="F12" s="0">
-        <v>0.10545627080138108</v>
+        <v>0.00072787836134325951</v>
       </c>
       <c r="G12" s="0">
-        <v>0.10002702104021828</v>
+        <v>0.00053757644363361856</v>
       </c>
       <c r="H12" s="0">
-        <v>0.10249658532690521</v>
+        <v>0.00039508481318119141</v>
       </c>
       <c r="I12" s="0">
-        <v>0.097818860182608894</v>
+        <v>0.00047376400806781421</v>
       </c>
       <c r="J12" s="0">
-        <v>0.096480363328798877</v>
+        <v>-0.0001594947141216733</v>
       </c>
       <c r="K12" s="0">
-        <v>0.10457011934048537</v>
+        <v>6.9355021418716223e-05</v>
       </c>
       <c r="L12" s="0">
-        <v>0.092170235015842816</v>
+        <v>0.00031443617050657801</v>
       </c>
       <c r="M12" s="0">
-        <v>0.091280531989394731</v>
+        <v>-0.00025980890291004045</v>
       </c>
       <c r="N12" s="0">
-        <v>0.088191098862777553</v>
+        <v>-8.3049504976002268e-05</v>
       </c>
       <c r="O12" s="0">
-        <v>0.085696331722334401</v>
+        <v>-0.00016971115843721855</v>
       </c>
       <c r="P12" s="0">
-        <v>0.082653410099551294</v>
+        <v>-0.00030952523821846395</v>
       </c>
       <c r="Q12" s="0">
-        <v>0.079976412685900986</v>
+        <v>-0.00040028924267024812</v>
       </c>
       <c r="R12" s="0">
-        <v>0.07704471357104048</v>
+        <v>-0.00085213017824565618</v>
       </c>
       <c r="S12" s="0">
-        <v>0.074705474262344765</v>
+        <v>-0.0010314837148826595</v>
       </c>
       <c r="T12" s="0">
-        <v>0.070610982406867362</v>
+        <v>-0.00046187931083325616</v>
       </c>
       <c r="U12" s="0">
-        <v>0.062823104733518972</v>
+        <v>0.00047299065322408773</v>
       </c>
       <c r="V12" s="0">
-        <v>0.060080984140842668</v>
+        <v>0.00075691479578390462</v>
       </c>
       <c r="W12" s="0">
-        <v>0.054805642067428433</v>
+        <v>-0.0001031651496259748</v>
       </c>
       <c r="X12" s="0">
-        <v>0.050516949582177208</v>
+        <v>-7.296656541991646e-05</v>
       </c>
       <c r="Y12" s="0">
-        <v>0.047805674140542903</v>
+        <v>0.00050181868982749245</v>
       </c>
       <c r="Z12" s="0">
-        <v>0.045591282442345053</v>
+        <v>0.00088662360182013204</v>
       </c>
       <c r="AA12" s="0">
-        <v>0.044207832351133965</v>
+        <v>0.00061795511642168002</v>
       </c>
       <c r="AB12" s="0">
-        <v>0.041804785931248117</v>
+        <v>-0.00046098453876434212</v>
       </c>
       <c r="AC12" s="0">
-        <v>0.04124962684251253</v>
+        <v>-0.00034866658530852265</v>
       </c>
       <c r="AD12" s="0">
-        <v>0.040871930009048388</v>
+        <v>-0.00014512106951935239</v>
       </c>
       <c r="AE12" s="0">
-        <v>0.039816460603801916</v>
+        <v>9.377182021514787e-05</v>
       </c>
       <c r="AF12" s="0">
-        <v>0.038230696842989208</v>
+        <v>0.00047234269779067046</v>
       </c>
       <c r="AG12" s="0">
-        <v>0.036712809387534427</v>
+        <v>0.00095329688939114121</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.035366278790592599</v>
+        <v>0.0014039468590864505</v>
       </c>
       <c r="AI12" s="0">
-        <v>0.034103804113198348</v>
+        <v>0.0016551372003671776</v>
       </c>
       <c r="AJ12" s="0">
-        <v>0.03292775661151566</v>
+        <v>0.0019710670094043536</v>
       </c>
       <c r="AK12" s="0">
-        <v>0.031813303143721057</v>
+        <v>0.0023507952116429156</v>
       </c>
       <c r="AL12" s="0">
-        <v>0.030846806921430672</v>
+        <v>0.0025513870795076899</v>
       </c>
       <c r="AM12" s="0">
-        <v>0.029961601608531025</v>
+        <v>0.002719996476736034</v>
       </c>
       <c r="AN12" s="0">
-        <v>0.029160243290941117</v>
+        <v>0.0028837617824500499</v>
       </c>
       <c r="AO12" s="0">
-        <v>0.028362086023628077</v>
+        <v>0.0031174294682592141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="B13" s="0">
-        <v>-0.18525013032928478</v>
+        <v>-0.35834807066599539</v>
       </c>
       <c r="C13" s="0">
-        <v>0.1236099553859327</v>
+        <v>0.0022171208019621477</v>
       </c>
       <c r="D13" s="0">
-        <v>0.12463348074012075</v>
+        <v>0.0022497995473598474</v>
       </c>
       <c r="E13" s="0">
-        <v>0.12281989464294402</v>
+        <v>0.0021482874199882022</v>
       </c>
       <c r="F13" s="0">
-        <v>0.1251306952946255</v>
+        <v>0.0021369182551695823</v>
       </c>
       <c r="G13" s="0">
-        <v>0.12044374451355407</v>
+        <v>0.0020469516856165318</v>
       </c>
       <c r="H13" s="0">
-        <v>0.12355693060213016</v>
+        <v>0.0019132899803076099</v>
       </c>
       <c r="I13" s="0">
-        <v>0.11889407990501209</v>
+        <v>0.0018687464532115977</v>
       </c>
       <c r="J13" s="0">
-        <v>0.11803091088152019</v>
+        <v>0.0016000080020164011</v>
       </c>
       <c r="K13" s="0">
-        <v>0.12598208324776061</v>
+        <v>0.0015700747771781509</v>
       </c>
       <c r="L13" s="0">
-        <v>0.11443764961056525</v>
+        <v>0.0015695055339967955</v>
       </c>
       <c r="M13" s="0">
-        <v>0.11414138028525442</v>
+        <v>0.0012194006029468587</v>
       </c>
       <c r="N13" s="0">
-        <v>0.11162469666438832</v>
+        <v>0.00080008053239988177</v>
       </c>
       <c r="O13" s="0">
-        <v>0.10898437954568645</v>
+        <v>0.00051158064831818264</v>
       </c>
       <c r="P13" s="0">
-        <v>0.10627124465019205</v>
+        <v>0.00028750048920467069</v>
       </c>
       <c r="Q13" s="0">
-        <v>0.10334913969679263</v>
+        <v>9.5989562010099963e-05</v>
       </c>
       <c r="R13" s="0">
-        <v>0.10106940497246596</v>
+        <v>-0.00012615791590068356</v>
       </c>
       <c r="S13" s="0">
-        <v>0.098680004715177974</v>
+        <v>-0.00082764938712557494</v>
       </c>
       <c r="T13" s="0">
-        <v>0.094977453863563294</v>
+        <v>-0.00093011338984266259</v>
       </c>
       <c r="U13" s="0">
-        <v>0.086600249258649592</v>
+        <v>-0.0010939344370006737</v>
       </c>
       <c r="V13" s="0">
-        <v>0.084455502102507019</v>
+        <v>-0.00036786032945099878</v>
       </c>
       <c r="W13" s="0">
-        <v>0.078559349317629396</v>
+        <v>-0.00017309061210042323</v>
       </c>
       <c r="X13" s="0">
-        <v>0.073457918609011824</v>
+        <v>-0.0017900450344081457</v>
       </c>
       <c r="Y13" s="0">
-        <v>0.07019333540858845</v>
+        <v>-0.0016088125690084127</v>
       </c>
       <c r="Z13" s="0">
-        <v>0.068414551002977345</v>
+        <v>-0.0013953755806399792</v>
       </c>
       <c r="AA13" s="0">
-        <v>0.066881294905168476</v>
+        <v>-0.0008070249161290725</v>
       </c>
       <c r="AB13" s="0">
-        <v>0.063354609597234671</v>
+        <v>-0.0013716157998159716</v>
       </c>
       <c r="AC13" s="0">
-        <v>0.06148847910731834</v>
+        <v>-0.0031249668558359848</v>
       </c>
       <c r="AD13" s="0">
-        <v>0.060583194769290166</v>
+        <v>-0.0030277846120129515</v>
       </c>
       <c r="AE13" s="0">
-        <v>0.059851706829368877</v>
+        <v>-0.0029065824108101134</v>
       </c>
       <c r="AF13" s="0">
-        <v>0.058514337491148496</v>
+        <v>-0.0027931516809583303</v>
       </c>
       <c r="AG13" s="0">
-        <v>0.056791870843915765</v>
+        <v>-0.0024247140710318155</v>
       </c>
       <c r="AH13" s="0">
-        <v>0.055091931349643554</v>
+        <v>-0.0018443612324068083</v>
       </c>
       <c r="AI13" s="0">
-        <v>0.053561619492070535</v>
+        <v>-0.0012677832770156023</v>
       </c>
       <c r="AJ13" s="0">
-        <v>0.052020119809765203</v>
+        <v>-0.0010321484515299734</v>
       </c>
       <c r="AK13" s="0">
-        <v>0.050550395449263721</v>
+        <v>-0.0006403112253874901</v>
       </c>
       <c r="AL13" s="0">
-        <v>0.04912804150994067</v>
+        <v>-7.6021047021720796e-05</v>
       </c>
       <c r="AM13" s="0">
-        <v>0.04781962129365367</v>
+        <v>0.0001416497461454685</v>
       </c>
       <c r="AN13" s="0">
-        <v>0.046558579836719752</v>
+        <v>0.000294121386878354</v>
       </c>
       <c r="AO13" s="0">
-        <v>0.045370169602065816</v>
+        <v>0.0004427828115284342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="B14" s="0">
-        <v>-0.18583563920433055</v>
+        <v>-0.35923256366411854</v>
       </c>
       <c r="C14" s="0">
-        <v>0.13642670785816144</v>
+        <v>0.0037186010661809897</v>
       </c>
       <c r="D14" s="0">
-        <v>0.13840412311818437</v>
+        <v>0.0037305530448068988</v>
       </c>
       <c r="E14" s="0">
-        <v>0.13657559537030201</v>
+        <v>0.0036964915289449882</v>
       </c>
       <c r="F14" s="0">
-        <v>0.1381450592040184</v>
+        <v>0.0036702630200264115</v>
       </c>
       <c r="G14" s="0">
-        <v>0.13591262323497491</v>
+        <v>0.0036311296093103221</v>
       </c>
       <c r="H14" s="0">
-        <v>0.1379481251806268</v>
+        <v>0.0035401024407397024</v>
       </c>
       <c r="I14" s="0">
-        <v>0.13466619138407199</v>
+        <v>0.0035152334709663206</v>
       </c>
       <c r="J14" s="0">
-        <v>0.1345721230843277</v>
+        <v>0.0033124045139042127</v>
       </c>
       <c r="K14" s="0">
-        <v>0.1398904068364718</v>
+        <v>0.0033671450053032715</v>
       </c>
       <c r="L14" s="0">
-        <v>0.13136752439894722</v>
+        <v>0.0033012324778144051</v>
       </c>
       <c r="M14" s="0">
-        <v>0.1321058015538438</v>
+        <v>0.0030365083321597874</v>
       </c>
       <c r="N14" s="0">
-        <v>0.13054982686680758</v>
+        <v>0.0028549269965790288</v>
       </c>
       <c r="O14" s="0">
-        <v>0.12827705153326774</v>
+        <v>0.0023917064802260021</v>
       </c>
       <c r="P14" s="0">
-        <v>0.12615583504482186</v>
+        <v>0.0021379980523580956</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.12446222609075301</v>
+        <v>0.0018305236416524058</v>
       </c>
       <c r="R14" s="0">
-        <v>0.12244466268290073</v>
+        <v>0.0015733350406953919</v>
       </c>
       <c r="S14" s="0">
-        <v>0.1212225646633048</v>
+        <v>0.0012013213136258347</v>
       </c>
       <c r="T14" s="0">
-        <v>0.11866224075875043</v>
+        <v>0.00068928543130651729</v>
       </c>
       <c r="U14" s="0">
-        <v>0.11249060037861129</v>
+        <v>2.8154338979151323e-05</v>
       </c>
       <c r="V14" s="0">
-        <v>0.10939356800451933</v>
+        <v>-0.00063469482462181722</v>
       </c>
       <c r="W14" s="0">
-        <v>0.10585606776406307</v>
+        <v>3.011942211058263e-06</v>
       </c>
       <c r="X14" s="0">
-        <v>0.10222501337494008</v>
+        <v>-0.00036486484918450994</v>
       </c>
       <c r="Y14" s="0">
-        <v>0.099394737870169891</v>
+        <v>-0.0021364570381968949</v>
       </c>
       <c r="Z14" s="0">
-        <v>0.098339032493910516</v>
+        <v>-0.0025503464359311165</v>
       </c>
       <c r="AA14" s="0">
-        <v>0.097075998687030637</v>
+        <v>-0.0025636469353936607</v>
       </c>
       <c r="AB14" s="0">
-        <v>0.09385086626814465</v>
+        <v>-0.0023231926197178929</v>
       </c>
       <c r="AC14" s="0">
-        <v>0.091946295399886982</v>
+        <v>-0.0034480276511438526</v>
       </c>
       <c r="AD14" s="0">
-        <v>0.089947111790312326</v>
+        <v>-0.0059032457524544977</v>
       </c>
       <c r="AE14" s="0">
-        <v>0.088885884680601449</v>
+        <v>-0.0059087341623858458</v>
       </c>
       <c r="AF14" s="0">
-        <v>0.087875244009705616</v>
+        <v>-0.0061903964740008897</v>
       </c>
       <c r="AG14" s="0">
-        <v>0.086478063459015306</v>
+        <v>-0.0066115875390877462</v>
       </c>
       <c r="AH14" s="0">
-        <v>0.084885126777531461</v>
+        <v>-0.0066407836609141237</v>
       </c>
       <c r="AI14" s="0">
-        <v>0.083331460452876302</v>
+        <v>-0.0062290490948341843</v>
       </c>
       <c r="AJ14" s="0">
-        <v>0.081910971925124115</v>
+        <v>-0.0058567046031363229</v>
       </c>
       <c r="AK14" s="0">
-        <v>0.080357392107367642</v>
+        <v>-0.0059674266096615474</v>
       </c>
       <c r="AL14" s="0">
-        <v>0.078884659462459095</v>
+        <v>-0.0057648587810327709</v>
       </c>
       <c r="AM14" s="0">
-        <v>0.077500135496956182</v>
+        <v>-0.0051443170157757009</v>
       </c>
       <c r="AN14" s="0">
-        <v>0.076074802449707588</v>
+        <v>-0.0052334290387415529</v>
       </c>
       <c r="AO14" s="0">
-        <v>0.074639483208057994</v>
+        <v>-0.0054270517804635553</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B15" s="0">
-        <v>-0.18595477979686748</v>
+        <v>-0.35941254218260454</v>
       </c>
       <c r="C15" s="0">
-        <v>0.14469825244242859</v>
+        <v>0.004404053305266266</v>
       </c>
       <c r="D15" s="0">
-        <v>0.14567493402533585</v>
+        <v>0.0044029843205737511</v>
       </c>
       <c r="E15" s="0">
-        <v>0.14497415290844629</v>
+        <v>0.0043979606987675189</v>
       </c>
       <c r="F15" s="0">
-        <v>0.14591656466487285</v>
+        <v>0.0043933407248534853</v>
       </c>
       <c r="G15" s="0">
-        <v>0.14445119496873218</v>
+        <v>0.0043806900032205952</v>
       </c>
       <c r="H15" s="0">
-        <v>0.14573615521202932</v>
+        <v>0.0043674454745946138</v>
       </c>
       <c r="I15" s="0">
-        <v>0.14402597689694804</v>
+        <v>0.0043461747295572839</v>
       </c>
       <c r="J15" s="0">
-        <v>0.14390432092556693</v>
+        <v>0.0043054613757049325</v>
       </c>
       <c r="K15" s="0">
-        <v>0.14692018299971935</v>
+        <v>0.0043021322193534921</v>
       </c>
       <c r="L15" s="0">
-        <v>0.14222715153504792</v>
+        <v>0.0043043189353657568</v>
       </c>
       <c r="M15" s="0">
-        <v>0.14304334495802171</v>
+        <v>0.0042016478524050998</v>
       </c>
       <c r="N15" s="0">
-        <v>0.14221652295487697</v>
+        <v>0.0041264780873396132</v>
       </c>
       <c r="O15" s="0">
-        <v>0.14126882865425147</v>
+        <v>0.0040120862593377125</v>
       </c>
       <c r="P15" s="0">
-        <v>0.13974342701120618</v>
+        <v>0.0038026527807167977</v>
       </c>
       <c r="Q15" s="0">
-        <v>0.1388241754703787</v>
+        <v>0.0036326588686554557</v>
       </c>
       <c r="R15" s="0">
-        <v>0.1378403322788912</v>
+        <v>0.0034636216213798721</v>
       </c>
       <c r="S15" s="0">
-        <v>0.13729175789297757</v>
+        <v>0.0032934624584910134</v>
       </c>
       <c r="T15" s="0">
-        <v>0.13611295440155491</v>
+        <v>0.0030287801501758865</v>
       </c>
       <c r="U15" s="0">
-        <v>0.13219485176763174</v>
+        <v>0.0025180998380075854</v>
       </c>
       <c r="V15" s="0">
-        <v>0.13044680540388121</v>
+        <v>0.0018977759083092455</v>
       </c>
       <c r="W15" s="0">
-        <v>0.12366450757937004</v>
+        <v>0.0014421491077477933</v>
       </c>
       <c r="X15" s="0">
-        <v>0.12601505537072361</v>
+        <v>0.0016769044405705474</v>
       </c>
       <c r="Y15" s="0">
-        <v>0.12477298393958049</v>
+        <v>0.0010568498889281827</v>
       </c>
       <c r="Z15" s="0">
-        <v>0.12461770246088336</v>
+        <v>-0.00044865658373753489</v>
       </c>
       <c r="AA15" s="0">
-        <v>0.12294262895440075</v>
+        <v>-0.00093787565961252043</v>
       </c>
       <c r="AB15" s="0">
-        <v>0.12010389318417192</v>
+        <v>-0.0013408222816249332</v>
       </c>
       <c r="AC15" s="0">
-        <v>0.11843277682515395</v>
+        <v>-0.0014087851925469739</v>
       </c>
       <c r="AD15" s="0">
-        <v>0.11644737637291236</v>
+        <v>-0.002698277748635678</v>
       </c>
       <c r="AE15" s="0">
-        <v>0.11438502839354509</v>
+        <v>-0.0049239922265489561</v>
       </c>
       <c r="AF15" s="0">
-        <v>0.11326616233672976</v>
+        <v>-0.0050870204729872347</v>
       </c>
       <c r="AG15" s="0">
-        <v>0.11205673665216845</v>
+        <v>-0.0057213383523697751</v>
       </c>
       <c r="AH15" s="0">
-        <v>0.11045419090223814</v>
+        <v>-0.0065369494603903008</v>
       </c>
       <c r="AI15" s="0">
-        <v>0.10864526749254681</v>
+        <v>-0.0070104298515691428</v>
       </c>
       <c r="AJ15" s="0">
-        <v>0.10695283559850001</v>
+        <v>-0.0069144710197574302</v>
       </c>
       <c r="AK15" s="0">
-        <v>0.10524569973782406</v>
+        <v>-0.0070808237548501728</v>
       </c>
       <c r="AL15" s="0">
-        <v>0.10341343322223258</v>
+        <v>-0.0075942689984641095</v>
       </c>
       <c r="AM15" s="0">
-        <v>0.10167380389613098</v>
+        <v>-0.0077723437526624143</v>
       </c>
       <c r="AN15" s="0">
-        <v>0.10007745388822817</v>
+        <v>-0.0074410436983565241</v>
       </c>
       <c r="AO15" s="0">
-        <v>0.098265776604646318</v>
+        <v>-0.008017129168044642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="B16" s="0">
-        <v>-0.18596820400938119</v>
+        <v>-0.35943282133204152</v>
       </c>
       <c r="C16" s="0">
-        <v>0.14853665947761849</v>
+        <v>0.0045614951682824718</v>
       </c>
       <c r="D16" s="0">
-        <v>0.14910668529066889</v>
+        <v>0.0045611725537010881</v>
       </c>
       <c r="E16" s="0">
-        <v>0.14877598609941203</v>
+        <v>0.0045608013286917983</v>
       </c>
       <c r="F16" s="0">
-        <v>0.14926832320897021</v>
+        <v>0.0045607271395494619</v>
       </c>
       <c r="G16" s="0">
-        <v>0.14857821766596532</v>
+        <v>0.0045593599987505092</v>
       </c>
       <c r="H16" s="0">
-        <v>0.14925554663181534</v>
+        <v>0.0045563435688858829</v>
       </c>
       <c r="I16" s="0">
-        <v>0.14840673488680128</v>
+        <v>0.0045475383248455674</v>
       </c>
       <c r="J16" s="0">
-        <v>0.14839332481216494</v>
+        <v>0.0045432957150160084</v>
       </c>
       <c r="K16" s="0">
-        <v>0.14987502677819012</v>
+        <v>0.0045452262691952289</v>
       </c>
       <c r="L16" s="0">
-        <v>0.14756646984426186</v>
+        <v>0.0045395151303888881</v>
       </c>
       <c r="M16" s="0">
-        <v>0.14812856219773465</v>
+        <v>0.0045199567926274891</v>
       </c>
       <c r="N16" s="0">
-        <v>0.1478034722972936</v>
+        <v>0.0045069234533319652</v>
       </c>
       <c r="O16" s="0">
-        <v>0.14739231988097323</v>
+        <v>0.0044942057615569211</v>
       </c>
       <c r="P16" s="0">
-        <v>0.14665805990630987</v>
+        <v>0.0044697018096814117</v>
       </c>
       <c r="Q16" s="0">
-        <v>0.14627296244498464</v>
+        <v>0.0044074671209604682</v>
       </c>
       <c r="R16" s="0">
-        <v>0.14589178332226399</v>
+        <v>0.004371671044885503</v>
       </c>
       <c r="S16" s="0">
-        <v>0.14575206390474826</v>
+        <v>0.0043175724550535387</v>
       </c>
       <c r="T16" s="0">
-        <v>0.14542664041042103</v>
+        <v>0.0042569236093182644</v>
       </c>
       <c r="U16" s="0">
-        <v>0.14143893161188895</v>
+        <v>0.004122829506408715</v>
       </c>
       <c r="V16" s="0">
-        <v>0.13880691127573402</v>
+        <v>0.0039109618922022167</v>
       </c>
       <c r="W16" s="0">
-        <v>0.13568204609754575</v>
+        <v>0.0036982871942146975</v>
       </c>
       <c r="X16" s="0">
-        <v>0.12721722434518265</v>
+        <v>0.0034960251960664776</v>
       </c>
       <c r="Y16" s="0">
-        <v>0.13526554483878148</v>
+        <v>0.0035185967767654629</v>
       </c>
       <c r="Z16" s="0">
-        <v>0.1304359634176534</v>
+        <v>0.0031288708525383656</v>
       </c>
       <c r="AA16" s="0">
-        <v>0.13299240873596269</v>
+        <v>0.0025124548926538826</v>
       </c>
       <c r="AB16" s="0">
-        <v>0.13389049051599225</v>
+        <v>0.0021795135121365646</v>
       </c>
       <c r="AC16" s="0">
-        <v>0.13241495746737722</v>
+        <v>0.0019465461154109091</v>
       </c>
       <c r="AD16" s="0">
-        <v>0.13094572733106269</v>
+        <v>0.0018620772593290469</v>
       </c>
       <c r="AE16" s="0">
-        <v>0.12924303141549001</v>
+        <v>0.0011325684925560246</v>
       </c>
       <c r="AF16" s="0">
-        <v>0.12765506755268205</v>
+        <v>0.00011098713987680418</v>
       </c>
       <c r="AG16" s="0">
-        <v>0.126678214302512</v>
+        <v>1.1819533423087632e-05</v>
       </c>
       <c r="AH16" s="0">
-        <v>0.12557664515789399</v>
+        <v>-0.0004347053978382526</v>
       </c>
       <c r="AI16" s="0">
-        <v>0.12411798939855165</v>
+        <v>-0.00095940481779308517</v>
       </c>
       <c r="AJ16" s="0">
-        <v>0.1224345306471281</v>
+        <v>-0.0013184698623558823</v>
       </c>
       <c r="AK16" s="0">
-        <v>0.12083454892746448</v>
+        <v>-0.0013120804623575075</v>
       </c>
       <c r="AL16" s="0">
-        <v>0.11912669492788301</v>
+        <v>-0.0016058366889768964</v>
       </c>
       <c r="AM16" s="0">
-        <v>0.11738725123768901</v>
+        <v>-0.001970304712798663</v>
       </c>
       <c r="AN16" s="0">
-        <v>0.1157042589153804</v>
+        <v>-0.0021328026854857299</v>
       </c>
       <c r="AO16" s="0">
-        <v>0.11410340427010869</v>
+        <v>-0.0020016163787032856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="B17" s="0">
-        <v>-0.084623364717872476</v>
+        <v>-0.1808836392184785</v>
       </c>
       <c r="C17" s="0">
-        <v>-0.060831658554711836</v>
+        <v>-0.11271408104826511</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.050816315161778113</v>
+        <v>-0.10964161294234391</v>
       </c>
       <c r="E17" s="0">
-        <v>-0.05557107567120969</v>
+        <v>-0.12050165852824901</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.025815607778539425</v>
+        <v>-0.11108702316073926</v>
       </c>
       <c r="G17" s="0">
-        <v>-0.036554068633100061</v>
+        <v>-0.089721406928654948</v>
       </c>
       <c r="H17" s="0">
-        <v>-0.036855280708466123</v>
+        <v>-0.089339812892212281</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.041206134055569242</v>
+        <v>-0.095369052458330425</v>
       </c>
       <c r="J17" s="0">
-        <v>-0.063160911718041834</v>
+        <v>-0.12802665346838157</v>
       </c>
       <c r="K17" s="0">
-        <v>-0.040418567004743382</v>
+        <v>-0.1103189770454127</v>
       </c>
       <c r="L17" s="0">
-        <v>-0.033903819269692305</v>
+        <v>-0.087053999731209405</v>
       </c>
       <c r="M17" s="0">
-        <v>-0.048567170259762642</v>
+        <v>-0.10421787761257538</v>
       </c>
       <c r="N17" s="0">
-        <v>-0.062676099293552473</v>
+        <v>-0.12466121213500901</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.086467328032466581</v>
+        <v>-0.15956546409395309</v>
       </c>
       <c r="P17" s="0">
-        <v>-0.093771162639060351</v>
+        <v>-0.17034781732781953</v>
       </c>
       <c r="Q17" s="0">
-        <v>-0.075987012494404357</v>
+        <v>-0.14404679194924122</v>
       </c>
       <c r="R17" s="0">
-        <v>-0.075813882605074448</v>
+        <v>-0.14393273112512261</v>
       </c>
       <c r="S17" s="0">
-        <v>-0.070446840083892945</v>
+        <v>-0.13626894468749362</v>
       </c>
       <c r="T17" s="0">
-        <v>-0.061901028161008065</v>
+        <v>-0.12401972635935904</v>
       </c>
       <c r="U17" s="0">
-        <v>-0.062143206698986472</v>
+        <v>-0.12536059300192637</v>
       </c>
       <c r="V17" s="0">
-        <v>-0.063702137916616219</v>
+        <v>-0.12774798139750357</v>
       </c>
       <c r="W17" s="0">
-        <v>-0.066043518044152927</v>
+        <v>-0.13286026363529307</v>
       </c>
       <c r="X17" s="0">
-        <v>-0.068058877962437037</v>
+        <v>-0.13607262055281244</v>
       </c>
       <c r="Y17" s="0">
-        <v>-0.071333974214442153</v>
+        <v>-0.14132896522832589</v>
       </c>
       <c r="Z17" s="0">
-        <v>-0.078151942336847025</v>
+        <v>-0.15198550779641978</v>
       </c>
       <c r="AA17" s="0">
-        <v>-0.072641866238364369</v>
+        <v>-0.14449477677701639</v>
       </c>
       <c r="AB17" s="0">
-        <v>-0.064973151972641377</v>
+        <v>-0.13381866172658288</v>
       </c>
       <c r="AC17" s="0">
-        <v>-0.054835555604305058</v>
+        <v>-0.11980744678586612</v>
       </c>
       <c r="AD17" s="0">
-        <v>-0.050609587471828157</v>
+        <v>-0.11504458813795375</v>
       </c>
       <c r="AE17" s="0">
-        <v>-0.05520668776368802</v>
+        <v>-0.12317538744146909</v>
       </c>
       <c r="AF17" s="0">
-        <v>-0.059855219233771448</v>
+        <v>-0.13068097897623276</v>
       </c>
       <c r="AG17" s="0">
-        <v>-0.058785211578123761</v>
+        <v>-0.12926453921858044</v>
       </c>
       <c r="AH17" s="0">
-        <v>-0.054794331974886833</v>
+        <v>-0.12327271274689017</v>
       </c>
       <c r="AI17" s="0">
-        <v>-0.049817231045056289</v>
+        <v>-0.11627967765404827</v>
       </c>
       <c r="AJ17" s="0">
-        <v>-0.046095773927360917</v>
+        <v>-0.11106222222462919</v>
       </c>
       <c r="AK17" s="0">
-        <v>-0.045733726189365359</v>
+        <v>-0.11062424771912245</v>
       </c>
       <c r="AL17" s="0">
-        <v>-0.047946620687525643</v>
+        <v>-0.11385112649610146</v>
       </c>
       <c r="AM17" s="0">
-        <v>-0.050043601956575208</v>
+        <v>-0.11670916176445364</v>
       </c>
       <c r="AN17" s="0">
-        <v>-0.050072576512029135</v>
+        <v>-0.11662261254270606</v>
       </c>
       <c r="AO17" s="0">
-        <v>-0.048363932190138147</v>
+        <v>-0.11374730376425871</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="B18" s="0">
-        <v>-0.13180919163398755</v>
+        <v>-0.27761806279818224</v>
       </c>
       <c r="C18" s="0">
-        <v>0.029175073915595762</v>
+        <v>0.0027073880616345965</v>
       </c>
       <c r="D18" s="0">
-        <v>0.029808307076928223</v>
+        <v>0.0039970240593046368</v>
       </c>
       <c r="E18" s="0">
-        <v>0.031483657772088655</v>
+        <v>0.0012921890471917416</v>
       </c>
       <c r="F18" s="0">
-        <v>0.04668465531006185</v>
+        <v>0.0027893573669169817</v>
       </c>
       <c r="G18" s="0">
-        <v>0.03017800556290649</v>
+        <v>0.0079231882261724847</v>
       </c>
       <c r="H18" s="0">
-        <v>0.029183513786690454</v>
+        <v>0.0062225658725371209</v>
       </c>
       <c r="I18" s="0">
-        <v>0.026893022625965633</v>
+        <v>0.0034811792083022943</v>
       </c>
       <c r="J18" s="0">
-        <v>0.018055322990375568</v>
+        <v>-0.0091570239904724682</v>
       </c>
       <c r="K18" s="0">
-        <v>0.036762046744613808</v>
+        <v>0.013418342489654688</v>
       </c>
       <c r="L18" s="0">
-        <v>0.025864334835758437</v>
+        <v>0.0077314503387144054</v>
       </c>
       <c r="M18" s="0">
-        <v>0.024559220703505181</v>
+        <v>0.0071105769457644515</v>
       </c>
       <c r="N18" s="0">
-        <v>0.025426599405734333</v>
+        <v>0.0091821331080426533</v>
       </c>
       <c r="O18" s="0">
-        <v>0.025030026282699736</v>
+        <v>0.0090251413326884571</v>
       </c>
       <c r="P18" s="0">
-        <v>0.024231499644914729</v>
+        <v>0.0082230158584767777</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.024041917854109942</v>
+        <v>0.0077751008957056833</v>
       </c>
       <c r="R18" s="0">
-        <v>0.024767112322113673</v>
+        <v>0.008160790814185399</v>
       </c>
       <c r="S18" s="0">
-        <v>0.024984759109343415</v>
+        <v>0.0086744766737578034</v>
       </c>
       <c r="T18" s="0">
-        <v>0.027152208740770678</v>
+        <v>0.011888332234592833</v>
       </c>
       <c r="U18" s="0">
-        <v>0.025871072574240095</v>
+        <v>0.0095480592758461682</v>
       </c>
       <c r="V18" s="0">
-        <v>0.025468027891558703</v>
+        <v>0.0096132011927537037</v>
       </c>
       <c r="W18" s="0">
-        <v>0.026869383091655985</v>
+        <v>0.010861446039978771</v>
       </c>
       <c r="X18" s="0">
-        <v>0.02608311722398635</v>
+        <v>0.010491378371628656</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.026058621923474353</v>
+        <v>0.010885361843108492</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.025824753446109055</v>
+        <v>0.010725838672628931</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.025465972752470624</v>
+        <v>0.010541218111524394</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.025395796098652466</v>
+        <v>0.010592089743344283</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.025396764145247056</v>
+        <v>0.010678476259119741</v>
       </c>
       <c r="AD18" s="0">
-        <v>0.02544404192199003</v>
+        <v>0.01079614465360355</v>
       </c>
       <c r="AE18" s="0">
-        <v>0.025234896417233098</v>
+        <v>0.010756753377856679</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.0247888644487004</v>
+        <v>0.010568102993084211</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.024492212115562122</v>
+        <v>0.010458867931785578</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.024448904524587353</v>
+        <v>0.010494414305488347</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.024447199890543048</v>
+        <v>0.010550019617456883</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.024429502787863527</v>
+        <v>0.010591326746038618</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.024351710837953885</v>
+        <v>0.010591286214933427</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.024187073884576273</v>
+        <v>0.010533327710072662</v>
       </c>
       <c r="AM18" s="0">
-        <v>0.023987793956849961</v>
+        <v>0.01044927084526559</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.023844926519495505</v>
+        <v>0.010396112146616714</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.023792065186640107</v>
+        <v>0.010395628844351731</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="B19" s="0">
-        <v>-0.13319954382713328</v>
+        <v>-0.27971838412920641</v>
       </c>
       <c r="C19" s="0">
-        <v>0.030219834300164859</v>
+        <v>0.0034958255892538564</v>
       </c>
       <c r="D19" s="0">
-        <v>0.03041387868881322</v>
+        <v>0.0035911418587520885</v>
       </c>
       <c r="E19" s="0">
-        <v>0.03087177698872428</v>
+        <v>0.0024224532770896747</v>
       </c>
       <c r="F19" s="0">
-        <v>0.038182306906281313</v>
+        <v>0.003254287094460291</v>
       </c>
       <c r="G19" s="0">
-        <v>0.030034223470145675</v>
+        <v>0.0065653231081081948</v>
       </c>
       <c r="H19" s="0">
-        <v>0.029174506211094041</v>
+        <v>0.0051664407525917133</v>
       </c>
       <c r="I19" s="0">
-        <v>0.027457994491335583</v>
+        <v>0.002861080044847337</v>
       </c>
       <c r="J19" s="0">
-        <v>0.020628783703033626</v>
+        <v>-0.0074171120709058819</v>
       </c>
       <c r="K19" s="0">
-        <v>0.037807411815565337</v>
+        <v>0.015320560378561526</v>
       </c>
       <c r="L19" s="0">
-        <v>0.027188454034025748</v>
+        <v>0.0087661489330080038</v>
       </c>
       <c r="M19" s="0">
-        <v>0.02432649275892634</v>
+        <v>0.0063241531203982494</v>
       </c>
       <c r="N19" s="0">
-        <v>0.025888610716903186</v>
+        <v>0.0084944540411443763</v>
       </c>
       <c r="O19" s="0">
-        <v>0.025831307879421391</v>
+        <v>0.0087264354369285882</v>
       </c>
       <c r="P19" s="0">
-        <v>0.025102364155247969</v>
+        <v>0.0076986179427923655</v>
       </c>
       <c r="Q19" s="0">
-        <v>0.02377506099019382</v>
+        <v>0.0062125096324576702</v>
       </c>
       <c r="R19" s="0">
-        <v>0.023811742666486099</v>
+        <v>0.0063148957835798443</v>
       </c>
       <c r="S19" s="0">
-        <v>0.024879182828060599</v>
+        <v>0.0072055176921265989</v>
       </c>
       <c r="T19" s="0">
-        <v>0.026642609214487228</v>
+        <v>0.01014571096182164</v>
       </c>
       <c r="U19" s="0">
-        <v>0.025534946522023212</v>
+        <v>0.0082748623154080686</v>
       </c>
       <c r="V19" s="0">
-        <v>0.025647720130139936</v>
+        <v>0.008819885638580079</v>
       </c>
       <c r="W19" s="0">
-        <v>0.027400652389153186</v>
+        <v>0.01019749778928182</v>
       </c>
       <c r="X19" s="0">
-        <v>0.026839541998812291</v>
+        <v>0.010440245921321202</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.026610035838412583</v>
+        <v>0.010829936736279334</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.026291967022638186</v>
+        <v>0.010686114167653612</v>
       </c>
       <c r="AA19" s="0">
-        <v>0.026060333933323701</v>
+        <v>0.010615893428368354</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.025618908612249858</v>
+        <v>0.010474146014773854</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.025562732981433967</v>
+        <v>0.010548150872825082</v>
       </c>
       <c r="AD19" s="0">
-        <v>0.025569830405865336</v>
+        <v>0.01065575334704915</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.025612454984814681</v>
+        <v>0.010776855442899504</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.025400127118142685</v>
+        <v>0.010743669155302895</v>
       </c>
       <c r="AG19" s="0">
-        <v>0.024952155538729297</v>
+        <v>0.010563425751827124</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.024653194527403985</v>
+        <v>0.01046060091024453</v>
       </c>
       <c r="AI19" s="0">
-        <v>0.024606742989699032</v>
+        <v>0.010499544843021463</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.02460174994354946</v>
+        <v>0.010557736083916721</v>
       </c>
       <c r="AK19" s="0">
-        <v>0.02458112593050308</v>
+        <v>0.010601682649260227</v>
       </c>
       <c r="AL19" s="0">
-        <v>0.024500773643030351</v>
+        <v>0.010604677604610114</v>
       </c>
       <c r="AM19" s="0">
-        <v>0.024333928425249826</v>
+        <v>0.010549965958403048</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.024132656540793173</v>
+        <v>0.010469239797246772</v>
       </c>
       <c r="AO19" s="0">
-        <v>0.023987841941668555</v>
+        <v>0.010418883838582938</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B20" s="0">
-        <v>-0.13688345467417917</v>
+        <v>-0.2852834464003246</v>
       </c>
       <c r="C20" s="0">
-        <v>0.0309771873727324</v>
+        <v>0.0026247855720443582</v>
       </c>
       <c r="D20" s="0">
-        <v>0.03159890258572752</v>
+        <v>0.0032534722653785775</v>
       </c>
       <c r="E20" s="0">
-        <v>0.030580244138761807</v>
+        <v>0.0019535342447399382</v>
       </c>
       <c r="F20" s="0">
-        <v>0.034550665001526357</v>
+        <v>0.0037849894006237554</v>
       </c>
       <c r="G20" s="0">
-        <v>0.030084991992929827</v>
+        <v>0.0046614118841392131</v>
       </c>
       <c r="H20" s="0">
-        <v>0.029717692868678605</v>
+        <v>0.0036739736843943208</v>
       </c>
       <c r="I20" s="0">
-        <v>0.028157353741693571</v>
+        <v>0.0020184510841615173</v>
       </c>
       <c r="J20" s="0">
-        <v>0.024548528965283343</v>
+        <v>-0.0038810496490973082</v>
       </c>
       <c r="K20" s="0">
-        <v>0.037269400063485773</v>
+        <v>0.012709675260553908</v>
       </c>
       <c r="L20" s="0">
-        <v>0.028717751030244872</v>
+        <v>0.0079346219534819212</v>
       </c>
       <c r="M20" s="0">
-        <v>0.025857386757479981</v>
+        <v>0.005797041494986087</v>
       </c>
       <c r="N20" s="0">
-        <v>0.02588798138758967</v>
+        <v>0.0070591602244591345</v>
       </c>
       <c r="O20" s="0">
-        <v>0.026553047867194465</v>
+        <v>0.0075734981987441718</v>
       </c>
       <c r="P20" s="0">
-        <v>0.026163106382875584</v>
+        <v>0.0067861057936471642</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.025187328827265352</v>
+        <v>0.0055988367126486253</v>
       </c>
       <c r="R20" s="0">
-        <v>0.024847912854996632</v>
+        <v>0.0057311182682434287</v>
       </c>
       <c r="S20" s="0">
-        <v>0.024655986675981741</v>
+        <v>0.0058335712080342167</v>
       </c>
       <c r="T20" s="0">
-        <v>0.027048234907728029</v>
+        <v>0.0087905764547939035</v>
       </c>
       <c r="U20" s="0">
-        <v>0.025786132560951771</v>
+        <v>0.0072667643651777693</v>
       </c>
       <c r="V20" s="0">
-        <v>0.025905704120906831</v>
+        <v>0.0075573668090441973</v>
       </c>
       <c r="W20" s="0">
-        <v>0.028061365228953021</v>
+        <v>0.0087375139063410063</v>
       </c>
       <c r="X20" s="0">
-        <v>0.027268569329539295</v>
+        <v>0.0088538088981725861</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.026448263875282717</v>
+        <v>0.008780997202201787</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.025737487838706642</v>
+        <v>0.0084234624629007868</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.02556131384313598</v>
+        <v>0.0085355078628643558</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.025242374582716377</v>
+        <v>0.0085744560131512937</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.02479150516027212</v>
+        <v>0.0084832275452897052</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.024714390694267431</v>
+        <v>0.0085754624668360306</v>
       </c>
       <c r="AE20" s="0">
-        <v>0.024695918306715952</v>
+        <v>0.0086890256227436201</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.024715188034600662</v>
+        <v>0.0088154386836388644</v>
       </c>
       <c r="AG20" s="0">
-        <v>0.024481442093684962</v>
+        <v>0.008792033995633896</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.024014422044760134</v>
+        <v>0.0086254862270605196</v>
       </c>
       <c r="AI20" s="0">
-        <v>0.023698000899197848</v>
+        <v>0.0085326306443541874</v>
       </c>
       <c r="AJ20" s="0">
-        <v>0.023635297463765005</v>
+        <v>0.0085767310646387655</v>
       </c>
       <c r="AK20" s="0">
-        <v>0.023615356113950353</v>
+        <v>0.0086390876863168611</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.023581104463843212</v>
+        <v>0.0086873138451807694</v>
       </c>
       <c r="AM20" s="0">
-        <v>0.023488230445159051</v>
+        <v>0.0086948978050361194</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.023310054346325472</v>
+        <v>0.0086455514582321914</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.023098471051050482</v>
+        <v>0.0085701078818641047</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="B21" s="0">
-        <v>-0.14234324678332527</v>
+        <v>-0.29353122555033373</v>
       </c>
       <c r="C21" s="0">
-        <v>0.031849256613476311</v>
+        <v>0.0015684563481622106</v>
       </c>
       <c r="D21" s="0">
-        <v>0.033061786838209872</v>
+        <v>0.0023648029694398297</v>
       </c>
       <c r="E21" s="0">
-        <v>0.03357599905071007</v>
+        <v>0.0044767300740359327</v>
       </c>
       <c r="F21" s="0">
-        <v>0.035345383889328376</v>
+        <v>0.0051885452115587776</v>
       </c>
       <c r="G21" s="0">
-        <v>0.031385426342490849</v>
+        <v>0.003311063279557751</v>
       </c>
       <c r="H21" s="0">
-        <v>0.031248334348529541</v>
+        <v>0.0027314498566691141</v>
       </c>
       <c r="I21" s="0">
-        <v>0.030164171006044863</v>
+        <v>0.0016907277871513796</v>
       </c>
       <c r="J21" s="0">
-        <v>0.028133024805091195</v>
+        <v>-0.0014960258607302846</v>
       </c>
       <c r="K21" s="0">
-        <v>0.035744732537941526</v>
+        <v>0.0080778316488250672</v>
       </c>
       <c r="L21" s="0">
-        <v>0.030028452567364475</v>
+        <v>0.0063251202361476787</v>
       </c>
       <c r="M21" s="0">
-        <v>0.028624046765372679</v>
+        <v>0.0050167308660983932</v>
       </c>
       <c r="N21" s="0">
-        <v>0.027930158735556893</v>
+        <v>0.0062831610829762602</v>
       </c>
       <c r="O21" s="0">
-        <v>0.02700489295694623</v>
+        <v>0.0059653172749445458</v>
       </c>
       <c r="P21" s="0">
-        <v>0.027536878279913878</v>
+        <v>0.0055120564139676254</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.026658283129231731</v>
+        <v>0.0046212315324230509</v>
       </c>
       <c r="R21" s="0">
-        <v>0.0266140064060034</v>
+        <v>0.0047897484084301108</v>
       </c>
       <c r="S21" s="0">
-        <v>0.025847574592018373</v>
+        <v>0.004881752180492826</v>
       </c>
       <c r="T21" s="0">
-        <v>0.026830431114082426</v>
+        <v>0.0070284089038626252</v>
       </c>
       <c r="U21" s="0">
-        <v>0.026379074507723348</v>
+        <v>0.0060670557782219175</v>
       </c>
       <c r="V21" s="0">
-        <v>0.026491693325072892</v>
+        <v>0.0065841089004013975</v>
       </c>
       <c r="W21" s="0">
-        <v>0.028939673599928269</v>
+        <v>0.0073219937861631968</v>
       </c>
       <c r="X21" s="0">
-        <v>0.028325366878732116</v>
+        <v>0.0073162348904180488</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.027381645431500304</v>
+        <v>0.0073319146220826451</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.026291098933103517</v>
+        <v>0.0068299428945308134</v>
       </c>
       <c r="AA21" s="0">
-        <v>0.025874711286077247</v>
+        <v>0.006903292499460572</v>
       </c>
       <c r="AB21" s="0">
-        <v>0.025574158192530973</v>
+        <v>0.0070363670669005944</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.025214037698882912</v>
+        <v>0.0070786894350243663</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.024699904269313282</v>
+        <v>0.007021738780132538</v>
       </c>
       <c r="AE21" s="0">
-        <v>0.024565147411312667</v>
+        <v>0.0071276906248575571</v>
       </c>
       <c r="AF21" s="0">
-        <v>0.024493203955550977</v>
+        <v>0.0072512651529277718</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.024463693868114159</v>
+        <v>0.0073866754369451429</v>
       </c>
       <c r="AH21" s="0">
-        <v>0.024184144215490918</v>
+        <v>0.0073803665706097862</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.023675235699143572</v>
+        <v>0.0072377575244518466</v>
       </c>
       <c r="AJ21" s="0">
-        <v>0.023321418376710305</v>
+        <v>0.0071629142263941519</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.023224527262115369</v>
+        <v>0.0072159004000708045</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.023173349342426045</v>
+        <v>0.0072856105533179406</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.023110350361963464</v>
+        <v>0.0073410993797585694</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.022991107221329545</v>
+        <v>0.0073568427641023263</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.022788686087050852</v>
+        <v>0.007316700920592484</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="B22" s="0">
-        <v>-0.14435212149250803</v>
+        <v>-0.29656591159884144</v>
       </c>
       <c r="C22" s="0">
-        <v>0.034887473148824587</v>
+        <v>0.0016869110289172815</v>
       </c>
       <c r="D22" s="0">
-        <v>0.035416509304760528</v>
+        <v>0.0015495070934896881</v>
       </c>
       <c r="E22" s="0">
-        <v>0.035223204395472586</v>
+        <v>0.0023294883340150342</v>
       </c>
       <c r="F22" s="0">
-        <v>0.035267467833033625</v>
+        <v>0.0015641784639507555</v>
       </c>
       <c r="G22" s="0">
-        <v>0.033733654965963956</v>
+        <v>0.0017995922736679555</v>
       </c>
       <c r="H22" s="0">
-        <v>0.033704342901700199</v>
+        <v>0.0016971833843786185</v>
       </c>
       <c r="I22" s="0">
-        <v>0.032736797698583855</v>
+        <v>0.00093113297090029374</v>
       </c>
       <c r="J22" s="0">
-        <v>0.031107429864099458</v>
+        <v>-0.0014541739990484328</v>
       </c>
       <c r="K22" s="0">
-        <v>0.0363945639168178</v>
+        <v>0.0054105306136369904</v>
       </c>
       <c r="L22" s="0">
-        <v>0.0313212512053846</v>
+        <v>0.0041715993553447014</v>
       </c>
       <c r="M22" s="0">
-        <v>0.031017354374989644</v>
+        <v>0.0035332212164288375</v>
       </c>
       <c r="N22" s="0">
-        <v>0.031014578765733325</v>
+        <v>0.0049765294392878651</v>
       </c>
       <c r="O22" s="0">
-        <v>0.029711237358803707</v>
+        <v>0.0050907734061543791</v>
       </c>
       <c r="P22" s="0">
-        <v>0.028799075799616887</v>
+        <v>0.0044434638521239789</v>
       </c>
       <c r="Q22" s="0">
-        <v>0.028796915963976089</v>
+        <v>0.0037696805031450994</v>
       </c>
       <c r="R22" s="0">
-        <v>0.028473166139476296</v>
+        <v>0.0038000392410765188</v>
       </c>
       <c r="S22" s="0">
-        <v>0.027981098369584307</v>
+        <v>0.0040000009381684215</v>
       </c>
       <c r="T22" s="0">
-        <v>0.02825101979352989</v>
+        <v>0.0060546463244369698</v>
       </c>
       <c r="U22" s="0">
-        <v>0.026883589369893421</v>
+        <v>0.0053675815568361741</v>
       </c>
       <c r="V22" s="0">
-        <v>0.027744270989120939</v>
+        <v>0.0060724069461508623</v>
       </c>
       <c r="W22" s="0">
-        <v>0.029855010074807592</v>
+        <v>0.0063846221065971889</v>
       </c>
       <c r="X22" s="0">
-        <v>0.029470682871491124</v>
+        <v>0.0061997268517199047</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.028900617747231169</v>
+        <v>0.0062650260873949471</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.027596652260910737</v>
+        <v>0.0057268358037010853</v>
       </c>
       <c r="AA22" s="0">
-        <v>0.026976732091439991</v>
+        <v>0.0058948313439737086</v>
       </c>
       <c r="AB22" s="0">
-        <v>0.026373807281161125</v>
+        <v>0.0060216073972580711</v>
       </c>
       <c r="AC22" s="0">
-        <v>0.026038085372129021</v>
+        <v>0.0061535662313675233</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.025610669418672741</v>
+        <v>0.0062291819825297298</v>
       </c>
       <c r="AE22" s="0">
-        <v>0.025042508544069961</v>
+        <v>0.0062236816634450862</v>
       </c>
       <c r="AF22" s="0">
-        <v>0.024853055277269293</v>
+        <v>0.0063508833060074918</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.024729719925690025</v>
+        <v>0.0064906102639551112</v>
       </c>
       <c r="AH22" s="0">
-        <v>0.024653095575650513</v>
+        <v>0.0066403082155331149</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.024333664979788495</v>
+        <v>0.0066626600036741278</v>
       </c>
       <c r="AJ22" s="0">
-        <v>0.023791382871594768</v>
+        <v>0.0065593134526957531</v>
       </c>
       <c r="AK22" s="0">
-        <v>0.023405832229651705</v>
+        <v>0.0065131485927777564</v>
       </c>
       <c r="AL22" s="0">
-        <v>0.023277193624352863</v>
+        <v>0.0065806998345903957</v>
       </c>
       <c r="AM22" s="0">
-        <v>0.023196416730579886</v>
+        <v>0.006662171460618216</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.023106646921021483</v>
+        <v>0.0067295206201916143</v>
       </c>
       <c r="AO22" s="0">
-        <v>0.022963426444302243</v>
+        <v>0.0067585369403143159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="B23" s="0">
-        <v>-0.149038256064499</v>
+        <v>-0.30364497289721182</v>
       </c>
       <c r="C23" s="0">
-        <v>0.039711273916062925</v>
+        <v>-5.879842801250371e-05</v>
       </c>
       <c r="D23" s="0">
-        <v>0.04059833799230441</v>
+        <v>0.00045302183019600375</v>
       </c>
       <c r="E23" s="0">
-        <v>0.039550238415279333</v>
+        <v>0.00054474550657396183</v>
       </c>
       <c r="F23" s="0">
-        <v>0.04057968806128974</v>
+        <v>0.0013558659443911867</v>
       </c>
       <c r="G23" s="0">
-        <v>0.038450089961774431</v>
+        <v>0.00069484040725288859</v>
       </c>
       <c r="H23" s="0">
-        <v>0.038733818855243393</v>
+        <v>0.00044745845331295068</v>
       </c>
       <c r="I23" s="0">
-        <v>0.03772184662160058</v>
+        <v>8.0818528206057683e-06</v>
       </c>
       <c r="J23" s="0">
-        <v>0.036416470629528248</v>
+        <v>-0.0018700812194721861</v>
       </c>
       <c r="K23" s="0">
-        <v>0.041001494290079037</v>
+        <v>0.0039687433605766738</v>
       </c>
       <c r="L23" s="0">
-        <v>0.035251298753127422</v>
+        <v>0.0031963623294938787</v>
       </c>
       <c r="M23" s="0">
-        <v>0.03478638267719672</v>
+        <v>0.0022130935870076454</v>
       </c>
       <c r="N23" s="0">
-        <v>0.034868885721015312</v>
+        <v>0.0031581276244708762</v>
       </c>
       <c r="O23" s="0">
-        <v>0.034369755817296566</v>
+        <v>0.003416288446156344</v>
       </c>
       <c r="P23" s="0">
-        <v>0.033054478976621199</v>
+        <v>0.0031449986923460412</v>
       </c>
       <c r="Q23" s="0">
-        <v>0.031599019816536546</v>
+        <v>0.0031474262295897414</v>
       </c>
       <c r="R23" s="0">
-        <v>0.031810258714197008</v>
+        <v>0.0030230231603926906</v>
       </c>
       <c r="S23" s="0">
-        <v>0.03109703513711079</v>
+        <v>0.0033283218713628278</v>
       </c>
       <c r="T23" s="0">
-        <v>0.031287086094557617</v>
+        <v>0.0051047062096803604</v>
       </c>
       <c r="U23" s="0">
-        <v>0.028912825828062923</v>
+        <v>0.0044359172359440492</v>
       </c>
       <c r="V23" s="0">
-        <v>0.028906012542813251</v>
+        <v>0.0052038822209320261</v>
       </c>
       <c r="W23" s="0">
-        <v>0.031385007968548227</v>
+        <v>0.0058332020609638373</v>
       </c>
       <c r="X23" s="0">
-        <v>0.030384777471479101</v>
+        <v>0.0051766127441901918</v>
       </c>
       <c r="Y23" s="0">
-        <v>0.030288492762665226</v>
+        <v>0.0053766197038094344</v>
       </c>
       <c r="Z23" s="0">
-        <v>0.029566968206794043</v>
+        <v>0.0050010248604745247</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.028974228810193191</v>
+        <v>0.0053230253175443722</v>
       </c>
       <c r="AB23" s="0">
-        <v>0.028078931221948985</v>
+        <v>0.0055069064528390013</v>
       </c>
       <c r="AC23" s="0">
-        <v>0.027452992777937779</v>
+        <v>0.005686501729884442</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.027038851591859005</v>
+        <v>0.0058574045081777161</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.026543172461096439</v>
+        <v>0.0059831828337058475</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.025916191802524316</v>
+        <v>0.0060396165763428114</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.025664643219102074</v>
+        <v>0.0061915059637509444</v>
       </c>
       <c r="AH23" s="0">
-        <v>0.025483073639831062</v>
+        <v>0.0063504977298397634</v>
       </c>
       <c r="AI23" s="0">
-        <v>0.025353177001245678</v>
+        <v>0.006517650002419443</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.024989490267896972</v>
+        <v>0.0065748945415730385</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.024410911028497722</v>
+        <v>0.0065192957661745618</v>
       </c>
       <c r="AL23" s="0">
-        <v>0.023990198728516182</v>
+        <v>0.0065080181922977766</v>
       </c>
       <c r="AM23" s="0">
-        <v>0.02382554941444005</v>
+        <v>0.0065932071014003822</v>
       </c>
       <c r="AN23" s="0">
-        <v>0.023711148548781948</v>
+        <v>0.0066890014635337764</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.023591002216054771</v>
+        <v>0.0067709434324609392</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="B24" s="0">
-        <v>-0.15362852480981454</v>
+        <v>-0.31057921546427419</v>
       </c>
       <c r="C24" s="0">
-        <v>0.047472488091334364</v>
+        <v>-0.00098253363573918076</v>
       </c>
       <c r="D24" s="0">
-        <v>0.048401417813244127</v>
+        <v>-0.0012257700022339521</v>
       </c>
       <c r="E24" s="0">
-        <v>0.048050732762561221</v>
+        <v>0.0013974346020181427</v>
       </c>
       <c r="F24" s="0">
-        <v>0.048483929640721089</v>
+        <v>0.0010543016321102655</v>
       </c>
       <c r="G24" s="0">
-        <v>0.045116563106180729</v>
+        <v>-0.00085877871240763954</v>
       </c>
       <c r="H24" s="0">
-        <v>0.045547979834380664</v>
+        <v>-0.0007936736713103612</v>
       </c>
       <c r="I24" s="0">
-        <v>0.04410367363642937</v>
+        <v>-0.0016559016065943769</v>
       </c>
       <c r="J24" s="0">
-        <v>0.042938619007640712</v>
+        <v>-0.0030930704232947953</v>
       </c>
       <c r="K24" s="0">
-        <v>0.047717829248015653</v>
+        <v>0.0021055214276182329</v>
       </c>
       <c r="L24" s="0">
-        <v>0.040917522297043644</v>
+        <v>0.0016359244934665233</v>
       </c>
       <c r="M24" s="0">
-        <v>0.039929893414434411</v>
+        <v>0.0010739160967429889</v>
       </c>
       <c r="N24" s="0">
-        <v>0.039629930485494472</v>
+        <v>0.0014583158934132294</v>
       </c>
       <c r="O24" s="0">
-        <v>0.039162701388749256</v>
+        <v>0.0012802063467833326</v>
       </c>
       <c r="P24" s="0">
-        <v>0.038794887724288261</v>
+        <v>0.0010238084907682196</v>
       </c>
       <c r="Q24" s="0">
-        <v>0.036764508021758235</v>
+        <v>0.001903707723545733</v>
       </c>
       <c r="R24" s="0">
-        <v>0.035365108383657529</v>
+        <v>0.0024218245156962669</v>
       </c>
       <c r="S24" s="0">
-        <v>0.034596353318300542</v>
+        <v>0.0018475598273173966</v>
       </c>
       <c r="T24" s="0">
-        <v>0.034192068037134454</v>
+        <v>0.0034347772414874784</v>
       </c>
       <c r="U24" s="0">
-        <v>0.031956156004780141</v>
+        <v>0.0030439128078231987</v>
       </c>
       <c r="V24" s="0">
-        <v>0.031208995865299873</v>
+        <v>0.0039440823243202658</v>
       </c>
       <c r="W24" s="0">
-        <v>0.032197327657004872</v>
+        <v>0.0043345359582885349</v>
       </c>
       <c r="X24" s="0">
-        <v>0.031641099565548614</v>
+        <v>0.0034334645114545087</v>
       </c>
       <c r="Y24" s="0">
-        <v>0.031410531946225916</v>
+        <v>0.0039879196904739692</v>
       </c>
       <c r="Z24" s="0">
-        <v>0.031345904517283155</v>
+        <v>0.003855086616502528</v>
       </c>
       <c r="AA24" s="0">
-        <v>0.031179904892329299</v>
+        <v>0.0042822615236875021</v>
       </c>
       <c r="AB24" s="0">
-        <v>0.030245369093930739</v>
+        <v>0.0046240419132902062</v>
       </c>
       <c r="AC24" s="0">
-        <v>0.029365821786885703</v>
+        <v>0.0048893368147847494</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.028657937882128282</v>
+        <v>0.0051607834668062121</v>
       </c>
       <c r="AE24" s="0">
-        <v>0.028156233943441765</v>
+        <v>0.0053845753727132092</v>
       </c>
       <c r="AF24" s="0">
-        <v>0.027585187742545356</v>
+        <v>0.0055769091298491138</v>
       </c>
       <c r="AG24" s="0">
-        <v>0.026896028380590676</v>
+        <v>0.0057170213558991939</v>
       </c>
       <c r="AH24" s="0">
-        <v>0.026573530281878227</v>
+        <v>0.0059025039971581528</v>
       </c>
       <c r="AI24" s="0">
-        <v>0.026324368291994246</v>
+        <v>0.0060871158999285602</v>
       </c>
       <c r="AJ24" s="0">
-        <v>0.026132484423411952</v>
+        <v>0.0062774761695096925</v>
       </c>
       <c r="AK24" s="0">
-        <v>0.025720030292130793</v>
+        <v>0.0063821373731244883</v>
       </c>
       <c r="AL24" s="0">
-        <v>0.0251042632742061</v>
+        <v>0.0063921691188830888</v>
       </c>
       <c r="AM24" s="0">
-        <v>0.024646119755515516</v>
+        <v>0.0064291424210317499</v>
       </c>
       <c r="AN24" s="0">
-        <v>0.024440372072273665</v>
+        <v>0.0065385904171135975</v>
       </c>
       <c r="AO24" s="0">
-        <v>0.02428746366058801</v>
+        <v>0.0066543026653349642</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="B25" s="0">
-        <v>-0.16018025387263496</v>
+        <v>-0.32047651801363636</v>
       </c>
       <c r="C25" s="0">
-        <v>0.058052334983969278</v>
+        <v>-0.0030670015824921584</v>
       </c>
       <c r="D25" s="0">
-        <v>0.059026718143675543</v>
+        <v>-0.0029356698932668946</v>
       </c>
       <c r="E25" s="0">
-        <v>0.057646746001998851</v>
+        <v>-0.0027590182894431984</v>
       </c>
       <c r="F25" s="0">
-        <v>0.058055711909110151</v>
+        <v>-0.0034109463199237288</v>
       </c>
       <c r="G25" s="0">
-        <v>0.054834418723098695</v>
+        <v>-0.0030551067992246792</v>
       </c>
       <c r="H25" s="0">
-        <v>0.055636764490767321</v>
+        <v>-0.0029491271730926862</v>
       </c>
       <c r="I25" s="0">
-        <v>0.053782521232761817</v>
+        <v>-0.0032616479142460867</v>
       </c>
       <c r="J25" s="0">
-        <v>0.052905546744431611</v>
+        <v>-0.0046187918462437683</v>
       </c>
       <c r="K25" s="0">
-        <v>0.057601938842459816</v>
+        <v>-0.00063793266143474564</v>
       </c>
       <c r="L25" s="0">
-        <v>0.04994454331014548</v>
+        <v>-0.00052707228461327041</v>
       </c>
       <c r="M25" s="0">
-        <v>0.048423065249687917</v>
+        <v>-0.00081403015249915055</v>
       </c>
       <c r="N25" s="0">
-        <v>0.047145234466217198</v>
+        <v>-9.5255010751290532e-05</v>
       </c>
       <c r="O25" s="0">
-        <v>0.04604546945244125</v>
+        <v>-0.00078655646724850388</v>
       </c>
       <c r="P25" s="0">
-        <v>0.046041162391693598</v>
+        <v>-0.0014213599868798958</v>
       </c>
       <c r="Q25" s="0">
-        <v>0.044427983787237571</v>
+        <v>-0.00072855704462524524</v>
       </c>
       <c r="R25" s="0">
-        <v>0.041872793937439305</v>
+        <v>0.00048438418999920341</v>
       </c>
       <c r="S25" s="0">
-        <v>0.039738154394568334</v>
+        <v>0.00136638581010916</v>
       </c>
       <c r="T25" s="0">
-        <v>0.03904848003505617</v>
+        <v>0.00168884441891672</v>
       </c>
       <c r="U25" s="0">
-        <v>0.035730790646410486</v>
+        <v>0.0010503155262706918</v>
       </c>
       <c r="V25" s="0">
-        <v>0.035452671959002355</v>
+        <v>0.0021924121161842744</v>
       </c>
       <c r="W25" s="0">
-        <v>0.035014158244247633</v>
+        <v>0.002939961615680282</v>
       </c>
       <c r="X25" s="0">
-        <v>0.032930176999015938</v>
+        <v>0.0022761318938422899</v>
       </c>
       <c r="Y25" s="0">
-        <v>0.033090304408420437</v>
+        <v>0.0023729391217483173</v>
       </c>
       <c r="Z25" s="0">
-        <v>0.032619539547223984</v>
+        <v>0.0021741981816999624</v>
       </c>
       <c r="AA25" s="0">
-        <v>0.033033240046375686</v>
+        <v>0.002595020847766145</v>
       </c>
       <c r="AB25" s="0">
-        <v>0.03233115167877422</v>
+        <v>0.0029670219193266203</v>
       </c>
       <c r="AC25" s="0">
-        <v>0.031492408094691275</v>
+        <v>0.0033624067711352122</v>
       </c>
       <c r="AD25" s="0">
-        <v>0.030526323925375416</v>
+        <v>0.0037552625455090031</v>
       </c>
       <c r="AE25" s="0">
-        <v>0.029737172043153699</v>
+        <v>0.0041326838902618684</v>
       </c>
       <c r="AF25" s="0">
-        <v>0.0291421113171722</v>
+        <v>0.0044137695309146522</v>
       </c>
       <c r="AG25" s="0">
-        <v>0.02849149530994519</v>
+        <v>0.0046798912446626888</v>
       </c>
       <c r="AH25" s="0">
-        <v>0.027737625906930512</v>
+        <v>0.0049141834936971343</v>
       </c>
       <c r="AI25" s="0">
-        <v>0.027337544877856324</v>
+        <v>0.0051356888435369653</v>
       </c>
       <c r="AJ25" s="0">
-        <v>0.027014681654147867</v>
+        <v>0.0053487573114569904</v>
       </c>
       <c r="AK25" s="0">
-        <v>0.026754967805989655</v>
+        <v>0.0055648997526468206</v>
       </c>
       <c r="AL25" s="0">
-        <v>0.026290629619933933</v>
+        <v>0.0057246627845806818</v>
       </c>
       <c r="AM25" s="0">
-        <v>0.025636292898499689</v>
+        <v>0.0058114025407281075</v>
       </c>
       <c r="AN25" s="0">
-        <v>0.025137782992584248</v>
+        <v>0.0059042189630143516</v>
       </c>
       <c r="AO25" s="0">
-        <v>0.024886748948003259</v>
+        <v>0.0060418014225013207</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="B26" s="0">
-        <v>-0.16687550237039195</v>
+        <v>-0.33059062673060108</v>
       </c>
       <c r="C26" s="0">
-        <v>0.073294642872468688</v>
+        <v>-0.0048103230050969975</v>
       </c>
       <c r="D26" s="0">
-        <v>0.074166063288269926</v>
+        <v>-0.0049521100847327712</v>
       </c>
       <c r="E26" s="0">
-        <v>0.072447933973772916</v>
+        <v>-0.0042540989014180509</v>
       </c>
       <c r="F26" s="0">
-        <v>0.073706081090952932</v>
+        <v>-0.003872176951050816</v>
       </c>
       <c r="G26" s="0">
-        <v>0.069106671648730508</v>
+        <v>-0.0044976153748544981</v>
       </c>
       <c r="H26" s="0">
-        <v>0.069808600493705561</v>
+        <v>-0.0050178660418563649</v>
       </c>
       <c r="I26" s="0">
-        <v>0.067158962441705175</v>
+        <v>-0.0053448484531710147</v>
       </c>
       <c r="J26" s="0">
-        <v>0.065972920615293335</v>
+        <v>-0.0062432613528869141</v>
       </c>
       <c r="K26" s="0">
-        <v>0.071364556230657739</v>
+        <v>-0.0037979488202130487</v>
       </c>
       <c r="L26" s="0">
-        <v>0.062051685810801373</v>
+        <v>-0.0034647160996737875</v>
       </c>
       <c r="M26" s="0">
-        <v>0.06098410909940595</v>
+        <v>-0.0033883803572699912</v>
       </c>
       <c r="N26" s="0">
-        <v>0.058745731134269577</v>
+        <v>-0.0024573962997235447</v>
       </c>
       <c r="O26" s="0">
-        <v>0.056676704434901116</v>
+        <v>-0.0023990451379449066</v>
       </c>
       <c r="P26" s="0">
-        <v>0.055395175910426232</v>
+        <v>-0.0040126740983795284</v>
       </c>
       <c r="Q26" s="0">
-        <v>0.054123073451053536</v>
+        <v>-0.0035837718380060191</v>
       </c>
       <c r="R26" s="0">
-        <v>0.052025918475513175</v>
+        <v>-0.0027396482700391476</v>
       </c>
       <c r="S26" s="0">
-        <v>0.048796145234708474</v>
+        <v>-0.0010628166717226856</v>
       </c>
       <c r="T26" s="0">
-        <v>0.046171591253544302</v>
+        <v>0.00068805313416707892</v>
       </c>
       <c r="U26" s="0">
-        <v>0.042000968327127436</v>
+        <v>-0.00092831507882144869</v>
       </c>
       <c r="V26" s="0">
-        <v>0.041015225718524534</v>
+        <v>-0.00016308079956431964</v>
       </c>
       <c r="W26" s="0">
-        <v>0.041243706899655154</v>
+        <v>0.00087678575488607568</v>
       </c>
       <c r="X26" s="0">
-        <v>0.037841784563695607</v>
+        <v>0.0010482680612358924</v>
       </c>
       <c r="Y26" s="0">
-        <v>0.036218579668907729</v>
+        <v>0.0012227268985723397</v>
       </c>
       <c r="Z26" s="0">
-        <v>0.035896661782127602</v>
+        <v>-0.00010748145077837053</v>
       </c>
       <c r="AA26" s="0">
-        <v>0.036074657781349634</v>
+        <v>0.00022799244295606291</v>
       </c>
       <c r="AB26" s="0">
-        <v>0.035555358286413527</v>
+        <v>0.00066341931827217245</v>
       </c>
       <c r="AC26" s="0">
-        <v>0.035031004175574226</v>
+        <v>0.0010855912770462799</v>
       </c>
       <c r="AD26" s="0">
-        <v>0.033987128337487911</v>
+        <v>0.0015934629313546279</v>
       </c>
       <c r="AE26" s="0">
-        <v>0.032832531264481851</v>
+        <v>0.0021383853282130562</v>
       </c>
       <c r="AF26" s="0">
-        <v>0.031877161977073722</v>
+        <v>0.0026537721130437141</v>
       </c>
       <c r="AG26" s="0">
-        <v>0.031102429882309782</v>
+        <v>0.0030004070083339859</v>
       </c>
       <c r="AH26" s="0">
-        <v>0.030293678946752722</v>
+        <v>0.0033602866108188622</v>
       </c>
       <c r="AI26" s="0">
-        <v>0.029403363483555208</v>
+        <v>0.0037207516767089168</v>
       </c>
       <c r="AJ26" s="0">
-        <v>0.028860329536016121</v>
+        <v>0.003990351544911357</v>
       </c>
       <c r="AK26" s="0">
-        <v>0.028401006206263756</v>
+        <v>0.004238697990251475</v>
       </c>
       <c r="AL26" s="0">
-        <v>0.028015272479436946</v>
+        <v>0.00448689707652379</v>
       </c>
       <c r="AM26" s="0">
-        <v>0.027444172888455638</v>
+        <v>0.004719563246751322</v>
       </c>
       <c r="AN26" s="0">
-        <v>0.026701576790508497</v>
+        <v>0.004912292398908313</v>
       </c>
       <c r="AO26" s="0">
-        <v>0.026118150017442558</v>
+        <v>0.0050839228247978136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="B27" s="0">
-        <v>-0.17446860650082407</v>
+        <v>-0.34206107188288382</v>
       </c>
       <c r="C27" s="0">
-        <v>0.092555159552896255</v>
+        <v>-0.0057263199392215778</v>
       </c>
       <c r="D27" s="0">
-        <v>0.093302680686413841</v>
+        <v>-0.0057337414703068244</v>
       </c>
       <c r="E27" s="0">
-        <v>0.09146745292910724</v>
+        <v>-0.005681535972171645</v>
       </c>
       <c r="F27" s="0">
-        <v>0.092895468622746141</v>
+        <v>-0.0056097647342499765</v>
       </c>
       <c r="G27" s="0">
-        <v>0.088320483890324653</v>
+        <v>-0.0058271248369727328</v>
       </c>
       <c r="H27" s="0">
-        <v>0.090127091301401327</v>
+        <v>-0.0058891585452983388</v>
       </c>
       <c r="I27" s="0">
-        <v>0.085874908739182923</v>
+        <v>-0.0063098343913354634</v>
       </c>
       <c r="J27" s="0">
-        <v>0.084826617399577808</v>
+        <v>-0.0075405078841403244</v>
       </c>
       <c r="K27" s="0">
-        <v>0.092075548512290412</v>
+        <v>-0.0056907628312938587</v>
       </c>
       <c r="L27" s="0">
-        <v>0.08094318702821468</v>
+        <v>-0.00586490066403562</v>
       </c>
       <c r="M27" s="0">
-        <v>0.079472695321694972</v>
+        <v>-0.0059041649184424705</v>
       </c>
       <c r="N27" s="0">
-        <v>0.076816096323588379</v>
+        <v>-0.0051417651461919981</v>
       </c>
       <c r="O27" s="0">
-        <v>0.074462606041181323</v>
+        <v>-0.0047684495650031191</v>
       </c>
       <c r="P27" s="0">
-        <v>0.071976068153948414</v>
+        <v>-0.0055940677003275645</v>
       </c>
       <c r="Q27" s="0">
-        <v>0.069806980474972136</v>
+        <v>-0.0063993523238046711</v>
       </c>
       <c r="R27" s="0">
-        <v>0.067698143906895616</v>
+        <v>-0.0061799265877258624</v>
       </c>
       <c r="S27" s="0">
-        <v>0.065123837513695618</v>
+        <v>-0.0052335935938422062</v>
       </c>
       <c r="T27" s="0">
-        <v>0.061227117932173281</v>
+        <v>-0.0021698970178442687</v>
       </c>
       <c r="U27" s="0">
-        <v>0.054242626871331009</v>
+        <v>-0.0017240743213400832</v>
       </c>
       <c r="V27" s="0">
-        <v>0.05253363053791596</v>
+        <v>-0.0032198040469720406</v>
       </c>
       <c r="W27" s="0">
-        <v>0.052654716147340318</v>
+        <v>-0.0022137947985836574</v>
       </c>
       <c r="X27" s="0">
-        <v>0.048729314433948387</v>
+        <v>-0.0018268037247965972</v>
       </c>
       <c r="Y27" s="0">
-        <v>0.045529056377618518</v>
+        <v>-0.00059898196956405291</v>
       </c>
       <c r="Z27" s="0">
-        <v>0.043849416294400416</v>
+        <v>-0.0013296883599684525</v>
       </c>
       <c r="AA27" s="0">
-        <v>0.044248458562545188</v>
+        <v>-0.0027600940771331513</v>
       </c>
       <c r="AB27" s="0">
-        <v>0.042921707751227348</v>
+        <v>-0.0024726665657147256</v>
       </c>
       <c r="AC27" s="0">
-        <v>0.042746728786249667</v>
+        <v>-0.0020549673912406011</v>
       </c>
       <c r="AD27" s="0">
-        <v>0.041900434958518674</v>
+        <v>-0.001575746100548838</v>
       </c>
       <c r="AE27" s="0">
-        <v>0.040327502653546253</v>
+        <v>-0.00091709932045625083</v>
       </c>
       <c r="AF27" s="0">
-        <v>0.038666606794727186</v>
+        <v>-0.00014817985407500396</v>
       </c>
       <c r="AG27" s="0">
-        <v>0.03726317445956185</v>
+        <v>0.00057639375337951949</v>
       </c>
       <c r="AH27" s="0">
-        <v>0.036038286966801988</v>
+        <v>0.0010149657300946391</v>
       </c>
       <c r="AI27" s="0">
-        <v>0.034819354077831148</v>
+        <v>0.0015184119660005063</v>
       </c>
       <c r="AJ27" s="0">
-        <v>0.033556878102090744</v>
+        <v>0.0020780157937414119</v>
       </c>
       <c r="AK27" s="0">
-        <v>0.0326592040244525</v>
+        <v>0.0024223735677296079</v>
       </c>
       <c r="AL27" s="0">
-        <v>0.031864670199303183</v>
+        <v>0.0027242074029349582</v>
       </c>
       <c r="AM27" s="0">
-        <v>0.031169013431780239</v>
+        <v>0.0030208280425088</v>
       </c>
       <c r="AN27" s="0">
-        <v>0.030317997632603282</v>
+        <v>0.0033694766755624473</v>
       </c>
       <c r="AO27" s="0">
-        <v>0.029328711989957564</v>
+        <v>0.0037346096220256643</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="B28" s="0">
-        <v>-0.18053673689619454</v>
+        <v>-0.35122783104769395</v>
       </c>
       <c r="C28" s="0">
-        <v>0.11323185106344581</v>
+        <v>-0.0041579312198773482</v>
       </c>
       <c r="D28" s="0">
-        <v>0.11378411847534159</v>
+        <v>-0.0042883405166482536</v>
       </c>
       <c r="E28" s="0">
-        <v>0.11156003848430623</v>
+        <v>-0.0039240802003600627</v>
       </c>
       <c r="F28" s="0">
-        <v>0.11363355971427537</v>
+        <v>-0.0043733364402434617</v>
       </c>
       <c r="G28" s="0">
-        <v>0.10859477503679291</v>
+        <v>-0.0048131851523909716</v>
       </c>
       <c r="H28" s="0">
-        <v>0.11084496145800106</v>
+        <v>-0.0051475711382250825</v>
       </c>
       <c r="I28" s="0">
-        <v>0.1066407714704329</v>
+        <v>-0.004960311069210902</v>
       </c>
       <c r="J28" s="0">
-        <v>0.10505942212244587</v>
+        <v>-0.0064370378134325033</v>
       </c>
       <c r="K28" s="0">
-        <v>0.11274615187605505</v>
+        <v>-0.005909175414684234</v>
       </c>
       <c r="L28" s="0">
-        <v>0.10162410518623778</v>
+        <v>-0.0053275591200510784</v>
       </c>
       <c r="M28" s="0">
-        <v>0.10076356790341179</v>
+        <v>-0.0066667262171453984</v>
       </c>
       <c r="N28" s="0">
-        <v>0.098106780629894808</v>
+        <v>-0.0062517780204624455</v>
       </c>
       <c r="O28" s="0">
-        <v>0.095818850827927557</v>
+        <v>-0.0064520280196992139</v>
       </c>
       <c r="P28" s="0">
-        <v>0.092900077352466442</v>
+        <v>-0.0067759477488310675</v>
       </c>
       <c r="Q28" s="0">
-        <v>0.090419993733363582</v>
+        <v>-0.0069856344407091837</v>
       </c>
       <c r="R28" s="0">
-        <v>0.087638688515871088</v>
+        <v>-0.0080376173646989849</v>
       </c>
       <c r="S28" s="0">
-        <v>0.085500374327554654</v>
+        <v>-0.0084542271818216358</v>
       </c>
       <c r="T28" s="0">
-        <v>0.081833893312001971</v>
+        <v>-0.0071219273626296434</v>
       </c>
       <c r="U28" s="0">
-        <v>0.073523326171597819</v>
+        <v>-0.0049353799882384981</v>
       </c>
       <c r="V28" s="0">
-        <v>0.070902514888381826</v>
+        <v>-0.0042708225292130576</v>
       </c>
       <c r="W28" s="0">
-        <v>0.070932990601530035</v>
+        <v>-0.0062702345016468208</v>
       </c>
       <c r="X28" s="0">
-        <v>0.065849006507690405</v>
+        <v>-0.0061971272765481327</v>
       </c>
       <c r="Y28" s="0">
-        <v>0.062760995708639924</v>
+        <v>-0.0048542885891689844</v>
       </c>
       <c r="Z28" s="0">
-        <v>0.059945863204743988</v>
+        <v>-0.0039552629699439864</v>
       </c>
       <c r="AA28" s="0">
-        <v>0.058547036693473609</v>
+        <v>-0.0045809844673845709</v>
       </c>
       <c r="AB28" s="0">
-        <v>0.055789493690418634</v>
+        <v>-0.0070966014193406387</v>
       </c>
       <c r="AC28" s="0">
-        <v>0.055069640842144683</v>
+        <v>-0.0068342389063087133</v>
       </c>
       <c r="AD28" s="0">
-        <v>0.054797203492236733</v>
+        <v>-0.0063589370753271849</v>
       </c>
       <c r="AE28" s="0">
-        <v>0.053594663780907333</v>
+        <v>-0.0058008311178170862</v>
       </c>
       <c r="AF28" s="0">
-        <v>0.051485647793147862</v>
+        <v>-0.0049167300452437465</v>
       </c>
       <c r="AG28" s="0">
-        <v>0.049281616315618157</v>
+        <v>-0.003793954924230231</v>
       </c>
       <c r="AH28" s="0">
-        <v>0.0473796614782971</v>
+        <v>-0.0027419003367830097</v>
       </c>
       <c r="AI28" s="0">
-        <v>0.045616888575716066</v>
+        <v>-0.0021552193513667186</v>
       </c>
       <c r="AJ28" s="0">
-        <v>0.043883590011063296</v>
+        <v>-0.0014176117577008338</v>
       </c>
       <c r="AK28" s="0">
-        <v>0.042124616237682981</v>
+        <v>-0.00053128282880421254</v>
       </c>
       <c r="AL28" s="0">
-        <v>0.040745692613574566</v>
+        <v>-6.2812453416440157e-05</v>
       </c>
       <c r="AM28" s="0">
-        <v>0.039479482319118638</v>
+        <v>0.00033100208539946192</v>
       </c>
       <c r="AN28" s="0">
-        <v>0.038333779494188029</v>
+        <v>0.00071347480844927136</v>
       </c>
       <c r="AO28" s="0">
-        <v>0.037043252260771063</v>
+        <v>0.0012589064313768519</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="B29" s="0">
-        <v>-0.18429152288510142</v>
+        <v>-0.35689996012751268</v>
       </c>
       <c r="C29" s="0">
-        <v>0.12898082270527375</v>
+        <v>-0.0009134084786991465</v>
       </c>
       <c r="D29" s="0">
-        <v>0.12982282718624003</v>
+        <v>-0.00083800819255470732</v>
       </c>
       <c r="E29" s="0">
-        <v>0.12824077981208545</v>
+        <v>-0.001073411228763323</v>
       </c>
       <c r="F29" s="0">
-        <v>0.13030234285355866</v>
+        <v>-0.0011017660153455598</v>
       </c>
       <c r="G29" s="0">
-        <v>0.1263506488306006</v>
+        <v>-0.0013078441415126237</v>
       </c>
       <c r="H29" s="0">
-        <v>0.12884467303551767</v>
+        <v>-0.0016223370518814837</v>
       </c>
       <c r="I29" s="0">
-        <v>0.12502505670007794</v>
+        <v>-0.0017223849133291978</v>
       </c>
       <c r="J29" s="0">
-        <v>0.12412499343232598</v>
+        <v>-0.00234882300607678</v>
       </c>
       <c r="K29" s="0">
-        <v>0.13079558481723835</v>
+        <v>-0.0024251962853564452</v>
       </c>
       <c r="L29" s="0">
-        <v>0.12122842293246551</v>
+        <v>-0.0024169648575197772</v>
       </c>
       <c r="M29" s="0">
-        <v>0.12082785660533665</v>
+        <v>-0.0032336959450792505</v>
       </c>
       <c r="N29" s="0">
-        <v>0.11870496207418528</v>
+        <v>-0.0042100104682116389</v>
       </c>
       <c r="O29" s="0">
-        <v>0.11637663044637239</v>
+        <v>-0.0048810487040213861</v>
       </c>
       <c r="P29" s="0">
-        <v>0.11406217730848989</v>
+        <v>-0.0054016703686383871</v>
       </c>
       <c r="Q29" s="0">
-        <v>0.11151743807643691</v>
+        <v>-0.0058461579626546828</v>
       </c>
       <c r="R29" s="0">
-        <v>0.10949636493080912</v>
+        <v>-0.0063626577219172593</v>
       </c>
       <c r="S29" s="0">
-        <v>0.10731663660533305</v>
+        <v>-0.0079975310142124528</v>
       </c>
       <c r="T29" s="0">
-        <v>0.10422697046539653</v>
+        <v>-0.0082335086173102867</v>
       </c>
       <c r="U29" s="0">
-        <v>0.096455303221901489</v>
+        <v>-0.0086092584444251424</v>
       </c>
       <c r="V29" s="0">
-        <v>0.094484643220892645</v>
+        <v>-0.0069135066215480299</v>
       </c>
       <c r="W29" s="0">
-        <v>0.094532985248322002</v>
+        <v>-0.0064511499472470245</v>
       </c>
       <c r="X29" s="0">
-        <v>0.089528485028046945</v>
+        <v>-0.010219918068487112</v>
       </c>
       <c r="Y29" s="0">
-        <v>0.086575422388039253</v>
+        <v>-0.0097944382679493337</v>
       </c>
       <c r="Z29" s="0">
-        <v>0.084985520096391584</v>
+        <v>-0.0092949998111227037</v>
       </c>
       <c r="AA29" s="0">
-        <v>0.083596334155801838</v>
+        <v>-0.0079210486836919398</v>
       </c>
       <c r="AB29" s="0">
-        <v>0.080199840436175229</v>
+        <v>-0.0092355669986629706</v>
       </c>
       <c r="AC29" s="0">
-        <v>0.078483961027433061</v>
+        <v>-0.013324785507539461</v>
       </c>
       <c r="AD29" s="0">
-        <v>0.07757784256040004</v>
+        <v>-0.013097364640870947</v>
       </c>
       <c r="AE29" s="0">
-        <v>0.077143950205796188</v>
+        <v>-0.012813782879273426</v>
       </c>
       <c r="AF29" s="0">
-        <v>0.076037116578168182</v>
+        <v>-0.012547918656881558</v>
       </c>
       <c r="AG29" s="0">
-        <v>0.074348977208942457</v>
+        <v>-0.011686960293303458</v>
       </c>
       <c r="AH29" s="0">
-        <v>0.072453765350342952</v>
+        <v>-0.010331785944860901</v>
       </c>
       <c r="AI29" s="0">
-        <v>0.070889936827061503</v>
+        <v>-0.0089854104811272206</v>
       </c>
       <c r="AJ29" s="0">
-        <v>0.069278422610074816</v>
+        <v>-0.0084345004865541522</v>
       </c>
       <c r="AK29" s="0">
-        <v>0.067640276272277214</v>
+        <v>-0.0075192925854868572</v>
       </c>
       <c r="AL29" s="0">
-        <v>0.065895904466486604</v>
+        <v>-0.0062019015496169935</v>
       </c>
       <c r="AM29" s="0">
-        <v>0.064520281649981817</v>
+        <v>-0.0056930678867659424</v>
       </c>
       <c r="AN29" s="0">
-        <v>0.063175830785952042</v>
+        <v>-0.0053363956677072609</v>
       </c>
       <c r="AO29" s="0">
-        <v>0.061916940311712118</v>
+        <v>-0.0049886554851528023</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="B30" s="0">
-        <v>-0.18565771113645946</v>
+        <v>-0.35896377844683336</v>
       </c>
       <c r="C30" s="0">
-        <v>0.13977577731192187</v>
+        <v>0.0025794835660215461</v>
       </c>
       <c r="D30" s="0">
-        <v>0.14133949824916067</v>
+        <v>0.0026056923737994776</v>
       </c>
       <c r="E30" s="0">
-        <v>0.13988063410390336</v>
+        <v>0.0025277625135265722</v>
       </c>
       <c r="F30" s="0">
-        <v>0.1412281569780825</v>
+        <v>0.0024652900208054183</v>
       </c>
       <c r="G30" s="0">
-        <v>0.13938324998488058</v>
+        <v>0.002375829807938832</v>
       </c>
       <c r="H30" s="0">
-        <v>0.14094703963849817</v>
+        <v>0.0021616817893219632</v>
       </c>
       <c r="I30" s="0">
-        <v>0.13836273928255213</v>
+        <v>0.002106446197911567</v>
       </c>
       <c r="J30" s="0">
-        <v>0.13819208589511392</v>
+        <v>0.0016332101637884944</v>
       </c>
       <c r="K30" s="0">
-        <v>0.14245330148965163</v>
+        <v>0.0017564508404315903</v>
       </c>
       <c r="L30" s="0">
-        <v>0.13567832004815894</v>
+        <v>0.0016098772171277158</v>
       </c>
       <c r="M30" s="0">
-        <v>0.13610354695201021</v>
+        <v>0.00099147951595260049</v>
       </c>
       <c r="N30" s="0">
-        <v>0.13480921398181137</v>
+        <v>0.00056908132319769</v>
       </c>
       <c r="O30" s="0">
-        <v>0.13285961085172732</v>
+        <v>-0.00050990449403837514</v>
       </c>
       <c r="P30" s="0">
-        <v>0.13105231855873564</v>
+        <v>-0.0011001515850990594</v>
       </c>
       <c r="Q30" s="0">
-        <v>0.12964920132340285</v>
+        <v>-0.0018161734851606765</v>
       </c>
       <c r="R30" s="0">
-        <v>0.12787211881983984</v>
+        <v>-0.0024146565626210928</v>
       </c>
       <c r="S30" s="0">
-        <v>0.12680415240715343</v>
+        <v>-0.0032816853731938819</v>
       </c>
       <c r="T30" s="0">
-        <v>0.12456145803734817</v>
+        <v>-0.0044743476297236023</v>
       </c>
       <c r="U30" s="0">
-        <v>0.11919042724891933</v>
+        <v>-0.0060119719436986692</v>
       </c>
       <c r="V30" s="0">
-        <v>0.11637049935210385</v>
+        <v>-0.0075561504616373414</v>
       </c>
       <c r="W30" s="0">
-        <v>0.11755944515213544</v>
+        <v>-0.0060628749315919965</v>
       </c>
       <c r="X30" s="0">
-        <v>0.11459288262047411</v>
+        <v>-0.0069181478028518791</v>
       </c>
       <c r="Y30" s="0">
-        <v>0.11200613728288789</v>
+        <v>-0.011049416631677692</v>
       </c>
       <c r="Z30" s="0">
-        <v>0.1111912997402424</v>
+        <v>-0.012014170939072425</v>
       </c>
       <c r="AA30" s="0">
-        <v>0.11026438226468828</v>
+        <v>-0.012044051165635533</v>
       </c>
       <c r="AB30" s="0">
-        <v>0.10766259172112955</v>
+        <v>-0.011480276587693747</v>
       </c>
       <c r="AC30" s="0">
-        <v>0.10606608952574553</v>
+        <v>-0.014103113730287111</v>
       </c>
       <c r="AD30" s="0">
-        <v>0.10403680183464065</v>
+        <v>-0.019830120120845552</v>
       </c>
       <c r="AE30" s="0">
-        <v>0.10322878024746002</v>
+        <v>-0.019841972982971329</v>
       </c>
       <c r="AF30" s="0">
-        <v>0.10260964876268591</v>
+        <v>-0.020498116675855271</v>
       </c>
       <c r="AG30" s="0">
-        <v>0.10159200767273587</v>
+        <v>-0.021479519358160712</v>
       </c>
       <c r="AH30" s="0">
-        <v>0.10038538423545332</v>
+        <v>-0.0215461820724599</v>
       </c>
       <c r="AI30" s="0">
-        <v>0.099103518382815142</v>
+        <v>-0.020584200523447924</v>
       </c>
       <c r="AJ30" s="0">
-        <v>0.098140099772998715</v>
+        <v>-0.019714073894741471</v>
       </c>
       <c r="AK30" s="0">
-        <v>0.09689182050058319</v>
+        <v>-0.019971028096025134</v>
       </c>
       <c r="AL30" s="0">
-        <v>0.095704778763864948</v>
+        <v>-0.019497103777324106</v>
       </c>
       <c r="AM30" s="0">
-        <v>0.094557310517333501</v>
+        <v>-0.01804808970869165</v>
       </c>
       <c r="AN30" s="0">
-        <v>0.093468300774063359</v>
+        <v>-0.018254681152171673</v>
       </c>
       <c r="AO30" s="0">
-        <v>0.092323344535053475</v>
+        <v>-0.018705134089701671</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="B31" s="0">
-        <v>-0.18593570529741982</v>
+        <v>-0.3593837274849575</v>
       </c>
       <c r="C31" s="0">
-        <v>0.14655624911801743</v>
+        <v>0.0041719675712140834</v>
       </c>
       <c r="D31" s="0">
-        <v>0.14727577775364098</v>
+        <v>0.0041686125487783105</v>
       </c>
       <c r="E31" s="0">
-        <v>0.1467351039161125</v>
+        <v>0.0041574946960236774</v>
       </c>
       <c r="F31" s="0">
-        <v>0.14752333994020178</v>
+        <v>0.0041459364353691143</v>
       </c>
       <c r="G31" s="0">
-        <v>0.14636251508587886</v>
+        <v>0.0041176627425011728</v>
       </c>
       <c r="H31" s="0">
-        <v>0.14734343974025094</v>
+        <v>0.0040856485306848588</v>
       </c>
       <c r="I31" s="0">
-        <v>0.14602746794352017</v>
+        <v>0.0040374895481275807</v>
       </c>
       <c r="J31" s="0">
-        <v>0.1459335645703484</v>
+        <v>0.0039425982161222124</v>
       </c>
       <c r="K31" s="0">
-        <v>0.14824606916746946</v>
+        <v>0.0039322256257210845</v>
       </c>
       <c r="L31" s="0">
-        <v>0.14463633919560073</v>
+        <v>0.0039413730764474393</v>
       </c>
       <c r="M31" s="0">
-        <v>0.14518893077998174</v>
+        <v>0.0037010628132769911</v>
       </c>
       <c r="N31" s="0">
-        <v>0.144547009490435</v>
+        <v>0.0035263778446611685</v>
       </c>
       <c r="O31" s="0">
-        <v>0.14377018527308155</v>
+        <v>0.0032602560555043472</v>
       </c>
       <c r="P31" s="0">
-        <v>0.14253002158151415</v>
+        <v>0.0027728589970632514</v>
       </c>
       <c r="Q31" s="0">
-        <v>0.14178026890517825</v>
+        <v>0.0023769787933884405</v>
       </c>
       <c r="R31" s="0">
-        <v>0.14091511922886835</v>
+        <v>0.001983348646195089</v>
       </c>
       <c r="S31" s="0">
-        <v>0.14043500323096694</v>
+        <v>0.0015867552374012285</v>
       </c>
       <c r="T31" s="0">
-        <v>0.13937411129669722</v>
+        <v>0.0009701010851450733</v>
       </c>
       <c r="U31" s="0">
-        <v>0.13606845496095146</v>
+        <v>-0.00021825747011802225</v>
       </c>
       <c r="V31" s="0">
-        <v>0.13446508738915885</v>
+        <v>-0.0016642994452514452</v>
       </c>
       <c r="W31" s="0">
-        <v>0.13159384824794568</v>
+        <v>-0.0027202289831282623</v>
       </c>
       <c r="X31" s="0">
-        <v>0.13326026676287564</v>
+        <v>-0.0021745819294148767</v>
       </c>
       <c r="Y31" s="0">
-        <v>0.13216261552672387</v>
+        <v>-0.003620343511457326</v>
       </c>
       <c r="Z31" s="0">
-        <v>0.131521583569184</v>
+        <v>-0.0071332641494783198</v>
       </c>
       <c r="AA31" s="0">
-        <v>0.13002180951003184</v>
+        <v>-0.0082734102953343977</v>
       </c>
       <c r="AB31" s="0">
-        <v>0.12784223693960514</v>
+        <v>-0.0092111271775239811</v>
       </c>
       <c r="AC31" s="0">
-        <v>0.12659256626763274</v>
+        <v>-0.0093682309259625566</v>
       </c>
       <c r="AD31" s="0">
-        <v>0.12472547253831111</v>
+        <v>-0.01237541567919489</v>
       </c>
       <c r="AE31" s="0">
-        <v>0.1224083387600523</v>
+        <v>-0.017567204320094013</v>
       </c>
       <c r="AF31" s="0">
-        <v>0.12159195815447361</v>
+        <v>-0.017946582166304646</v>
       </c>
       <c r="AG31" s="0">
-        <v>0.1206124895135397</v>
+        <v>-0.019425564816055809</v>
       </c>
       <c r="AH31" s="0">
-        <v>0.11922521809109318</v>
+        <v>-0.021327263669097398</v>
       </c>
       <c r="AI31" s="0">
-        <v>0.11774825163241241</v>
+        <v>-0.022430462124875959</v>
       </c>
       <c r="AJ31" s="0">
-        <v>0.1164784762473064</v>
+        <v>-0.022205057719241986</v>
       </c>
       <c r="AK31" s="0">
-        <v>0.11520661364317906</v>
+        <v>-0.022591661085839161</v>
       </c>
       <c r="AL31" s="0">
-        <v>0.11366023566006317</v>
+        <v>-0.023788109603776461</v>
       </c>
       <c r="AM31" s="0">
-        <v>0.11227364357284268</v>
+        <v>-0.02420208519330096</v>
       </c>
       <c r="AN31" s="0">
-        <v>0.11113503955222412</v>
+        <v>-0.023427623336806636</v>
       </c>
       <c r="AO31" s="0">
-        <v>0.10959399128532643</v>
+        <v>-0.024770234665892149</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="B32" s="0">
-        <v>-0.18596702843074348</v>
+        <v>-0.35943104545618698</v>
       </c>
       <c r="C32" s="0">
-        <v>0.14956991890751686</v>
+        <v>0.0045360538739769819</v>
       </c>
       <c r="D32" s="0">
-        <v>0.1499860468091474</v>
+        <v>0.0045347970243554562</v>
       </c>
       <c r="E32" s="0">
-        <v>0.14973473215478383</v>
+        <v>0.0045342177891940496</v>
       </c>
       <c r="F32" s="0">
-        <v>0.15014552586245555</v>
+        <v>0.0045336376196294598</v>
       </c>
       <c r="G32" s="0">
-        <v>0.14960537353267006</v>
+        <v>0.0045310378811303162</v>
       </c>
       <c r="H32" s="0">
-        <v>0.15011723379245295</v>
+        <v>0.0045234100778321386</v>
       </c>
       <c r="I32" s="0">
-        <v>0.14947549913620911</v>
+        <v>0.0045036029201219012</v>
       </c>
       <c r="J32" s="0">
-        <v>0.149478175633803</v>
+        <v>0.0044937226223696822</v>
       </c>
       <c r="K32" s="0">
-        <v>0.15059927854177987</v>
+        <v>0.0044969384069148306</v>
       </c>
       <c r="L32" s="0">
-        <v>0.1488392953672682</v>
+        <v>0.0044856127469471247</v>
       </c>
       <c r="M32" s="0">
-        <v>0.14924000865279388</v>
+        <v>0.0044394745534394146</v>
       </c>
       <c r="N32" s="0">
-        <v>0.14901194604558007</v>
+        <v>0.0044093566399491498</v>
       </c>
       <c r="O32" s="0">
-        <v>0.14870444018515916</v>
+        <v>0.0043800414656961495</v>
       </c>
       <c r="P32" s="0">
-        <v>0.14815551637433622</v>
+        <v>0.0043235077880616792</v>
       </c>
       <c r="Q32" s="0">
-        <v>0.14786146773553027</v>
+        <v>0.0041786264597744047</v>
       </c>
       <c r="R32" s="0">
-        <v>0.14754430182997713</v>
+        <v>0.0040954178292343085</v>
       </c>
       <c r="S32" s="0">
-        <v>0.1474256006988991</v>
+        <v>0.0039693028981143781</v>
       </c>
       <c r="T32" s="0">
-        <v>0.14712151434375112</v>
+        <v>0.0038280405811494064</v>
       </c>
       <c r="U32" s="0">
-        <v>0.1440239582663011</v>
+        <v>0.0035185750697707846</v>
       </c>
       <c r="V32" s="0">
-        <v>0.14195804706724494</v>
+        <v>0.0030264652582649935</v>
       </c>
       <c r="W32" s="0">
-        <v>0.14139934953422484</v>
+        <v>0.0025339456244146299</v>
       </c>
       <c r="X32" s="0">
-        <v>0.13556126406823227</v>
+        <v>0.0020696606281534638</v>
       </c>
       <c r="Y32" s="0">
-        <v>0.14099224834441321</v>
+        <v>0.0021149845901368642</v>
       </c>
       <c r="Z32" s="0">
-        <v>0.13771511332661798</v>
+        <v>0.0012100396898879469</v>
       </c>
       <c r="AA32" s="0">
-        <v>0.13861773671100075</v>
+        <v>-0.00023103336131329976</v>
       </c>
       <c r="AB32" s="0">
-        <v>0.13886316442767341</v>
+        <v>-0.0010089069630734846</v>
       </c>
       <c r="AC32" s="0">
-        <v>0.13773924693304904</v>
+        <v>-0.0015512098158617614</v>
       </c>
       <c r="AD32" s="0">
-        <v>0.13668304454554256</v>
+        <v>-0.0017469886628040641</v>
       </c>
       <c r="AE32" s="0">
-        <v>0.1351590697245719</v>
+        <v>-0.0034477943256713784</v>
       </c>
       <c r="AF32" s="0">
-        <v>0.13360237369976335</v>
+        <v>-0.0058302523209330355</v>
       </c>
       <c r="AG32" s="0">
-        <v>0.13296121183307119</v>
+        <v>-0.0060607288482728448</v>
       </c>
       <c r="AH32" s="0">
-        <v>0.13207087909199802</v>
+        <v>-0.0071016638946593191</v>
       </c>
       <c r="AI32" s="0">
-        <v>0.13086843896307129</v>
+        <v>-0.0083247125693247243</v>
       </c>
       <c r="AJ32" s="0">
-        <v>0.12955651462065737</v>
+        <v>-0.0091610543962814626</v>
       </c>
       <c r="AK32" s="0">
-        <v>0.12845132088220171</v>
+        <v>-0.0091446834522760541</v>
       </c>
       <c r="AL32" s="0">
-        <v>0.12713738317143092</v>
+        <v>-0.0098286073045503169</v>
       </c>
       <c r="AM32" s="0">
-        <v>0.1257746635981688</v>
+        <v>-0.010677504275628193</v>
       </c>
       <c r="AN32" s="0">
-        <v>0.12454353197385522</v>
+        <v>-0.011055148923506175</v>
       </c>
       <c r="AO32" s="0">
-        <v>0.1234879617762927</v>
+        <v>-0.010747555065157925</v>
       </c>
     </row>
   </sheetData>
